--- a/docs/operacao/modelo-caixa-anuncios.xlsx
+++ b/docs/operacao/modelo-caixa-anuncios.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="404">
   <si>
     <t xml:space="preserve">Resumo — caixa necessário para o teste de anúncios</t>
   </si>
@@ -151,7 +151,7 @@
     <t xml:space="preserve">Taxas adiantadas (logística + transação)</t>
   </si>
   <si>
-    <t xml:space="preserve">COD: saldo de expedição + transação; antec.: manuseio</t>
+    <t xml:space="preserve">COD: logística + transação; antec.: manuseio (tudo do saldo de expedição)</t>
   </si>
   <si>
     <t xml:space="preserve">Estorno do que não foi entregue, já líquido da taxa de recusa/devolução</t>
@@ -400,13 +400,13 @@
     <t xml:space="preserve">Frete de retorno na devolução (depende do ticket)</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTIMADO (R$ 25 − R$ 5 de manuseio); operador diz que tende a ser maior — medir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo TOTAL da devolução (frete + manuseio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10: devolver = frete + manuseio</t>
+    <t xml:space="preserve">Operador, 09/10: entre R$ 30 e R$ 60; usei o meio. Medir nas primeiras devoluções</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo do RETORNO na devolução (frete + manuseio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: para devolver paga frete + manuseio. Soma-se a isso as taxas já pagas, que não voltam (chave abaixo)</t>
   </si>
   <si>
     <t xml:space="preserve">Impostos sobre faturamento recebido</t>
@@ -490,13 +490,13 @@
     <t xml:space="preserve">Como o caixa sai (chaves 1 = sim / 0 = não)</t>
   </si>
   <si>
-    <t xml:space="preserve">Produto sai do SEU caixa no dia do pedido?</t>
+    <t xml:space="preserve">Produto sai do caixa (saldo de expedição) após a venda? (1 = sim)</t>
   </si>
   <si>
     <t xml:space="preserve">1/0</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador: pago antecipadamente</t>
+    <t xml:space="preserve">Operador, 09/10: o custo do produto sai do saldo de expedição após toda venda</t>
   </si>
   <si>
     <t xml:space="preserve">COD: dias do pedido criado até 'em separação' (débito do saldo de expedição)</t>
@@ -508,13 +508,19 @@
     <t xml:space="preserve">Logística (entrega R$ 19,99 + manuseio) sai do saldo de expedição? (1 = sim)</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador: taxas antecipadas; blog Coinzz: saldo debitado em 'em separação'</t>
+    <t xml:space="preserve">Operador, 09/10: todo o caixa fica no saldo de expedição, de onde saem os custos do pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na devolução, as taxas já pagas (entrega, transação, manuseio original) NÃO voltam? (1 = não voltam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: 'sim, perde'</t>
   </si>
   <si>
     <t xml:space="preserve">Transação COD (6,99% + R$ 2,49) também sai do caixa antes do repasse? (1 = sim)</t>
   </si>
   <si>
-    <t xml:space="preserve">Conservador. 0 = abatida do repasse. A CONFIRMAR</t>
+    <t xml:space="preserve">Operador, 09/10: a transação sai do valor em caixa antes do repasse</t>
   </si>
   <si>
     <t xml:space="preserve">Seu caixa</t>
@@ -592,13 +598,16 @@
     <t xml:space="preserve">Perda esperada por devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">antecipado: taxa MP não volta</t>
+    <t xml:space="preserve">devolução: frete + manuseio de retorno + taxas já pagas que não voltam</t>
   </si>
   <si>
     <t xml:space="preserve">Margem esperada (antes de lead/IA/WhatsApp)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead (CPL ÷ conversão)</t>
+    <t xml:space="preserve">Lead (CPL ÷ conversão, com imposto da Meta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 1,50 + 13,83% de imposto</t>
   </si>
   <si>
     <t xml:space="preserve">IA (custo por lead ÷ conversão)</t>
@@ -670,13 +679,13 @@
     <t xml:space="preserve">Pedidos antec. criados</t>
   </si>
   <si>
-    <t xml:space="preserve">COD: produto (pedido) + taxas (separação)</t>
+    <t xml:space="preserve">COD: produto + taxas (saldo de expedição)</t>
   </si>
   <si>
     <t xml:space="preserve">COD: recusa (estorno − taxa)</t>
   </si>
   <si>
-    <t xml:space="preserve">COD: devolução (estorno − taxa)</t>
+    <t xml:space="preserve">COD: devolução (estorno − custos)</t>
   </si>
   <si>
     <t xml:space="preserve">COD: repasse (entrada)</t>
@@ -685,7 +694,7 @@
     <t xml:space="preserve">Antec.: entrada MP</t>
   </si>
   <si>
-    <t xml:space="preserve">Antec.: produto + manuseio no pedido</t>
+    <t xml:space="preserve">Antec.: produto + manuseio (saldo de expedição)</t>
   </si>
   <si>
     <t xml:space="preserve">Antec.: devolução</t>
@@ -745,70 +754,70 @@
     <t xml:space="preserve">Sua resposta</t>
   </si>
   <si>
-    <t xml:space="preserve">Devolução: qual o valor do frete de retorno hoje (por faixa de ticket)? Hoje uso R$ 20 + R$ 5 de manuseio = R$ 25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada R$ 10 a mais no frete custa R$ 1,00 por pedido COD e R$ 0,30 por pedido antecipado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frete de retorno R$ 20,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na devolução, além de frete + manuseio, você perde alguma taxa que já pagou (entrega concluída R$ 19,99, transação)? Você disse antes 'e taxas que já paguei antes'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se perder, cada devolução custa até R$ 31 a mais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não: a logística volta, só frete + manuseio ficam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A transação do COD (6,99% + R$ 2,49) sai do saldo antes do repasse ou é abatida do repasse?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">É a maior parte do que ainda está 'adiantado': R$ 11,57 por pedido COD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sai antes (conservador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O saldo de expedição precisa estar recarregado ANTES de o pedido entrar em separação? Quanto você mantém nele?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O saldo é o caixa travado dentro da Logzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debitado 1 dia depois do pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O estoque desta rodada já está pago? Se sim, os R$ 30/peça já saíram do caixa e não entram no pico do teste.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoje conto R$ 30 por pedido no dia do pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produto sai do caixa no pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando um pedido é recusado, a Logzz estorna mesmo a entrega (R$ 19,99) e o manuseio, ficando só R$ 4,99 + R$ 5,00?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define o custo real da recusa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim, custo total R$ 9,99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Meta cobra no cartão a cada R$ 100 e no fim do mês: o saldo menor que R$ 100 de cada mês é cobrado no dia 30/31? Esses valores ficam na fatura do mês seguinte?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pequeno, mas move até R$ 100 para a fatura seguinte</t>
+    <t xml:space="preserve">Você escreveu 'R$ 2,99' de antifraude; a Central e os docs dizem R$ 2,49. Qual vale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 0,50 por pedido COD (cerca de R$ 16 no teste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 2,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na devolução você perde a entrega (R$ 19,99), a transação e o manuseio original e ainda paga frete + manuseio de retorno. O manuseio é cobrado duas vezes (R$ 5 + R$ 5)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se for uma vez só, cada devolução COD custa R$ 5 a menos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas vezes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que paga fixos (R$ 53,50), IA, WhatsApp e o saque (R$ 3,99) se todo o caixa fica no saldo de expedição? Você retira do saldo ou usa outro dinheiro?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esses custos somam ~R$ 300 no teste e não saem do saldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saem do mesmo caixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O repasse (disponível em 14 dias) recarrega o saldo de expedição direto, sem pagar o saque de R$ 3,99?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tiver que sacar e recarregar por Pix, há taxa e dia extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recarrega direto, sem taxa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O saldo de expedição bloqueia pedidos com 'saldo insuficiente'. Qual colchão mínimo você quer manter, além do pico?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido parado por falta de saldo é venda perdida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margem de R$ 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frete de retorno: R$ 30 a R$ 60. Posso usar R$ 45 até medir as primeiras devoluções?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada R$ 15 muda o pico em ~R$ 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Meta cobra a cada R$ 100 e no fim do mês: o saldo menor que R$ 100 de cada mês cai na fatura do mês seguinte?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pequeno, move até R$ 100 de fatura</t>
   </si>
   <si>
     <t xml:space="preserve">Modelei pela data do gasto</t>
   </si>
   <si>
-    <t xml:space="preserve">O imposto de 13,83% aparece no valor de cada cobrança de R$ 100? (a Meta diz que R$ 100 viram R$ 113,83)</t>
+    <t xml:space="preserve">O imposto de 13,83% aparece no valor de cada cobrança de R$ 100 no cartão?</t>
   </si>
   <si>
     <t xml:space="preserve">Soma R$ 93 sobre R$ 675 de verba</t>
@@ -817,24 +826,6 @@
     <t xml:space="preserve">13,83%</t>
   </si>
   <si>
-    <t xml:space="preserve">Antecipado: o Mercado Pago libera na hora também para cartão? Há reserva/retenção por risco nas primeiras vendas?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se retido 14 dias, o pico passa de R$ 2.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na hora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O frete de abastecimento do estoque e o saldo mínimo para operar na Logzz exigem algum valor fixo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não está na conta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zero</t>
-  </si>
-  <si>
     <t xml:space="preserve">Documentação do projeto x fontes públicas (consulta de 09/10/2026)</t>
   </si>
   <si>
@@ -928,13 +919,13 @@
     <t xml:space="preserve">Devolução / retorno de produto</t>
   </si>
   <si>
-    <t xml:space="preserve">R$ 25,00 (estimativa do operador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhuma tarifa de devolução publicada; Logzz estorna a entrega quando a entrega falha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10: custo = frete de retorno (depende do ticket) + manuseio R$ 5,00. Frete de retorno ainda estimado em R$ 20</t>
+    <t xml:space="preserve">R$ 25,00 (estimativa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma tarifa de devolução publicada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: paga frete de retorno (R$ 30–60, modelo usa R$ 45) + manuseio, e perde as taxas já pagas (entrega, transação, manuseio original)</t>
   </si>
   <si>
     <t xml:space="preserve">Central Logzz; blog Coinzz</t>
@@ -949,7 +940,7 @@
     <t xml:space="preserve">Blog Coinzz: saldo de expedição debitado quando o pedido vai para 'em separação'; estornado se a entrega falha</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador confirma o saldo de expedição; ver aba Taxas antecipadas</t>
+    <t xml:space="preserve">Operador, 09/10: todo o caixa fica no saldo de expedição e dele saem os custos do pedido; ver aba Taxas antecipadas</t>
   </si>
   <si>
     <t xml:space="preserve">blog.coinzz.com.br — pagamento na entrega</t>
@@ -1072,10 +1063,10 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Dia do pedido criado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seu caixa (operador paga antecipado)</t>
+    <t xml:space="preserve">'Em separação' (após a venda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de expedição</t>
   </si>
   <si>
     <t xml:space="preserve">R$ 30 por peça</t>
@@ -1084,15 +1075,9 @@
     <t xml:space="preserve">Volta ao estoque; sem perda (operador)</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmado</t>
-  </si>
-  <si>
     <t xml:space="preserve">'Em separação' (~1 dia após o pedido)</t>
   </si>
   <si>
-    <t xml:space="preserve">Saldo de expedição</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fixo</t>
   </si>
   <si>
@@ -1153,25 +1138,28 @@
     <t xml:space="preserve">Custo TOTAL da devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">Quando o produto chega ao centro (~D+9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frete de retorno (depende do ticket) + manuseio</t>
+    <t xml:space="preserve">Produto chega ao centro (~D+9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seu caixa / saldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frete de retorno (R$ 30–60) + manuseio + taxas já pagas que não voltam (entrega, manuseio, transação)</t>
   </si>
   <si>
     <t xml:space="preserve">Produto volta ao estoque</t>
   </si>
   <si>
-    <t xml:space="preserve">Frete de retorno ESTIMADO</t>
+    <t xml:space="preserve">Operador, 09/10; frete de retorno estimado no meio da faixa</t>
   </si>
   <si>
     <t xml:space="preserve">Volta ao estoque</t>
   </si>
   <si>
-    <t xml:space="preserve">Dia do pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devolução: já incluído na taxa de devolução</t>
+    <t xml:space="preserve">Frete + manuseio de retorno + manuseio original + taxa MP (não volta); o preço é devolvido à cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devolução: não volta</t>
   </si>
   <si>
     <t xml:space="preserve">Taxa Mercado Pago</t>
@@ -1875,7 +1863,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">-'Fluxo diário'!B99</f>
-        <v>922.58402946</v>
+        <v>1027.3772187</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
@@ -1887,7 +1875,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">'Fluxo diário'!B100</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
@@ -1899,7 +1887,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Fluxo diário'!B101</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -1911,7 +1899,7 @@
       </c>
       <c r="B12" s="4" t="n">
         <f aca="false">-'Fluxo diário'!B102</f>
-        <v>1690.93652946</v>
+        <v>1795.7297187</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
@@ -1922,7 +1910,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="4" t="n">
-        <f aca="false">Premissas!$B$61-Premissas!$B$62</f>
+        <f aca="false">Premissas!$B$62-Premissas!$B$63</f>
         <v>1075</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1935,7 +1923,7 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">B13-B9</f>
-        <v>152.41597054</v>
+        <v>47.6227813000003</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>23</v>
@@ -1947,7 +1935,7 @@
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">'Fluxo diário'!S94</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
@@ -1959,7 +1947,7 @@
       </c>
       <c r="B16" s="4" t="n">
         <f aca="false">Unitário!B18</f>
-        <v>31.85669584</v>
+        <v>24.57299514</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>27</v>
@@ -1971,7 +1959,7 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">IFERROR(B13/B9,0)</f>
-        <v>1.16520551589129</v>
+        <v>1.04635374469395</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2013,12 +2001,12 @@
         <v>36</v>
       </c>
       <c r="B21" s="12" t="n">
-        <f aca="false">(Premissas!$B$15+Premissas!$B$17)/Premissas!$B$16+Premissas!$B$18</f>
-        <v>17.74</v>
+        <f aca="false">(Premissas!$B$15*(1+Premissas!$B$14)+Premissas!$B$17)/Premissas!$B$16+Premissas!$B$18</f>
+        <v>19.8145</v>
       </c>
       <c r="C21" s="12" t="n">
-        <f aca="false">(Premissas!$B$15+Premissas!$B$17)/Premissas!$B$16+Premissas!$B$18</f>
-        <v>17.74</v>
+        <f aca="false">(Premissas!$B$15*(1+Premissas!$B$14)+Premissas!$B$17)/Premissas!$B$16+Premissas!$B$18</f>
+        <v>19.8145</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>37</v>
@@ -2045,7 +2033,7 @@
         <v>40</v>
       </c>
       <c r="B23" s="12" t="n">
-        <f aca="false">Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25</f>
+        <f aca="false">Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25</f>
         <v>36.56001</v>
       </c>
       <c r="C23" s="12" t="n">
@@ -2061,12 +2049,12 @@
         <v>42</v>
       </c>
       <c r="B24" s="12" t="n">
-        <f aca="false">-(Premissas!$B$23+Premissas!$B$24)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)+Premissas!$B$23*Premissas!$B$36+Premissas!$B$24*Premissas!$B$38</f>
-        <v>-13.7729027</v>
+        <f aca="false">-Premissas!$B$23*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))+Premissas!$B$23*Premissas!$B$36+Premissas!$B$24*Premissas!$B$38</f>
+        <v>-7.6169017</v>
       </c>
       <c r="C24" s="12" t="n">
-        <f aca="false">-Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)+Premissas!$B$24*Premissas!$B$38</f>
-        <v>-1</v>
+        <f aca="false">-Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*Premissas!$B$28)+Premissas!$B$24*Premissas!$B$38</f>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>43</v>
@@ -2078,11 +2066,11 @@
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">SUM(B22:B24)</f>
-        <v>52.7871073</v>
+        <v>58.9431083</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">SUM(C22:C24)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>45</v>
@@ -2149,11 +2137,11 @@
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">A32*B9</f>
-        <v>922.58402946</v>
+        <v>1027.3772187</v>
       </c>
       <c r="D32" s="17" t="n">
         <f aca="false">$B$13-C32</f>
-        <v>152.41597054</v>
+        <v>47.6227813000003</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2166,11 +2154,11 @@
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">A33*B9</f>
-        <v>1845.16805892</v>
+        <v>2054.7544374</v>
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">$B$13-C33</f>
-        <v>-770.168058919999</v>
+        <v>-979.7544374</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2183,11 +2171,11 @@
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">A34*B9</f>
-        <v>2767.75208838</v>
+        <v>3082.1316561</v>
       </c>
       <c r="D34" s="17" t="n">
         <f aca="false">$B$13-C34</f>
-        <v>-1692.75208838</v>
+        <v>-2007.1316561</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2200,11 +2188,11 @@
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">A35*B9</f>
-        <v>4612.9201473</v>
+        <v>5136.8860935</v>
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">$B$13-C35</f>
-        <v>-3537.9201473</v>
+        <v>-4061.8860935</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2217,11 +2205,11 @@
       </c>
       <c r="C36" s="17" t="n">
         <f aca="false">A36*B9</f>
-        <v>9225.8402946</v>
+        <v>10273.772187</v>
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">$B$13-C36</f>
-        <v>-8150.8402946</v>
+        <v>-9198.772187</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2245,7 +2233,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -2706,7 +2694,7 @@
         <v>123</v>
       </c>
       <c r="B37" s="20" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>106</v>
@@ -2721,7 +2709,7 @@
       </c>
       <c r="B38" s="12" t="n">
         <f aca="false">Premissas!$B$37+Premissas!$B$28</f>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>106</v>
@@ -2988,7 +2976,7 @@
       <c r="A59" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -2999,67 +2987,81 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
+      <c r="B60" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" s="25" t="n">
-        <v>1325</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="A61" s="18" t="s">
         <v>165</v>
       </c>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B62" s="25" t="n">
-        <v>250</v>
+        <v>1325</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B63" s="25" t="n">
-        <v>3.99</v>
+        <v>250</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B64" s="25" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="23" t="n">
+      <c r="D64" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B65" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>172</v>
+      <c r="C65" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3088,26 +3090,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B4" s="12" t="n">
         <f aca="false">Premissas!$B$48</f>
@@ -3121,7 +3123,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">-Premissas!$B$26*Premissas!$B$47</f>
@@ -3132,12 +3134,12 @@
         <v>-30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">-(Premissas!$B$29*Premissas!$B$48+Premissas!$B$30)</f>
@@ -3151,7 +3153,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">-Premissas!$B$27</f>
@@ -3162,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3181,7 +3183,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">SUM(B4:B8)</f>
@@ -3195,7 +3197,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">-Premissas!$B$23*(B9+Premissas!$B$36)</f>
@@ -3206,56 +3208,58 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="12" t="n">
-        <f aca="false">-Premissas!$B$24*(B9+Premissas!$B$38)</f>
-        <v>-8.833999</v>
+        <f aca="false">-Premissas!$B$24*(B9+Premissas!$B$38+Premissas!$B$59*(Premissas!$B$27+Premissas!$B$28+Premissas!$B$29*Premissas!$B$48+Premissas!$B$30))</f>
+        <v>-14.99</v>
       </c>
       <c r="C11" s="12" t="n">
-        <f aca="false">-Premissas!$B$24*(C9+Premissas!$B$38-C6)</f>
-        <v>-10.691</v>
+        <f aca="false">-Premissas!$B$24*(C9+Premissas!$B$38-C6+Premissas!$B$59*Premissas!$B$28)</f>
+        <v>-13.691</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">SUM(B9:B11)</f>
-        <v>42.0398927</v>
+        <v>35.8838917</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">SUM(C9:C11)</f>
-        <v>67.2292365</v>
+        <v>64.2292365</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" s="12" t="n">
-        <f aca="false">-Premissas!$B$15/Premissas!$B$16</f>
-        <v>-15</v>
+        <f aca="false">-Premissas!$B$15*(1+Premissas!$B$14)/Premissas!$B$16</f>
+        <v>-17.0745</v>
       </c>
       <c r="C13" s="12" t="n">
-        <f aca="false">-Premissas!$B$15/Premissas!$B$16</f>
-        <v>-15</v>
-      </c>
-      <c r="D13" s="2"/>
+        <f aca="false">-Premissas!$B$15*(1+Premissas!$B$14)/Premissas!$B$16</f>
+        <v>-17.0745</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">-Premissas!$B$17/Premissas!$B$16</f>
@@ -3269,7 +3273,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">-Premissas!$B$18</f>
@@ -3283,7 +3287,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">-Premissas!$B$39*Premissas!$B$48*(1-Premissas!$B$23-Premissas!$B$24)</f>
@@ -3297,35 +3301,35 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">SUM(B12:B16)</f>
-        <v>24.2998927</v>
+        <v>16.0693917</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">SUM(C12:C16)</f>
-        <v>49.4892365</v>
+        <v>44.4147365</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">Premissas!$B$20*B17+Premissas!$B$21*C17</f>
-        <v>31.85669584</v>
+        <v>24.57299514</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B21" s="27" t="n">
         <f aca="false">1-Premissas!$B$23-Premissas!$B$24</f>
@@ -3334,7 +3338,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Premissas!$B$26*Premissas!$B$47</f>
@@ -3343,7 +3347,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">-(B6+B7+B8)</f>
@@ -3352,7 +3356,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">-(B7+B8)</f>
@@ -3361,7 +3365,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">-B6</f>
@@ -3370,16 +3374,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B26" s="12" t="n">
         <f aca="false">Unitário!$B$21*Unitário!$B$23+Premissas!$B$23*Premissas!$B$36+Premissas!$B$24*Premissas!$B$38</f>
-        <v>30.8871073</v>
+        <v>33.3871073</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">-C6</f>
@@ -3411,83 +3415,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3523,19 +3527,19 @@
         <v>1.5</v>
       </c>
       <c r="I5" s="12" t="n">
-        <f aca="false">-G5*Premissas!$B$56*Unitário!$B$22-IF($A5-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
-        <v>-105</v>
+        <f aca="false">-IF($A5-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
+        <v>-0</v>
       </c>
       <c r="J5" s="12" t="n">
-        <f aca="false">IF($A5-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A5-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L5" s="12" t="n">
-        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M5" s="12" t="n">
@@ -3543,11 +3547,11 @@
         <v>169.38035475</v>
       </c>
       <c r="N5" s="12" t="n">
-        <f aca="false">-H5*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
-        <v>-52.5</v>
+        <f aca="false">-IF($A5-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <v>-0</v>
       </c>
       <c r="O5" s="12" t="n">
-        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A5-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P5" s="12" t="n">
@@ -3555,16 +3559,16 @@
         <v>-0</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <f aca="false">IF(DAY(B5)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B5)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R5" s="12" t="n">
         <f aca="false">E5+F5+SUM(I5:Q5)</f>
-        <v>11.88035475</v>
+        <v>169.38035475</v>
       </c>
       <c r="S5" s="12" t="n">
         <f aca="false">R5</f>
-        <v>11.88035475</v>
+        <v>169.38035475</v>
       </c>
       <c r="T5" s="15" t="n">
         <f aca="false">IF(AND($A5&gt;$B$100,S5&gt;=0),1,0)</f>
@@ -3572,7 +3576,7 @@
       </c>
       <c r="U5" s="12" t="n">
         <f aca="false">S5-SUM($E$5:E5)-(1+Premissas!$B$14)*SUM($C$5:C5)</f>
-        <v>-73.49214525</v>
+        <v>84.00785475</v>
       </c>
       <c r="V5" s="12" t="n">
         <f aca="false">C5/Premissas!$B$15*Premissas!$B$17+(G5+H5)*Premissas!$B$18</f>
@@ -3616,19 +3620,19 @@
         <v>1.5</v>
       </c>
       <c r="I6" s="12" t="n">
-        <f aca="false">-G6*Premissas!$B$56*Unitário!$B$22-IF($A6-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A6-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-232.960035</v>
       </c>
       <c r="J6" s="12" t="n">
-        <f aca="false">IF($A6-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A6-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
-        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L6" s="12" t="n">
-        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M6" s="12" t="n">
@@ -3636,11 +3640,11 @@
         <v>169.38035475</v>
       </c>
       <c r="N6" s="12" t="n">
-        <f aca="false">-H6*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A6-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-52.5</v>
       </c>
       <c r="O6" s="12" t="n">
-        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A6-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P6" s="12" t="n">
@@ -3648,7 +3652,7 @@
         <v>-0</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <f aca="false">IF(DAY(B6)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B6)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
@@ -3657,7 +3661,7 @@
       </c>
       <c r="S6" s="12" t="n">
         <f aca="false">S5+R6</f>
-        <v>-104.1993255</v>
+        <v>53.3006745000001</v>
       </c>
       <c r="T6" s="15" t="n">
         <f aca="false">IF(AND($A6&gt;$B$100,S6&gt;=0),1,0)</f>
@@ -3665,7 +3669,7 @@
       </c>
       <c r="U6" s="12" t="n">
         <f aca="false">S6-SUM($E$5:E6)-(1+Premissas!$B$14)*SUM($C$5:C6)</f>
-        <v>-274.9443255</v>
+        <v>-117.4443255</v>
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">C6/Premissas!$B$15*Premissas!$B$17+(G6+H6)*Premissas!$B$18</f>
@@ -3709,19 +3713,19 @@
         <v>1.5</v>
       </c>
       <c r="I7" s="12" t="n">
-        <f aca="false">-G7*Premissas!$B$56*Unitário!$B$22-IF($A7-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A7-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-232.960035</v>
       </c>
       <c r="J7" s="12" t="n">
-        <f aca="false">IF($A7-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A7-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>33.65915595</v>
       </c>
       <c r="K7" s="12" t="n">
-        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L7" s="12" t="n">
-        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M7" s="12" t="n">
@@ -3729,11 +3733,11 @@
         <v>169.38035475</v>
       </c>
       <c r="N7" s="12" t="n">
-        <f aca="false">-H7*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A7-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-52.5</v>
       </c>
       <c r="O7" s="12" t="n">
-        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A7-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P7" s="12" t="n">
@@ -3741,7 +3745,7 @@
         <v>-0</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <f aca="false">IF(DAY(B7)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B7)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
@@ -3750,7 +3754,7 @@
       </c>
       <c r="S7" s="12" t="n">
         <f aca="false">S6+R7</f>
-        <v>-186.6198498</v>
+        <v>-29.1198497999999</v>
       </c>
       <c r="T7" s="15" t="n">
         <f aca="false">IF(AND($A7&gt;$B$100,S7&gt;=0),1,0)</f>
@@ -3758,7 +3762,7 @@
       </c>
       <c r="U7" s="12" t="n">
         <f aca="false">S7-SUM($E$5:E7)-(1+Premissas!$B$14)*SUM($C$5:C7)</f>
-        <v>-442.7373498</v>
+        <v>-285.2373498</v>
       </c>
       <c r="V7" s="12" t="n">
         <f aca="false">C7/Premissas!$B$15*Premissas!$B$17+(G7+H7)*Premissas!$B$18</f>
@@ -3802,19 +3806,19 @@
         <v>1.5</v>
       </c>
       <c r="I8" s="12" t="n">
-        <f aca="false">-G8*Premissas!$B$56*Unitário!$B$22-IF($A8-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A8-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-232.960035</v>
       </c>
       <c r="J8" s="12" t="n">
-        <f aca="false">IF($A8-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A8-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>33.65915595</v>
       </c>
       <c r="K8" s="12" t="n">
-        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M8" s="12" t="n">
@@ -3822,11 +3826,11 @@
         <v>169.38035475</v>
       </c>
       <c r="N8" s="12" t="n">
-        <f aca="false">-H8*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A8-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-52.5</v>
       </c>
       <c r="O8" s="12" t="n">
-        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A8-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P8" s="12" t="n">
@@ -3834,7 +3838,7 @@
         <v>-0</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <f aca="false">IF(DAY(B8)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B8)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
@@ -3843,7 +3847,7 @@
       </c>
       <c r="S8" s="12" t="n">
         <f aca="false">S7+R8</f>
-        <v>-269.0403741</v>
+        <v>-111.5403741</v>
       </c>
       <c r="T8" s="15" t="n">
         <f aca="false">IF(AND($A8&gt;$B$100,S8&gt;=0),1,0)</f>
@@ -3851,7 +3855,7 @@
       </c>
       <c r="U8" s="12" t="n">
         <f aca="false">S8-SUM($E$5:E8)-(1+Premissas!$B$14)*SUM($C$5:C8)</f>
-        <v>-610.5303741</v>
+        <v>-453.0303741</v>
       </c>
       <c r="V8" s="12" t="n">
         <f aca="false">C8/Premissas!$B$15*Premissas!$B$17+(G8+H8)*Premissas!$B$18</f>
@@ -3895,19 +3899,19 @@
         <v>1.5</v>
       </c>
       <c r="I9" s="12" t="n">
-        <f aca="false">-G9*Premissas!$B$56*Unitário!$B$22-IF($A9-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A9-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-232.960035</v>
       </c>
       <c r="J9" s="12" t="n">
-        <f aca="false">IF($A9-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A9-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>33.65915595</v>
       </c>
       <c r="K9" s="12" t="n">
-        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L9" s="12" t="n">
-        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M9" s="12" t="n">
@@ -3915,11 +3919,11 @@
         <v>169.38035475</v>
       </c>
       <c r="N9" s="12" t="n">
-        <f aca="false">-H9*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A9-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-52.5</v>
       </c>
       <c r="O9" s="12" t="n">
-        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A9-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -3927,7 +3931,7 @@
         <v>-0</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <f aca="false">IF(DAY(B9)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B9)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R9" s="12" t="n">
@@ -3936,7 +3940,7 @@
       </c>
       <c r="S9" s="12" t="n">
         <f aca="false">S8+R9</f>
-        <v>-351.4608984</v>
+        <v>-193.9608984</v>
       </c>
       <c r="T9" s="15" t="n">
         <f aca="false">IF(AND($A9&gt;$B$100,S9&gt;=0),1,0)</f>
@@ -3944,7 +3948,7 @@
       </c>
       <c r="U9" s="12" t="n">
         <f aca="false">S9-SUM($E$5:E9)-(1+Premissas!$B$14)*SUM($C$5:C9)</f>
-        <v>-778.3233984</v>
+        <v>-620.8233984</v>
       </c>
       <c r="V9" s="12" t="n">
         <f aca="false">C9/Premissas!$B$15*Premissas!$B$17+(G9+H9)*Premissas!$B$18</f>
@@ -3988,19 +3992,19 @@
         <v>0</v>
       </c>
       <c r="I10" s="12" t="n">
-        <f aca="false">-G10*Premissas!$B$56*Unitário!$B$22-IF($A10-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
-        <v>-127.960035</v>
+        <f aca="false">-IF($A10-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
+        <v>-232.960035</v>
       </c>
       <c r="J10" s="12" t="n">
-        <f aca="false">IF($A10-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A10-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>33.65915595</v>
       </c>
       <c r="K10" s="12" t="n">
-        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L10" s="12" t="n">
-        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M10" s="12" t="n">
@@ -4008,11 +4012,11 @@
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <f aca="false">-H10*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
-        <v>-0</v>
+        <f aca="false">-IF($A10-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <v>-52.5</v>
       </c>
       <c r="O10" s="12" t="n">
-        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A10-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P10" s="12" t="n">
@@ -4020,12 +4024,12 @@
         <v>-0</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <f aca="false">IF(DAY(B10)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B10)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
         <f aca="false">E10+F10+SUM(I10:Q10)</f>
-        <v>-94.30087905</v>
+        <v>-251.80087905</v>
       </c>
       <c r="S10" s="12" t="n">
         <f aca="false">S9+R10</f>
@@ -4081,19 +4085,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="12" t="n">
-        <f aca="false">-G11*Premissas!$B$56*Unitário!$B$22-IF($A11-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A11-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <f aca="false">IF($A11-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A11-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>33.65915595</v>
       </c>
       <c r="K11" s="12" t="n">
-        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L11" s="12" t="n">
-        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
@@ -4101,11 +4105,11 @@
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <f aca="false">-H11*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A11-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A11-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -4113,7 +4117,7 @@
         <v>-0</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <f aca="false">IF(DAY(B11)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B11)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R11" s="12" t="n">
@@ -4174,19 +4178,19 @@
         <v>1.2</v>
       </c>
       <c r="I12" s="12" t="n">
-        <f aca="false">-G12*Premissas!$B$56*Unitário!$B$22-IF($A12-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
-        <v>-84</v>
+        <f aca="false">-IF($A12-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
+        <v>-0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <f aca="false">IF($A12-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A12-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L12" s="12" t="n">
-        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M12" s="12" t="n">
@@ -4194,11 +4198,11 @@
         <v>135.5042838</v>
       </c>
       <c r="N12" s="12" t="n">
-        <f aca="false">-H12*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
-        <v>-42</v>
+        <f aca="false">-IF($A12-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <v>-0</v>
       </c>
       <c r="O12" s="12" t="n">
-        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A12-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P12" s="12" t="n">
@@ -4206,16 +4210,16 @@
         <v>-0</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <f aca="false">IF(DAY(B12)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B12)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R12" s="12" t="n">
         <f aca="false">E12+F12+SUM(I12:Q12)</f>
-        <v>9.50428380000002</v>
+        <v>135.5042838</v>
       </c>
       <c r="S12" s="12" t="n">
         <f aca="false">S11+R12</f>
-        <v>-402.5983377</v>
+        <v>-276.5983377</v>
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(AND($A12&gt;$B$100,S12&gt;=0),1,0)</f>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="U12" s="12" t="n">
         <f aca="false">S12-SUM($E$5:E12)-(1+Premissas!$B$14)*SUM($C$5:C12)</f>
-        <v>-897.7588377</v>
+        <v>-771.7588377</v>
       </c>
       <c r="V12" s="12" t="n">
         <f aca="false">C12/Premissas!$B$15*Premissas!$B$17+(G12+H12)*Premissas!$B$18</f>
@@ -4267,19 +4271,19 @@
         <v>1.2</v>
       </c>
       <c r="I13" s="12" t="n">
-        <f aca="false">-G13*Premissas!$B$56*Unitário!$B$22-IF($A13-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A13-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-186.368028</v>
       </c>
       <c r="J13" s="12" t="n">
-        <f aca="false">IF($A13-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A13-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M13" s="12" t="n">
@@ -4287,11 +4291,11 @@
         <v>135.5042838</v>
       </c>
       <c r="N13" s="12" t="n">
-        <f aca="false">-H13*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A13-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-42</v>
       </c>
       <c r="O13" s="12" t="n">
-        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A13-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P13" s="12" t="n">
@@ -4299,7 +4303,7 @@
         <v>-0</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <f aca="false">IF(DAY(B13)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B13)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
@@ -4308,7 +4312,7 @@
       </c>
       <c r="S13" s="12" t="n">
         <f aca="false">S12+R13</f>
-        <v>-495.4620819</v>
+        <v>-369.4620819</v>
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(AND($A13&gt;$B$100,S13&gt;=0),1,0)</f>
@@ -4316,7 +4320,7 @@
       </c>
       <c r="U13" s="12" t="n">
         <f aca="false">S13-SUM($E$5:E13)-(1+Premissas!$B$14)*SUM($C$5:C13)</f>
-        <v>-1058.9205819</v>
+        <v>-932.9205819</v>
       </c>
       <c r="V13" s="12" t="n">
         <f aca="false">C13/Premissas!$B$15*Premissas!$B$17+(G13+H13)*Premissas!$B$18</f>
@@ -4360,19 +4364,19 @@
         <v>1.2</v>
       </c>
       <c r="I14" s="12" t="n">
-        <f aca="false">-G14*Premissas!$B$56*Unitário!$B$22-IF($A14-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A14-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-186.368028</v>
       </c>
       <c r="J14" s="12" t="n">
-        <f aca="false">IF($A14-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A14-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>26.92732476</v>
       </c>
       <c r="K14" s="12" t="n">
-        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>14.5460035</v>
+        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-7</v>
       </c>
       <c r="L14" s="12" t="n">
-        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M14" s="12" t="n">
@@ -4380,28 +4384,28 @@
         <v>135.5042838</v>
       </c>
       <c r="N14" s="12" t="n">
-        <f aca="false">-H14*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A14-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-42</v>
       </c>
       <c r="O14" s="12" t="n">
-        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-16.0365</v>
+        <f aca="false">IF($A14-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-20.5365</v>
       </c>
       <c r="P14" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A14-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A14-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <f aca="false">IF(DAY(B14)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B14)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>-57.49</v>
       </c>
       <c r="R14" s="12" t="n">
         <f aca="false">E14+F14+SUM(I14:Q14)</f>
-        <v>-215.33691594</v>
+        <v>-241.38291944</v>
       </c>
       <c r="S14" s="12" t="n">
         <f aca="false">S13+R14</f>
-        <v>-710.79899784</v>
+        <v>-610.84500134</v>
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(AND($A14&gt;$B$100,S14&gt;=0),1,0)</f>
@@ -4409,7 +4413,7 @@
       </c>
       <c r="U14" s="12" t="n">
         <f aca="false">S14-SUM($E$5:E14)-(1+Premissas!$B$14)*SUM($C$5:C14)</f>
-        <v>-1342.55549784</v>
+        <v>-1242.60150134</v>
       </c>
       <c r="V14" s="12" t="n">
         <f aca="false">C14/Premissas!$B$15*Premissas!$B$17+(G14+H14)*Premissas!$B$18</f>
@@ -4453,19 +4457,19 @@
         <v>1.2</v>
       </c>
       <c r="I15" s="12" t="n">
-        <f aca="false">-G15*Premissas!$B$56*Unitário!$B$22-IF($A15-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A15-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-186.368028</v>
       </c>
       <c r="J15" s="12" t="n">
-        <f aca="false">IF($A15-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A15-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>26.92732476</v>
       </c>
       <c r="K15" s="12" t="n">
-        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>14.5460035</v>
+        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-7</v>
       </c>
       <c r="L15" s="12" t="n">
-        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M15" s="12" t="n">
@@ -4473,28 +4477,28 @@
         <v>135.5042838</v>
       </c>
       <c r="N15" s="12" t="n">
-        <f aca="false">-H15*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A15-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-42</v>
       </c>
       <c r="O15" s="12" t="n">
-        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-16.0365</v>
+        <f aca="false">IF($A15-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-20.5365</v>
       </c>
       <c r="P15" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A15-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A15-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <f aca="false">IF(DAY(B15)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B15)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
         <f aca="false">E15+F15+SUM(I15:Q15)</f>
-        <v>-67.42691594</v>
+        <v>-93.47291944</v>
       </c>
       <c r="S15" s="12" t="n">
         <f aca="false">S14+R15</f>
-        <v>-778.22591378</v>
+        <v>-704.31792078</v>
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(AND($A15&gt;$B$100,S15&gt;=0),1,0)</f>
@@ -4502,7 +4506,7 @@
       </c>
       <c r="U15" s="12" t="n">
         <f aca="false">S15-SUM($E$5:E15)-(1+Premissas!$B$14)*SUM($C$5:C15)</f>
-        <v>-1478.28041378</v>
+        <v>-1404.37242078</v>
       </c>
       <c r="V15" s="12" t="n">
         <f aca="false">C15/Premissas!$B$15*Premissas!$B$17+(G15+H15)*Premissas!$B$18</f>
@@ -4546,19 +4550,19 @@
         <v>1.2</v>
       </c>
       <c r="I16" s="12" t="n">
-        <f aca="false">-G16*Premissas!$B$56*Unitário!$B$22-IF($A16-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A16-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-186.368028</v>
       </c>
       <c r="J16" s="12" t="n">
-        <f aca="false">IF($A16-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A16-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>26.92732476</v>
       </c>
       <c r="K16" s="12" t="n">
-        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>14.5460035</v>
+        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-7</v>
       </c>
       <c r="L16" s="12" t="n">
-        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M16" s="12" t="n">
@@ -4566,28 +4570,28 @@
         <v>135.5042838</v>
       </c>
       <c r="N16" s="12" t="n">
-        <f aca="false">-H16*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A16-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-42</v>
       </c>
       <c r="O16" s="12" t="n">
-        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-16.0365</v>
+        <f aca="false">IF($A16-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-20.5365</v>
       </c>
       <c r="P16" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A16-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A16-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <f aca="false">IF(DAY(B16)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B16)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R16" s="12" t="n">
         <f aca="false">E16+F16+SUM(I16:Q16)</f>
-        <v>-67.42691594</v>
+        <v>-93.47291944</v>
       </c>
       <c r="S16" s="12" t="n">
         <f aca="false">S15+R16</f>
-        <v>-845.65282972</v>
+        <v>-797.79084022</v>
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(AND($A16&gt;$B$100,S16&gt;=0),1,0)</f>
@@ -4595,7 +4599,7 @@
       </c>
       <c r="U16" s="12" t="n">
         <f aca="false">S16-SUM($E$5:E16)-(1+Premissas!$B$14)*SUM($C$5:C16)</f>
-        <v>-1614.00532972</v>
+        <v>-1566.14334022</v>
       </c>
       <c r="V16" s="12" t="n">
         <f aca="false">C16/Premissas!$B$15*Premissas!$B$17+(G16+H16)*Premissas!$B$18</f>
@@ -4639,19 +4643,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <f aca="false">-G17*Premissas!$B$56*Unitário!$B$22-IF($A17-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
-        <v>-102.368028</v>
+        <f aca="false">-IF($A17-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
+        <v>-186.368028</v>
       </c>
       <c r="J17" s="12" t="n">
-        <f aca="false">IF($A17-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A17-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>26.92732476</v>
       </c>
       <c r="K17" s="12" t="n">
-        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>14.5460035</v>
+        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-7</v>
       </c>
       <c r="L17" s="12" t="n">
-        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M17" s="12" t="n">
@@ -4659,28 +4663,28 @@
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <f aca="false">-H17*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
-        <v>-0</v>
+        <f aca="false">-IF($A17-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <v>-42</v>
       </c>
       <c r="O17" s="12" t="n">
-        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-16.0365</v>
+        <f aca="false">IF($A17-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-20.5365</v>
       </c>
       <c r="P17" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A17-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A17-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <f aca="false">IF(DAY(B17)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B17)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R17" s="12" t="n">
         <f aca="false">E17+F17+SUM(I17:Q17)</f>
-        <v>-76.93119974</v>
+        <v>-228.97720324</v>
       </c>
       <c r="S17" s="12" t="n">
         <f aca="false">S16+R17</f>
-        <v>-922.58402946</v>
+        <v>-1026.76804346</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(AND($A17&gt;$B$100,S17&gt;=0),1,0)</f>
@@ -4688,7 +4692,7 @@
       </c>
       <c r="U17" s="12" t="n">
         <f aca="false">S17-SUM($E$5:E17)-(1+Premissas!$B$14)*SUM($C$5:C17)</f>
-        <v>-1690.93652946</v>
+        <v>-1795.12054346</v>
       </c>
       <c r="V17" s="12" t="n">
         <f aca="false">C17/Premissas!$B$15*Premissas!$B$17+(G17+H17)*Premissas!$B$18</f>
@@ -4732,19 +4736,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <f aca="false">-G18*Premissas!$B$56*Unitário!$B$22-IF($A18-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A18-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <f aca="false">IF($A18-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A18-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>26.92732476</v>
       </c>
       <c r="K18" s="12" t="n">
-        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>14.5460035</v>
+        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-7</v>
       </c>
       <c r="L18" s="12" t="n">
-        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M18" s="12" t="n">
@@ -4752,28 +4756,28 @@
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <f aca="false">-H18*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A18-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O18" s="12" t="n">
-        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-16.0365</v>
+        <f aca="false">IF($A18-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-20.5365</v>
       </c>
       <c r="P18" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A18-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A18-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <f aca="false">IF(DAY(B18)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B18)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R18" s="12" t="n">
         <f aca="false">E18+F18+SUM(I18:Q18)</f>
-        <v>25.43682826</v>
+        <v>-0.609175240000003</v>
       </c>
       <c r="S18" s="12" t="n">
         <f aca="false">S17+R18</f>
-        <v>-897.1472012</v>
+        <v>-1027.3772187</v>
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(AND($A18&gt;$B$100,S18&gt;=0),1,0)</f>
@@ -4781,7 +4785,7 @@
       </c>
       <c r="U18" s="12" t="n">
         <f aca="false">S18-SUM($E$5:E18)-(1+Premissas!$B$14)*SUM($C$5:C18)</f>
-        <v>-1665.4997012</v>
+        <v>-1795.7297187</v>
       </c>
       <c r="V18" s="12" t="n">
         <f aca="false">C18/Premissas!$B$15*Premissas!$B$17+(G18+H18)*Premissas!$B$18</f>
@@ -4825,19 +4829,19 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <f aca="false">-G19*Premissas!$B$56*Unitário!$B$22-IF($A19-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A19-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <f aca="false">IF($A19-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A19-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L19" s="12" t="n">
-        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M19" s="12" t="n">
@@ -4845,11 +4849,11 @@
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <f aca="false">-H19*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A19-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A19-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P19" s="12" t="n">
@@ -4857,7 +4861,7 @@
         <v>-0</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <f aca="false">IF(DAY(B19)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B19)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R19" s="12" t="n">
@@ -4866,7 +4870,7 @@
       </c>
       <c r="S19" s="12" t="n">
         <f aca="false">S18+R19</f>
-        <v>-897.1472012</v>
+        <v>-1027.3772187</v>
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(AND($A19&gt;$B$100,S19&gt;=0),1,0)</f>
@@ -4874,7 +4878,7 @@
       </c>
       <c r="U19" s="12" t="n">
         <f aca="false">S19-SUM($E$5:E19)-(1+Premissas!$B$14)*SUM($C$5:C19)</f>
-        <v>-1665.4997012</v>
+        <v>-1795.7297187</v>
       </c>
       <c r="V19" s="12" t="n">
         <f aca="false">C19/Premissas!$B$15*Premissas!$B$17+(G19+H19)*Premissas!$B$18</f>
@@ -4918,19 +4922,19 @@
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <f aca="false">-G20*Premissas!$B$56*Unitário!$B$22-IF($A20-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A20-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <f aca="false">IF($A20-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A20-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L20" s="12" t="n">
-        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M20" s="12" t="n">
@@ -4938,11 +4942,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <f aca="false">-H20*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A20-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O20" s="12" t="n">
-        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A20-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P20" s="12" t="n">
@@ -4950,7 +4954,7 @@
         <v>-0</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <f aca="false">IF(DAY(B20)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B20)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R20" s="12" t="n">
@@ -4959,7 +4963,7 @@
       </c>
       <c r="S20" s="12" t="n">
         <f aca="false">S19+R20</f>
-        <v>-897.1472012</v>
+        <v>-1027.3772187</v>
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(AND($A20&gt;$B$100,S20&gt;=0),1,0)</f>
@@ -4967,7 +4971,7 @@
       </c>
       <c r="U20" s="12" t="n">
         <f aca="false">S20-SUM($E$5:E20)-(1+Premissas!$B$14)*SUM($C$5:C20)</f>
-        <v>-1665.4997012</v>
+        <v>-1795.7297187</v>
       </c>
       <c r="V20" s="12" t="n">
         <f aca="false">C20/Premissas!$B$15*Premissas!$B$17+(G20+H20)*Premissas!$B$18</f>
@@ -5011,19 +5015,19 @@
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <f aca="false">-G21*Premissas!$B$56*Unitário!$B$22-IF($A21-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A21-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <f aca="false">IF($A21-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A21-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>11.6368028</v>
+        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-5.6</v>
       </c>
       <c r="L21" s="12" t="n">
-        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>331.8945</v>
       </c>
       <c r="M21" s="12" t="n">
@@ -5031,28 +5035,28 @@
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <f aca="false">-H21*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A21-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O21" s="12" t="n">
-        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-12.8292</v>
+        <f aca="false">IF($A21-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-16.4292</v>
       </c>
       <c r="P21" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A21-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A21-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <f aca="false">IF(DAY(B21)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B21)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
         <f aca="false">E21+F21+SUM(I21:Q21)</f>
-        <v>330.7021028</v>
+        <v>309.8653</v>
       </c>
       <c r="S21" s="12" t="n">
         <f aca="false">S20+R21</f>
-        <v>-566.4450984</v>
+        <v>-717.5119187</v>
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(AND($A21&gt;$B$100,S21&gt;=0),1,0)</f>
@@ -5060,7 +5064,7 @@
       </c>
       <c r="U21" s="12" t="n">
         <f aca="false">S21-SUM($E$5:E21)-(1+Premissas!$B$14)*SUM($C$5:C21)</f>
-        <v>-1334.7975984</v>
+        <v>-1485.8644187</v>
       </c>
       <c r="V21" s="12" t="n">
         <f aca="false">C21/Premissas!$B$15*Premissas!$B$17+(G21+H21)*Premissas!$B$18</f>
@@ -5104,19 +5108,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <f aca="false">-G22*Premissas!$B$56*Unitário!$B$22-IF($A22-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A22-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <f aca="false">IF($A22-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A22-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
-        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>11.6368028</v>
+        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-5.6</v>
       </c>
       <c r="L22" s="12" t="n">
-        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>331.8945</v>
       </c>
       <c r="M22" s="12" t="n">
@@ -5124,28 +5128,28 @@
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <f aca="false">-H22*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A22-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O22" s="12" t="n">
-        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-12.8292</v>
+        <f aca="false">IF($A22-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-16.4292</v>
       </c>
       <c r="P22" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A22-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A22-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <f aca="false">IF(DAY(B22)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B22)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
         <f aca="false">E22+F22+SUM(I22:Q22)</f>
-        <v>330.7021028</v>
+        <v>309.8653</v>
       </c>
       <c r="S22" s="12" t="n">
         <f aca="false">S21+R22</f>
-        <v>-235.7429956</v>
+        <v>-407.6466187</v>
       </c>
       <c r="T22" s="15" t="n">
         <f aca="false">IF(AND($A22&gt;$B$100,S22&gt;=0),1,0)</f>
@@ -5153,7 +5157,7 @@
       </c>
       <c r="U22" s="12" t="n">
         <f aca="false">S22-SUM($E$5:E22)-(1+Premissas!$B$14)*SUM($C$5:C22)</f>
-        <v>-1004.0954956</v>
+        <v>-1175.9991187</v>
       </c>
       <c r="V22" s="12" t="n">
         <f aca="false">C22/Premissas!$B$15*Premissas!$B$17+(G22+H22)*Premissas!$B$18</f>
@@ -5197,19 +5201,19 @@
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <f aca="false">-G23*Premissas!$B$56*Unitário!$B$22-IF($A23-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A23-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <f aca="false">IF($A23-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A23-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>11.6368028</v>
+        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-5.6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>331.8945</v>
       </c>
       <c r="M23" s="12" t="n">
@@ -5217,36 +5221,36 @@
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <f aca="false">-H23*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A23-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O23" s="12" t="n">
-        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-12.8292</v>
+        <f aca="false">IF($A23-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-16.4292</v>
       </c>
       <c r="P23" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A23-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A23-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <f aca="false">IF(DAY(B23)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B23)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
         <f aca="false">E23+F23+SUM(I23:Q23)</f>
-        <v>330.7021028</v>
+        <v>309.8653</v>
       </c>
       <c r="S23" s="12" t="n">
         <f aca="false">S22+R23</f>
-        <v>94.9591072000004</v>
+        <v>-97.7813186999998</v>
       </c>
       <c r="T23" s="15" t="n">
         <f aca="false">IF(AND($A23&gt;$B$100,S23&gt;=0),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="12" t="n">
         <f aca="false">S23-SUM($E$5:E23)-(1+Premissas!$B$14)*SUM($C$5:C23)</f>
-        <v>-673.3933928</v>
+        <v>-866.1338187</v>
       </c>
       <c r="V23" s="12" t="n">
         <f aca="false">C23/Premissas!$B$15*Premissas!$B$17+(G23+H23)*Premissas!$B$18</f>
@@ -5290,19 +5294,19 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <f aca="false">-G24*Premissas!$B$56*Unitário!$B$22-IF($A24-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A24-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <f aca="false">IF($A24-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A24-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>11.6368028</v>
+        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-5.6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>331.8945</v>
       </c>
       <c r="M24" s="12" t="n">
@@ -5310,28 +5314,28 @@
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <f aca="false">-H24*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A24-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O24" s="12" t="n">
-        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-12.8292</v>
+        <f aca="false">IF($A24-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-16.4292</v>
       </c>
       <c r="P24" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A24-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A24-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <f aca="false">IF(DAY(B24)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B24)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
         <f aca="false">E24+F24+SUM(I24:Q24)</f>
-        <v>330.7021028</v>
+        <v>309.8653</v>
       </c>
       <c r="S24" s="12" t="n">
         <f aca="false">S23+R24</f>
-        <v>425.66121</v>
+        <v>212.0839813</v>
       </c>
       <c r="T24" s="15" t="n">
         <f aca="false">IF(AND($A24&gt;$B$100,S24&gt;=0),1,0)</f>
@@ -5339,7 +5343,7 @@
       </c>
       <c r="U24" s="12" t="n">
         <f aca="false">S24-SUM($E$5:E24)-(1+Premissas!$B$14)*SUM($C$5:C24)</f>
-        <v>-342.69129</v>
+        <v>-556.2685187</v>
       </c>
       <c r="V24" s="12" t="n">
         <f aca="false">C24/Premissas!$B$15*Premissas!$B$17+(G24+H24)*Premissas!$B$18</f>
@@ -5383,19 +5387,19 @@
         <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <f aca="false">-G25*Premissas!$B$56*Unitário!$B$22-IF($A25-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A25-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <f aca="false">IF($A25-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A25-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>11.6368028</v>
+        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-5.6</v>
       </c>
       <c r="L25" s="12" t="n">
-        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>331.8945</v>
       </c>
       <c r="M25" s="12" t="n">
@@ -5403,28 +5407,28 @@
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <f aca="false">-H25*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A25-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O25" s="12" t="n">
-        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
-        <v>-12.8292</v>
+        <f aca="false">IF($A25-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <v>-16.4292</v>
       </c>
       <c r="P25" s="12" t="n">
         <f aca="false">-Premissas!$B$39*(IF($A25-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*Premissas!$B$48+IF($A25-(Premissas!$B$53)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$53)),0)*(1-Premissas!$B$24)*Premissas!$B$49)</f>
         <v>-0</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <f aca="false">IF(DAY(B25)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B25)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
         <f aca="false">E25+F25+SUM(I25:Q25)</f>
-        <v>330.7021028</v>
+        <v>309.8653</v>
       </c>
       <c r="S25" s="12" t="n">
         <f aca="false">S24+R25</f>
-        <v>756.3633128</v>
+        <v>521.9492813</v>
       </c>
       <c r="T25" s="15" t="n">
         <f aca="false">IF(AND($A25&gt;$B$100,S25&gt;=0),1,0)</f>
@@ -5432,7 +5436,7 @@
       </c>
       <c r="U25" s="12" t="n">
         <f aca="false">S25-SUM($E$5:E25)-(1+Premissas!$B$14)*SUM($C$5:C25)</f>
-        <v>-11.9891871999997</v>
+        <v>-246.4032187</v>
       </c>
       <c r="V25" s="12" t="n">
         <f aca="false">C25/Premissas!$B$15*Premissas!$B$17+(G25+H25)*Premissas!$B$18</f>
@@ -5476,19 +5480,19 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <f aca="false">-G26*Premissas!$B$56*Unitário!$B$22-IF($A26-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A26-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <f aca="false">IF($A26-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A26-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L26" s="12" t="n">
-        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M26" s="12" t="n">
@@ -5496,11 +5500,11 @@
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <f aca="false">-H26*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A26-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O26" s="12" t="n">
-        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A26-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P26" s="12" t="n">
@@ -5508,7 +5512,7 @@
         <v>-0</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <f aca="false">IF(DAY(B26)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B26)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
@@ -5517,7 +5521,7 @@
       </c>
       <c r="S26" s="12" t="n">
         <f aca="false">S25+R26</f>
-        <v>756.3633128</v>
+        <v>521.9492813</v>
       </c>
       <c r="T26" s="15" t="n">
         <f aca="false">IF(AND($A26&gt;$B$100,S26&gt;=0),1,0)</f>
@@ -5525,7 +5529,7 @@
       </c>
       <c r="U26" s="12" t="n">
         <f aca="false">S26-SUM($E$5:E26)-(1+Premissas!$B$14)*SUM($C$5:C26)</f>
-        <v>-11.9891871999997</v>
+        <v>-246.4032187</v>
       </c>
       <c r="V26" s="12" t="n">
         <f aca="false">C26/Premissas!$B$15*Premissas!$B$17+(G26+H26)*Premissas!$B$18</f>
@@ -5569,19 +5573,19 @@
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <f aca="false">-G27*Premissas!$B$56*Unitário!$B$22-IF($A27-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A27-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <f aca="false">IF($A27-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A27-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
@@ -5589,11 +5593,11 @@
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <f aca="false">-H27*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A27-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O27" s="12" t="n">
-        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A27-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -5601,7 +5605,7 @@
         <v>-0</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <f aca="false">IF(DAY(B27)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B27)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
@@ -5610,7 +5614,7 @@
       </c>
       <c r="S27" s="12" t="n">
         <f aca="false">S26+R27</f>
-        <v>756.3633128</v>
+        <v>521.9492813</v>
       </c>
       <c r="T27" s="15" t="n">
         <f aca="false">IF(AND($A27&gt;$B$100,S27&gt;=0),1,0)</f>
@@ -5618,7 +5622,7 @@
       </c>
       <c r="U27" s="12" t="n">
         <f aca="false">S27-SUM($E$5:E27)-(1+Premissas!$B$14)*SUM($C$5:C27)</f>
-        <v>-11.9891871999997</v>
+        <v>-246.4032187</v>
       </c>
       <c r="V27" s="12" t="n">
         <f aca="false">C27/Premissas!$B$15*Premissas!$B$17+(G27+H27)*Premissas!$B$18</f>
@@ -5662,19 +5666,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <f aca="false">-G28*Premissas!$B$56*Unitário!$B$22-IF($A28-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A28-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <f aca="false">IF($A28-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A28-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L28" s="12" t="n">
-        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>265.5156</v>
       </c>
       <c r="M28" s="12" t="n">
@@ -5682,11 +5686,11 @@
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <f aca="false">-H28*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A28-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O28" s="12" t="n">
-        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A28-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P28" s="12" t="n">
@@ -5694,7 +5698,7 @@
         <v>-0</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <f aca="false">IF(DAY(B28)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B28)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
@@ -5703,7 +5707,7 @@
       </c>
       <c r="S28" s="12" t="n">
         <f aca="false">S27+R28</f>
-        <v>1021.8789128</v>
+        <v>787.4648813</v>
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(AND($A28&gt;$B$100,S28&gt;=0),1,0)</f>
@@ -5711,7 +5715,7 @@
       </c>
       <c r="U28" s="12" t="n">
         <f aca="false">S28-SUM($E$5:E28)-(1+Premissas!$B$14)*SUM($C$5:C28)</f>
-        <v>253.5264128</v>
+        <v>19.1123813</v>
       </c>
       <c r="V28" s="12" t="n">
         <f aca="false">C28/Premissas!$B$15*Premissas!$B$17+(G28+H28)*Premissas!$B$18</f>
@@ -5755,19 +5759,19 @@
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <f aca="false">-G29*Premissas!$B$56*Unitário!$B$22-IF($A29-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A29-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <f aca="false">IF($A29-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A29-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
-        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L29" s="12" t="n">
-        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>265.5156</v>
       </c>
       <c r="M29" s="12" t="n">
@@ -5775,11 +5779,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <f aca="false">-H29*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A29-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O29" s="12" t="n">
-        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A29-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -5787,7 +5791,7 @@
         <v>-0</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <f aca="false">IF(DAY(B29)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B29)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
@@ -5796,7 +5800,7 @@
       </c>
       <c r="S29" s="12" t="n">
         <f aca="false">S28+R29</f>
-        <v>1287.3945128</v>
+        <v>1052.9804813</v>
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(AND($A29&gt;$B$100,S29&gt;=0),1,0)</f>
@@ -5804,7 +5808,7 @@
       </c>
       <c r="U29" s="12" t="n">
         <f aca="false">S29-SUM($E$5:E29)-(1+Premissas!$B$14)*SUM($C$5:C29)</f>
-        <v>519.0420128</v>
+        <v>284.6279813</v>
       </c>
       <c r="V29" s="12" t="n">
         <f aca="false">C29/Premissas!$B$15*Premissas!$B$17+(G29+H29)*Premissas!$B$18</f>
@@ -5848,19 +5852,19 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <f aca="false">-G30*Premissas!$B$56*Unitário!$B$22-IF($A30-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A30-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <f aca="false">IF($A30-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A30-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
-        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>265.5156</v>
       </c>
       <c r="M30" s="12" t="n">
@@ -5868,11 +5872,11 @@
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <f aca="false">-H30*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A30-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A30-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O30" s="12" t="n">
-        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A30-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A30-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A30-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P30" s="12" t="n">
@@ -5880,7 +5884,7 @@
         <v>-0</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <f aca="false">IF(DAY(B30)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B30)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
@@ -5889,7 +5893,7 @@
       </c>
       <c r="S30" s="12" t="n">
         <f aca="false">S29+R30</f>
-        <v>1552.9101128</v>
+        <v>1318.4960813</v>
       </c>
       <c r="T30" s="15" t="n">
         <f aca="false">IF(AND($A30&gt;$B$100,S30&gt;=0),1,0)</f>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="U30" s="12" t="n">
         <f aca="false">S30-SUM($E$5:E30)-(1+Premissas!$B$14)*SUM($C$5:C30)</f>
-        <v>784.5576128</v>
+        <v>550.1435813</v>
       </c>
       <c r="V30" s="12" t="n">
         <f aca="false">C30/Premissas!$B$15*Premissas!$B$17+(G30+H30)*Premissas!$B$18</f>
@@ -5941,19 +5945,19 @@
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <f aca="false">-G31*Premissas!$B$56*Unitário!$B$22-IF($A31-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A31-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <f aca="false">IF($A31-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A31-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
-        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>265.5156</v>
       </c>
       <c r="M31" s="12" t="n">
@@ -5961,11 +5965,11 @@
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <f aca="false">-H31*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A31-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A31-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O31" s="12" t="n">
-        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A31-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A31-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A31-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -5973,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <f aca="false">IF(DAY(B31)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B31)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
@@ -5982,7 +5986,7 @@
       </c>
       <c r="S31" s="12" t="n">
         <f aca="false">S30+R31</f>
-        <v>1818.4257128</v>
+        <v>1584.0116813</v>
       </c>
       <c r="T31" s="15" t="n">
         <f aca="false">IF(AND($A31&gt;$B$100,S31&gt;=0),1,0)</f>
@@ -5990,7 +5994,7 @@
       </c>
       <c r="U31" s="12" t="n">
         <f aca="false">S31-SUM($E$5:E31)-(1+Premissas!$B$14)*SUM($C$5:C31)</f>
-        <v>1050.0732128</v>
+        <v>815.6591813</v>
       </c>
       <c r="V31" s="12" t="n">
         <f aca="false">C31/Premissas!$B$15*Premissas!$B$17+(G31+H31)*Premissas!$B$18</f>
@@ -6034,19 +6038,19 @@
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <f aca="false">-G32*Premissas!$B$56*Unitário!$B$22-IF($A32-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A32-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <f aca="false">IF($A32-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A32-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>265.5156</v>
       </c>
       <c r="M32" s="12" t="n">
@@ -6054,11 +6058,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <f aca="false">-H32*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A32-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A32-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O32" s="12" t="n">
-        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A32-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A32-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A32-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P32" s="12" t="n">
@@ -6066,7 +6070,7 @@
         <v>-0</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <f aca="false">IF(DAY(B32)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B32)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
@@ -6075,7 +6079,7 @@
       </c>
       <c r="S32" s="12" t="n">
         <f aca="false">S31+R32</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T32" s="15" t="n">
         <f aca="false">IF(AND($A32&gt;$B$100,S32&gt;=0),1,0)</f>
@@ -6083,7 +6087,7 @@
       </c>
       <c r="U32" s="12" t="n">
         <f aca="false">S32-SUM($E$5:E32)-(1+Premissas!$B$14)*SUM($C$5:C32)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V32" s="12" t="n">
         <f aca="false">C32/Premissas!$B$15*Premissas!$B$17+(G32+H32)*Premissas!$B$18</f>
@@ -6127,19 +6131,19 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <f aca="false">-G33*Premissas!$B$56*Unitário!$B$22-IF($A33-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A33-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <f aca="false">IF($A33-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A33-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
@@ -6147,11 +6151,11 @@
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <f aca="false">-H33*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A33-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A33-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O33" s="12" t="n">
-        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A33-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A33-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A33-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -6159,7 +6163,7 @@
         <v>-0</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <f aca="false">IF(DAY(B33)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B33)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R33" s="12" t="n">
@@ -6168,7 +6172,7 @@
       </c>
       <c r="S33" s="12" t="n">
         <f aca="false">S32+R33</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T33" s="15" t="n">
         <f aca="false">IF(AND($A33&gt;$B$100,S33&gt;=0),1,0)</f>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="U33" s="12" t="n">
         <f aca="false">S33-SUM($E$5:E33)-(1+Premissas!$B$14)*SUM($C$5:C33)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V33" s="12" t="n">
         <f aca="false">C33/Premissas!$B$15*Premissas!$B$17+(G33+H33)*Premissas!$B$18</f>
@@ -6220,19 +6224,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <f aca="false">-G34*Premissas!$B$56*Unitário!$B$22-IF($A34-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A34-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <f aca="false">IF($A34-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A34-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
@@ -6240,11 +6244,11 @@
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <f aca="false">-H34*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A34-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A34-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O34" s="12" t="n">
-        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A34-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A34-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A34-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P34" s="12" t="n">
@@ -6252,7 +6256,7 @@
         <v>-0</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <f aca="false">IF(DAY(B34)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B34)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R34" s="12" t="n">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="S34" s="12" t="n">
         <f aca="false">S33+R34</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T34" s="15" t="n">
         <f aca="false">IF(AND($A34&gt;$B$100,S34&gt;=0),1,0)</f>
@@ -6269,7 +6273,7 @@
       </c>
       <c r="U34" s="12" t="n">
         <f aca="false">S34-SUM($E$5:E34)-(1+Premissas!$B$14)*SUM($C$5:C34)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V34" s="12" t="n">
         <f aca="false">C34/Premissas!$B$15*Premissas!$B$17+(G34+H34)*Premissas!$B$18</f>
@@ -6313,19 +6317,19 @@
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <f aca="false">-G35*Premissas!$B$56*Unitário!$B$22-IF($A35-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A35-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <f aca="false">IF($A35-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A35-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
-        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
@@ -6333,11 +6337,11 @@
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <f aca="false">-H35*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A35-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A35-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O35" s="12" t="n">
-        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A35-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A35-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A35-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -6345,7 +6349,7 @@
         <v>-0</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <f aca="false">IF(DAY(B35)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B35)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R35" s="12" t="n">
@@ -6354,7 +6358,7 @@
       </c>
       <c r="S35" s="12" t="n">
         <f aca="false">S34+R35</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T35" s="15" t="n">
         <f aca="false">IF(AND($A35&gt;$B$100,S35&gt;=0),1,0)</f>
@@ -6362,7 +6366,7 @@
       </c>
       <c r="U35" s="12" t="n">
         <f aca="false">S35-SUM($E$5:E35)-(1+Premissas!$B$14)*SUM($C$5:C35)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V35" s="12" t="n">
         <f aca="false">C35/Premissas!$B$15*Premissas!$B$17+(G35+H35)*Premissas!$B$18</f>
@@ -6406,19 +6410,19 @@
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <f aca="false">-G36*Premissas!$B$56*Unitário!$B$22-IF($A36-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A36-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <f aca="false">IF($A36-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A36-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
@@ -6426,11 +6430,11 @@
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <f aca="false">-H36*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A36-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A36-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O36" s="12" t="n">
-        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A36-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A36-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A36-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P36" s="12" t="n">
@@ -6438,7 +6442,7 @@
         <v>-0</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <f aca="false">IF(DAY(B36)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B36)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R36" s="12" t="n">
@@ -6447,7 +6451,7 @@
       </c>
       <c r="S36" s="12" t="n">
         <f aca="false">S35+R36</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T36" s="15" t="n">
         <f aca="false">IF(AND($A36&gt;$B$100,S36&gt;=0),1,0)</f>
@@ -6455,7 +6459,7 @@
       </c>
       <c r="U36" s="12" t="n">
         <f aca="false">S36-SUM($E$5:E36)-(1+Premissas!$B$14)*SUM($C$5:C36)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V36" s="12" t="n">
         <f aca="false">C36/Premissas!$B$15*Premissas!$B$17+(G36+H36)*Premissas!$B$18</f>
@@ -6499,19 +6503,19 @@
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <f aca="false">-G37*Premissas!$B$56*Unitário!$B$22-IF($A37-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A37-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <f aca="false">IF($A37-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A37-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A37-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M37" s="12" t="n">
@@ -6519,11 +6523,11 @@
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <f aca="false">-H37*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A37-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A37-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O37" s="12" t="n">
-        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A37-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A37-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A37-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -6531,7 +6535,7 @@
         <v>-0</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <f aca="false">IF(DAY(B37)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B37)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R37" s="12" t="n">
@@ -6540,7 +6544,7 @@
       </c>
       <c r="S37" s="12" t="n">
         <f aca="false">S36+R37</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T37" s="15" t="n">
         <f aca="false">IF(AND($A37&gt;$B$100,S37&gt;=0),1,0)</f>
@@ -6548,7 +6552,7 @@
       </c>
       <c r="U37" s="12" t="n">
         <f aca="false">S37-SUM($E$5:E37)-(1+Premissas!$B$14)*SUM($C$5:C37)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V37" s="12" t="n">
         <f aca="false">C37/Premissas!$B$15*Premissas!$B$17+(G37+H37)*Premissas!$B$18</f>
@@ -6592,19 +6596,19 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <f aca="false">-G38*Premissas!$B$56*Unitário!$B$22-IF($A38-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A38-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <f aca="false">IF($A38-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A38-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A38-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
@@ -6612,11 +6616,11 @@
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <f aca="false">-H38*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A38-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A38-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O38" s="12" t="n">
-        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A38-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A38-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A38-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P38" s="12" t="n">
@@ -6624,7 +6628,7 @@
         <v>-0</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <f aca="false">IF(DAY(B38)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B38)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R38" s="12" t="n">
@@ -6633,7 +6637,7 @@
       </c>
       <c r="S38" s="12" t="n">
         <f aca="false">S37+R38</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">IF(AND($A38&gt;$B$100,S38&gt;=0),1,0)</f>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="U38" s="12" t="n">
         <f aca="false">S38-SUM($E$5:E38)-(1+Premissas!$B$14)*SUM($C$5:C38)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V38" s="12" t="n">
         <f aca="false">C38/Premissas!$B$15*Premissas!$B$17+(G38+H38)*Premissas!$B$18</f>
@@ -6685,19 +6689,19 @@
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <f aca="false">-G39*Premissas!$B$56*Unitário!$B$22-IF($A39-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A39-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <f aca="false">IF($A39-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A39-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
-        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A39-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
@@ -6705,11 +6709,11 @@
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <f aca="false">-H39*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A39-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A39-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O39" s="12" t="n">
-        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A39-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A39-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A39-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -6717,7 +6721,7 @@
         <v>-0</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <f aca="false">IF(DAY(B39)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B39)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R39" s="12" t="n">
@@ -6726,7 +6730,7 @@
       </c>
       <c r="S39" s="12" t="n">
         <f aca="false">S38+R39</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T39" s="15" t="n">
         <f aca="false">IF(AND($A39&gt;$B$100,S39&gt;=0),1,0)</f>
@@ -6734,7 +6738,7 @@
       </c>
       <c r="U39" s="12" t="n">
         <f aca="false">S39-SUM($E$5:E39)-(1+Premissas!$B$14)*SUM($C$5:C39)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V39" s="12" t="n">
         <f aca="false">C39/Premissas!$B$15*Premissas!$B$17+(G39+H39)*Premissas!$B$18</f>
@@ -6778,19 +6782,19 @@
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <f aca="false">-G40*Premissas!$B$56*Unitário!$B$22-IF($A40-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A40-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <f aca="false">IF($A40-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A40-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L40" s="12" t="n">
-        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A40-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
@@ -6798,11 +6802,11 @@
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <f aca="false">-H40*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A40-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A40-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O40" s="12" t="n">
-        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A40-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A40-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A40-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P40" s="12" t="n">
@@ -6810,7 +6814,7 @@
         <v>-0</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <f aca="false">IF(DAY(B40)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B40)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
@@ -6819,7 +6823,7 @@
       </c>
       <c r="S40" s="12" t="n">
         <f aca="false">S39+R40</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T40" s="15" t="n">
         <f aca="false">IF(AND($A40&gt;$B$100,S40&gt;=0),1,0)</f>
@@ -6827,7 +6831,7 @@
       </c>
       <c r="U40" s="12" t="n">
         <f aca="false">S40-SUM($E$5:E40)-(1+Premissas!$B$14)*SUM($C$5:C40)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V40" s="12" t="n">
         <f aca="false">C40/Premissas!$B$15*Premissas!$B$17+(G40+H40)*Premissas!$B$18</f>
@@ -6871,19 +6875,19 @@
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <f aca="false">-G41*Premissas!$B$56*Unitário!$B$22-IF($A41-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A41-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <f aca="false">IF($A41-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A41-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
-        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L41" s="12" t="n">
-        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A41-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M41" s="12" t="n">
@@ -6891,11 +6895,11 @@
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <f aca="false">-H41*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A41-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A41-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A41-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A41-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A41-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -6903,7 +6907,7 @@
         <v>-0</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <f aca="false">IF(DAY(B41)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B41)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R41" s="12" t="n">
@@ -6912,7 +6916,7 @@
       </c>
       <c r="S41" s="12" t="n">
         <f aca="false">S40+R41</f>
-        <v>2083.9413128</v>
+        <v>1849.5272813</v>
       </c>
       <c r="T41" s="15" t="n">
         <f aca="false">IF(AND($A41&gt;$B$100,S41&gt;=0),1,0)</f>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="U41" s="12" t="n">
         <f aca="false">S41-SUM($E$5:E41)-(1+Premissas!$B$14)*SUM($C$5:C41)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V41" s="12" t="n">
         <f aca="false">C41/Premissas!$B$15*Premissas!$B$17+(G41+H41)*Premissas!$B$18</f>
@@ -6964,19 +6968,19 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <f aca="false">-G42*Premissas!$B$56*Unitário!$B$22-IF($A42-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A42-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <f aca="false">IF($A42-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A42-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A42-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M42" s="12" t="n">
@@ -6984,11 +6988,11 @@
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <f aca="false">-H42*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A42-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A42-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O42" s="12" t="n">
-        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A42-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A42-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A42-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P42" s="12" t="n">
@@ -6996,7 +7000,7 @@
         <v>-0</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <f aca="false">IF(DAY(B42)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B42)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R42" s="12" t="n">
@@ -7005,7 +7009,7 @@
       </c>
       <c r="S42" s="12" t="n">
         <f aca="false">S41+R42</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="T42" s="15" t="n">
         <f aca="false">IF(AND($A42&gt;$B$100,S42&gt;=0),1,0)</f>
@@ -7013,7 +7017,7 @@
       </c>
       <c r="U42" s="12" t="n">
         <f aca="false">S42-SUM($E$5:E42)-(1+Premissas!$B$14)*SUM($C$5:C42)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V42" s="12" t="n">
         <f aca="false">C42/Premissas!$B$15*Premissas!$B$17+(G42+H42)*Premissas!$B$18</f>
@@ -7057,19 +7061,19 @@
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <f aca="false">-G43*Premissas!$B$56*Unitário!$B$22-IF($A43-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A43-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <f aca="false">IF($A43-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A43-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
-        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A43-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
@@ -7077,11 +7081,11 @@
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <f aca="false">-H43*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A43-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A43-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O43" s="12" t="n">
-        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A43-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A43-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A43-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -7089,7 +7093,7 @@
         <v>-0</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <f aca="false">IF(DAY(B43)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B43)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R43" s="12" t="n">
@@ -7098,7 +7102,7 @@
       </c>
       <c r="S43" s="12" t="n">
         <f aca="false">S42+R43</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="T43" s="15" t="n">
         <f aca="false">IF(AND($A43&gt;$B$100,S43&gt;=0),1,0)</f>
@@ -7106,7 +7110,7 @@
       </c>
       <c r="U43" s="12" t="n">
         <f aca="false">S43-SUM($E$5:E43)-(1+Premissas!$B$14)*SUM($C$5:C43)</f>
-        <v>1315.5888128</v>
+        <v>1081.1747813</v>
       </c>
       <c r="V43" s="12" t="n">
         <f aca="false">C43/Premissas!$B$15*Premissas!$B$17+(G43+H43)*Premissas!$B$18</f>
@@ -7150,19 +7154,19 @@
         <v>0</v>
       </c>
       <c r="I44" s="12" t="n">
-        <f aca="false">-G44*Premissas!$B$56*Unitário!$B$22-IF($A44-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A44-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <f aca="false">IF($A44-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A44-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A44-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M44" s="12" t="n">
@@ -7170,11 +7174,11 @@
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <f aca="false">-H44*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A44-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A44-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O44" s="12" t="n">
-        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A44-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A44-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A44-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P44" s="12" t="n">
@@ -7182,7 +7186,7 @@
         <v>-0</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <f aca="false">IF(DAY(B44)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B44)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>-57.49</v>
       </c>
       <c r="R44" s="12" t="n">
@@ -7191,7 +7195,7 @@
       </c>
       <c r="S44" s="12" t="n">
         <f aca="false">S43+R44</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">IF(AND($A44&gt;$B$100,S44&gt;=0),1,0)</f>
@@ -7199,7 +7203,7 @@
       </c>
       <c r="U44" s="12" t="n">
         <f aca="false">S44-SUM($E$5:E44)-(1+Premissas!$B$14)*SUM($C$5:C44)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V44" s="12" t="n">
         <f aca="false">C44/Premissas!$B$15*Premissas!$B$17+(G44+H44)*Premissas!$B$18</f>
@@ -7243,19 +7247,19 @@
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <f aca="false">-G45*Premissas!$B$56*Unitário!$B$22-IF($A45-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A45-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <f aca="false">IF($A45-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A45-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
-        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A45-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
@@ -7263,11 +7267,11 @@
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <f aca="false">-H45*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A45-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A45-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A45-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A45-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A45-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P45" s="12" t="n">
@@ -7275,7 +7279,7 @@
         <v>-0</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <f aca="false">IF(DAY(B45)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B45)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R45" s="12" t="n">
@@ -7284,7 +7288,7 @@
       </c>
       <c r="S45" s="12" t="n">
         <f aca="false">S44+R45</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T45" s="15" t="n">
         <f aca="false">IF(AND($A45&gt;$B$100,S45&gt;=0),1,0)</f>
@@ -7292,7 +7296,7 @@
       </c>
       <c r="U45" s="12" t="n">
         <f aca="false">S45-SUM($E$5:E45)-(1+Premissas!$B$14)*SUM($C$5:C45)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V45" s="12" t="n">
         <f aca="false">C45/Premissas!$B$15*Premissas!$B$17+(G45+H45)*Premissas!$B$18</f>
@@ -7336,19 +7340,19 @@
         <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <f aca="false">-G46*Premissas!$B$56*Unitário!$B$22-IF($A46-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A46-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <f aca="false">IF($A46-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A46-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
-        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A46-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
@@ -7356,11 +7360,11 @@
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <f aca="false">-H46*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A46-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A46-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O46" s="12" t="n">
-        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A46-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A46-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A46-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P46" s="12" t="n">
@@ -7368,7 +7372,7 @@
         <v>-0</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <f aca="false">IF(DAY(B46)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B46)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R46" s="12" t="n">
@@ -7377,7 +7381,7 @@
       </c>
       <c r="S46" s="12" t="n">
         <f aca="false">S45+R46</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">IF(AND($A46&gt;$B$100,S46&gt;=0),1,0)</f>
@@ -7385,7 +7389,7 @@
       </c>
       <c r="U46" s="12" t="n">
         <f aca="false">S46-SUM($E$5:E46)-(1+Premissas!$B$14)*SUM($C$5:C46)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V46" s="12" t="n">
         <f aca="false">C46/Premissas!$B$15*Premissas!$B$17+(G46+H46)*Premissas!$B$18</f>
@@ -7429,19 +7433,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <f aca="false">-G47*Premissas!$B$56*Unitário!$B$22-IF($A47-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A47-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <f aca="false">IF($A47-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A47-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
-        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A47-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
@@ -7449,11 +7453,11 @@
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <f aca="false">-H47*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A47-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A47-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O47" s="12" t="n">
-        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A47-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A47-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A47-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -7461,7 +7465,7 @@
         <v>-0</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <f aca="false">IF(DAY(B47)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B47)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R47" s="12" t="n">
@@ -7470,7 +7474,7 @@
       </c>
       <c r="S47" s="12" t="n">
         <f aca="false">S46+R47</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">IF(AND($A47&gt;$B$100,S47&gt;=0),1,0)</f>
@@ -7478,7 +7482,7 @@
       </c>
       <c r="U47" s="12" t="n">
         <f aca="false">S47-SUM($E$5:E47)-(1+Premissas!$B$14)*SUM($C$5:C47)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V47" s="12" t="n">
         <f aca="false">C47/Premissas!$B$15*Premissas!$B$17+(G47+H47)*Premissas!$B$18</f>
@@ -7522,19 +7526,19 @@
         <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <f aca="false">-G48*Premissas!$B$56*Unitário!$B$22-IF($A48-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A48-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J48" s="12" t="n">
-        <f aca="false">IF($A48-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A48-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
-        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L48" s="12" t="n">
-        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A48-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M48" s="12" t="n">
@@ -7542,11 +7546,11 @@
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <f aca="false">-H48*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A48-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A48-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O48" s="12" t="n">
-        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A48-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A48-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A48-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P48" s="12" t="n">
@@ -7554,7 +7558,7 @@
         <v>-0</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <f aca="false">IF(DAY(B48)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B48)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R48" s="12" t="n">
@@ -7563,7 +7567,7 @@
       </c>
       <c r="S48" s="12" t="n">
         <f aca="false">S47+R48</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">IF(AND($A48&gt;$B$100,S48&gt;=0),1,0)</f>
@@ -7571,7 +7575,7 @@
       </c>
       <c r="U48" s="12" t="n">
         <f aca="false">S48-SUM($E$5:E48)-(1+Premissas!$B$14)*SUM($C$5:C48)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V48" s="12" t="n">
         <f aca="false">C48/Premissas!$B$15*Premissas!$B$17+(G48+H48)*Premissas!$B$18</f>
@@ -7615,19 +7619,19 @@
         <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <f aca="false">-G49*Premissas!$B$56*Unitário!$B$22-IF($A49-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A49-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <f aca="false">IF($A49-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A49-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
-        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L49" s="12" t="n">
-        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A49-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M49" s="12" t="n">
@@ -7635,11 +7639,11 @@
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <f aca="false">-H49*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A49-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A49-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O49" s="12" t="n">
-        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A49-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A49-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A49-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P49" s="12" t="n">
@@ -7647,7 +7651,7 @@
         <v>-0</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <f aca="false">IF(DAY(B49)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B49)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R49" s="12" t="n">
@@ -7656,7 +7660,7 @@
       </c>
       <c r="S49" s="12" t="n">
         <f aca="false">S48+R49</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">IF(AND($A49&gt;$B$100,S49&gt;=0),1,0)</f>
@@ -7664,7 +7668,7 @@
       </c>
       <c r="U49" s="12" t="n">
         <f aca="false">S49-SUM($E$5:E49)-(1+Premissas!$B$14)*SUM($C$5:C49)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V49" s="12" t="n">
         <f aca="false">C49/Premissas!$B$15*Premissas!$B$17+(G49+H49)*Premissas!$B$18</f>
@@ -7708,19 +7712,19 @@
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <f aca="false">-G50*Premissas!$B$56*Unitário!$B$22-IF($A50-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A50-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <f aca="false">IF($A50-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A50-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
-        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A50-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M50" s="12" t="n">
@@ -7728,11 +7732,11 @@
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <f aca="false">-H50*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A50-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A50-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O50" s="12" t="n">
-        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A50-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A50-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A50-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P50" s="12" t="n">
@@ -7740,7 +7744,7 @@
         <v>-0</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <f aca="false">IF(DAY(B50)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B50)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R50" s="12" t="n">
@@ -7749,7 +7753,7 @@
       </c>
       <c r="S50" s="12" t="n">
         <f aca="false">S49+R50</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T50" s="15" t="n">
         <f aca="false">IF(AND($A50&gt;$B$100,S50&gt;=0),1,0)</f>
@@ -7757,7 +7761,7 @@
       </c>
       <c r="U50" s="12" t="n">
         <f aca="false">S50-SUM($E$5:E50)-(1+Premissas!$B$14)*SUM($C$5:C50)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V50" s="12" t="n">
         <f aca="false">C50/Premissas!$B$15*Premissas!$B$17+(G50+H50)*Premissas!$B$18</f>
@@ -7801,19 +7805,19 @@
         <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <f aca="false">-G51*Premissas!$B$56*Unitário!$B$22-IF($A51-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A51-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <f aca="false">IF($A51-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A51-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
-        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L51" s="12" t="n">
-        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A51-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M51" s="12" t="n">
@@ -7821,11 +7825,11 @@
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <f aca="false">-H51*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A51-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A51-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O51" s="12" t="n">
-        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A51-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A51-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A51-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P51" s="12" t="n">
@@ -7833,7 +7837,7 @@
         <v>-0</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <f aca="false">IF(DAY(B51)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B51)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R51" s="12" t="n">
@@ -7842,7 +7846,7 @@
       </c>
       <c r="S51" s="12" t="n">
         <f aca="false">S50+R51</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T51" s="15" t="n">
         <f aca="false">IF(AND($A51&gt;$B$100,S51&gt;=0),1,0)</f>
@@ -7850,7 +7854,7 @@
       </c>
       <c r="U51" s="12" t="n">
         <f aca="false">S51-SUM($E$5:E51)-(1+Premissas!$B$14)*SUM($C$5:C51)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V51" s="12" t="n">
         <f aca="false">C51/Premissas!$B$15*Premissas!$B$17+(G51+H51)*Premissas!$B$18</f>
@@ -7894,19 +7898,19 @@
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <f aca="false">-G52*Premissas!$B$56*Unitário!$B$22-IF($A52-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A52-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J52" s="12" t="n">
-        <f aca="false">IF($A52-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A52-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K52" s="12" t="n">
-        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L52" s="12" t="n">
-        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A52-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M52" s="12" t="n">
@@ -7914,11 +7918,11 @@
         <v>0</v>
       </c>
       <c r="N52" s="12" t="n">
-        <f aca="false">-H52*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A52-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A52-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O52" s="12" t="n">
-        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A52-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A52-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A52-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P52" s="12" t="n">
@@ -7926,7 +7930,7 @@
         <v>-0</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <f aca="false">IF(DAY(B52)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B52)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R52" s="12" t="n">
@@ -7935,7 +7939,7 @@
       </c>
       <c r="S52" s="12" t="n">
         <f aca="false">S51+R52</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T52" s="15" t="n">
         <f aca="false">IF(AND($A52&gt;$B$100,S52&gt;=0),1,0)</f>
@@ -7943,7 +7947,7 @@
       </c>
       <c r="U52" s="12" t="n">
         <f aca="false">S52-SUM($E$5:E52)-(1+Premissas!$B$14)*SUM($C$5:C52)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V52" s="12" t="n">
         <f aca="false">C52/Premissas!$B$15*Premissas!$B$17+(G52+H52)*Premissas!$B$18</f>
@@ -7987,19 +7991,19 @@
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <f aca="false">-G53*Premissas!$B$56*Unitário!$B$22-IF($A53-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A53-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J53" s="12" t="n">
-        <f aca="false">IF($A53-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A53-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
-        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L53" s="12" t="n">
-        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A53-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
@@ -8007,11 +8011,11 @@
         <v>0</v>
       </c>
       <c r="N53" s="12" t="n">
-        <f aca="false">-H53*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A53-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A53-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O53" s="12" t="n">
-        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A53-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A53-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A53-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -8019,7 +8023,7 @@
         <v>-0</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <f aca="false">IF(DAY(B53)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B53)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R53" s="12" t="n">
@@ -8028,7 +8032,7 @@
       </c>
       <c r="S53" s="12" t="n">
         <f aca="false">S52+R53</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T53" s="15" t="n">
         <f aca="false">IF(AND($A53&gt;$B$100,S53&gt;=0),1,0)</f>
@@ -8036,7 +8040,7 @@
       </c>
       <c r="U53" s="12" t="n">
         <f aca="false">S53-SUM($E$5:E53)-(1+Premissas!$B$14)*SUM($C$5:C53)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V53" s="12" t="n">
         <f aca="false">C53/Premissas!$B$15*Premissas!$B$17+(G53+H53)*Premissas!$B$18</f>
@@ -8080,19 +8084,19 @@
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <f aca="false">-G54*Premissas!$B$56*Unitário!$B$22-IF($A54-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A54-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J54" s="12" t="n">
-        <f aca="false">IF($A54-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A54-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K54" s="12" t="n">
-        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L54" s="12" t="n">
-        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A54-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M54" s="12" t="n">
@@ -8100,11 +8104,11 @@
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <f aca="false">-H54*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A54-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A54-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O54" s="12" t="n">
-        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A54-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A54-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A54-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P54" s="12" t="n">
@@ -8112,7 +8116,7 @@
         <v>-0</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <f aca="false">IF(DAY(B54)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B54)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R54" s="12" t="n">
@@ -8121,7 +8125,7 @@
       </c>
       <c r="S54" s="12" t="n">
         <f aca="false">S53+R54</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T54" s="15" t="n">
         <f aca="false">IF(AND($A54&gt;$B$100,S54&gt;=0),1,0)</f>
@@ -8129,7 +8133,7 @@
       </c>
       <c r="U54" s="12" t="n">
         <f aca="false">S54-SUM($E$5:E54)-(1+Premissas!$B$14)*SUM($C$5:C54)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V54" s="12" t="n">
         <f aca="false">C54/Premissas!$B$15*Premissas!$B$17+(G54+H54)*Premissas!$B$18</f>
@@ -8173,19 +8177,19 @@
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <f aca="false">-G55*Premissas!$B$56*Unitário!$B$22-IF($A55-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A55-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J55" s="12" t="n">
-        <f aca="false">IF($A55-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A55-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
-        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L55" s="12" t="n">
-        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A55-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M55" s="12" t="n">
@@ -8193,11 +8197,11 @@
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <f aca="false">-H55*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A55-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A55-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O55" s="12" t="n">
-        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A55-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A55-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A55-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -8205,7 +8209,7 @@
         <v>-0</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <f aca="false">IF(DAY(B55)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B55)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
@@ -8214,7 +8218,7 @@
       </c>
       <c r="S55" s="12" t="n">
         <f aca="false">S54+R55</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T55" s="15" t="n">
         <f aca="false">IF(AND($A55&gt;$B$100,S55&gt;=0),1,0)</f>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="U55" s="12" t="n">
         <f aca="false">S55-SUM($E$5:E55)-(1+Premissas!$B$14)*SUM($C$5:C55)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V55" s="12" t="n">
         <f aca="false">C55/Premissas!$B$15*Premissas!$B$17+(G55+H55)*Premissas!$B$18</f>
@@ -8266,19 +8270,19 @@
         <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <f aca="false">-G56*Premissas!$B$56*Unitário!$B$22-IF($A56-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A56-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J56" s="12" t="n">
-        <f aca="false">IF($A56-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A56-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K56" s="12" t="n">
-        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L56" s="12" t="n">
-        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A56-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M56" s="12" t="n">
@@ -8286,11 +8290,11 @@
         <v>0</v>
       </c>
       <c r="N56" s="12" t="n">
-        <f aca="false">-H56*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A56-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A56-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O56" s="12" t="n">
-        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A56-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A56-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A56-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P56" s="12" t="n">
@@ -8298,7 +8302,7 @@
         <v>-0</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <f aca="false">IF(DAY(B56)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B56)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R56" s="12" t="n">
@@ -8307,7 +8311,7 @@
       </c>
       <c r="S56" s="12" t="n">
         <f aca="false">S55+R56</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T56" s="15" t="n">
         <f aca="false">IF(AND($A56&gt;$B$100,S56&gt;=0),1,0)</f>
@@ -8315,7 +8319,7 @@
       </c>
       <c r="U56" s="12" t="n">
         <f aca="false">S56-SUM($E$5:E56)-(1+Premissas!$B$14)*SUM($C$5:C56)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V56" s="12" t="n">
         <f aca="false">C56/Premissas!$B$15*Premissas!$B$17+(G56+H56)*Premissas!$B$18</f>
@@ -8359,19 +8363,19 @@
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <f aca="false">-G57*Premissas!$B$56*Unitário!$B$22-IF($A57-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A57-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <f aca="false">IF($A57-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A57-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K57" s="12" t="n">
-        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L57" s="12" t="n">
-        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A57-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M57" s="12" t="n">
@@ -8379,11 +8383,11 @@
         <v>0</v>
       </c>
       <c r="N57" s="12" t="n">
-        <f aca="false">-H57*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A57-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A57-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O57" s="12" t="n">
-        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A57-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A57-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A57-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -8391,7 +8395,7 @@
         <v>-0</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <f aca="false">IF(DAY(B57)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B57)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R57" s="12" t="n">
@@ -8400,7 +8404,7 @@
       </c>
       <c r="S57" s="12" t="n">
         <f aca="false">S56+R57</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T57" s="15" t="n">
         <f aca="false">IF(AND($A57&gt;$B$100,S57&gt;=0),1,0)</f>
@@ -8408,7 +8412,7 @@
       </c>
       <c r="U57" s="12" t="n">
         <f aca="false">S57-SUM($E$5:E57)-(1+Premissas!$B$14)*SUM($C$5:C57)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V57" s="12" t="n">
         <f aca="false">C57/Premissas!$B$15*Premissas!$B$17+(G57+H57)*Premissas!$B$18</f>
@@ -8452,19 +8456,19 @@
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <f aca="false">-G58*Premissas!$B$56*Unitário!$B$22-IF($A58-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A58-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J58" s="12" t="n">
-        <f aca="false">IF($A58-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A58-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K58" s="12" t="n">
-        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L58" s="12" t="n">
-        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A58-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M58" s="12" t="n">
@@ -8472,11 +8476,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="12" t="n">
-        <f aca="false">-H58*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A58-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A58-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O58" s="12" t="n">
-        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A58-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A58-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A58-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P58" s="12" t="n">
@@ -8484,7 +8488,7 @@
         <v>-0</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <f aca="false">IF(DAY(B58)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B58)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R58" s="12" t="n">
@@ -8493,7 +8497,7 @@
       </c>
       <c r="S58" s="12" t="n">
         <f aca="false">S57+R58</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T58" s="15" t="n">
         <f aca="false">IF(AND($A58&gt;$B$100,S58&gt;=0),1,0)</f>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="U58" s="12" t="n">
         <f aca="false">S58-SUM($E$5:E58)-(1+Premissas!$B$14)*SUM($C$5:C58)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V58" s="12" t="n">
         <f aca="false">C58/Premissas!$B$15*Premissas!$B$17+(G58+H58)*Premissas!$B$18</f>
@@ -8545,19 +8549,19 @@
         <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <f aca="false">-G59*Premissas!$B$56*Unitário!$B$22-IF($A59-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A59-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <f aca="false">IF($A59-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A59-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K59" s="12" t="n">
-        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L59" s="12" t="n">
-        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A59-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M59" s="12" t="n">
@@ -8565,11 +8569,11 @@
         <v>0</v>
       </c>
       <c r="N59" s="12" t="n">
-        <f aca="false">-H59*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A59-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A59-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O59" s="12" t="n">
-        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A59-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A59-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A59-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -8577,7 +8581,7 @@
         <v>-0</v>
       </c>
       <c r="Q59" s="12" t="n">
-        <f aca="false">IF(DAY(B59)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B59)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R59" s="12" t="n">
@@ -8586,7 +8590,7 @@
       </c>
       <c r="S59" s="12" t="n">
         <f aca="false">S58+R59</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T59" s="15" t="n">
         <f aca="false">IF(AND($A59&gt;$B$100,S59&gt;=0),1,0)</f>
@@ -8594,7 +8598,7 @@
       </c>
       <c r="U59" s="12" t="n">
         <f aca="false">S59-SUM($E$5:E59)-(1+Premissas!$B$14)*SUM($C$5:C59)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V59" s="12" t="n">
         <f aca="false">C59/Premissas!$B$15*Premissas!$B$17+(G59+H59)*Premissas!$B$18</f>
@@ -8638,19 +8642,19 @@
         <v>0</v>
       </c>
       <c r="I60" s="12" t="n">
-        <f aca="false">-G60*Premissas!$B$56*Unitário!$B$22-IF($A60-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A60-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <f aca="false">IF($A60-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A60-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K60" s="12" t="n">
-        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L60" s="12" t="n">
-        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A60-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M60" s="12" t="n">
@@ -8658,11 +8662,11 @@
         <v>0</v>
       </c>
       <c r="N60" s="12" t="n">
-        <f aca="false">-H60*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A60-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A60-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O60" s="12" t="n">
-        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A60-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A60-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A60-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P60" s="12" t="n">
@@ -8670,7 +8674,7 @@
         <v>-0</v>
       </c>
       <c r="Q60" s="12" t="n">
-        <f aca="false">IF(DAY(B60)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B60)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R60" s="12" t="n">
@@ -8679,7 +8683,7 @@
       </c>
       <c r="S60" s="12" t="n">
         <f aca="false">S59+R60</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T60" s="15" t="n">
         <f aca="false">IF(AND($A60&gt;$B$100,S60&gt;=0),1,0)</f>
@@ -8687,7 +8691,7 @@
       </c>
       <c r="U60" s="12" t="n">
         <f aca="false">S60-SUM($E$5:E60)-(1+Premissas!$B$14)*SUM($C$5:C60)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V60" s="12" t="n">
         <f aca="false">C60/Premissas!$B$15*Premissas!$B$17+(G60+H60)*Premissas!$B$18</f>
@@ -8731,19 +8735,19 @@
         <v>0</v>
       </c>
       <c r="I61" s="12" t="n">
-        <f aca="false">-G61*Premissas!$B$56*Unitário!$B$22-IF($A61-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A61-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J61" s="12" t="n">
-        <f aca="false">IF($A61-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A61-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K61" s="12" t="n">
-        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L61" s="12" t="n">
-        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A61-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M61" s="12" t="n">
@@ -8751,11 +8755,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="12" t="n">
-        <f aca="false">-H61*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A61-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A61-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O61" s="12" t="n">
-        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A61-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A61-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A61-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -8763,7 +8767,7 @@
         <v>-0</v>
       </c>
       <c r="Q61" s="12" t="n">
-        <f aca="false">IF(DAY(B61)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B61)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R61" s="12" t="n">
@@ -8772,7 +8776,7 @@
       </c>
       <c r="S61" s="12" t="n">
         <f aca="false">S60+R61</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T61" s="15" t="n">
         <f aca="false">IF(AND($A61&gt;$B$100,S61&gt;=0),1,0)</f>
@@ -8780,7 +8784,7 @@
       </c>
       <c r="U61" s="12" t="n">
         <f aca="false">S61-SUM($E$5:E61)-(1+Premissas!$B$14)*SUM($C$5:C61)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V61" s="12" t="n">
         <f aca="false">C61/Premissas!$B$15*Premissas!$B$17+(G61+H61)*Premissas!$B$18</f>
@@ -8824,19 +8828,19 @@
         <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <f aca="false">-G62*Premissas!$B$56*Unitário!$B$22-IF($A62-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A62-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <f aca="false">IF($A62-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A62-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
-        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L62" s="12" t="n">
-        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A62-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M62" s="12" t="n">
@@ -8844,11 +8848,11 @@
         <v>0</v>
       </c>
       <c r="N62" s="12" t="n">
-        <f aca="false">-H62*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A62-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A62-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O62" s="12" t="n">
-        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A62-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A62-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A62-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P62" s="12" t="n">
@@ -8856,7 +8860,7 @@
         <v>-0</v>
       </c>
       <c r="Q62" s="12" t="n">
-        <f aca="false">IF(DAY(B62)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B62)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R62" s="12" t="n">
@@ -8865,7 +8869,7 @@
       </c>
       <c r="S62" s="12" t="n">
         <f aca="false">S61+R62</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T62" s="15" t="n">
         <f aca="false">IF(AND($A62&gt;$B$100,S62&gt;=0),1,0)</f>
@@ -8873,7 +8877,7 @@
       </c>
       <c r="U62" s="12" t="n">
         <f aca="false">S62-SUM($E$5:E62)-(1+Premissas!$B$14)*SUM($C$5:C62)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V62" s="12" t="n">
         <f aca="false">C62/Premissas!$B$15*Premissas!$B$17+(G62+H62)*Premissas!$B$18</f>
@@ -8917,19 +8921,19 @@
         <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <f aca="false">-G63*Premissas!$B$56*Unitário!$B$22-IF($A63-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A63-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <f aca="false">IF($A63-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A63-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K63" s="12" t="n">
-        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L63" s="12" t="n">
-        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A63-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M63" s="12" t="n">
@@ -8937,11 +8941,11 @@
         <v>0</v>
       </c>
       <c r="N63" s="12" t="n">
-        <f aca="false">-H63*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A63-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A63-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O63" s="12" t="n">
-        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A63-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A63-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A63-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -8949,7 +8953,7 @@
         <v>-0</v>
       </c>
       <c r="Q63" s="12" t="n">
-        <f aca="false">IF(DAY(B63)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B63)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R63" s="12" t="n">
@@ -8958,7 +8962,7 @@
       </c>
       <c r="S63" s="12" t="n">
         <f aca="false">S62+R63</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T63" s="15" t="n">
         <f aca="false">IF(AND($A63&gt;$B$100,S63&gt;=0),1,0)</f>
@@ -8966,7 +8970,7 @@
       </c>
       <c r="U63" s="12" t="n">
         <f aca="false">S63-SUM($E$5:E63)-(1+Premissas!$B$14)*SUM($C$5:C63)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">C63/Premissas!$B$15*Premissas!$B$17+(G63+H63)*Premissas!$B$18</f>
@@ -9010,19 +9014,19 @@
         <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <f aca="false">-G64*Premissas!$B$56*Unitário!$B$22-IF($A64-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A64-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J64" s="12" t="n">
-        <f aca="false">IF($A64-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A64-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K64" s="12" t="n">
-        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A64-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M64" s="12" t="n">
@@ -9030,11 +9034,11 @@
         <v>0</v>
       </c>
       <c r="N64" s="12" t="n">
-        <f aca="false">-H64*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A64-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A64-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O64" s="12" t="n">
-        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A64-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A64-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A64-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P64" s="12" t="n">
@@ -9042,7 +9046,7 @@
         <v>-0</v>
       </c>
       <c r="Q64" s="12" t="n">
-        <f aca="false">IF(DAY(B64)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B64)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R64" s="12" t="n">
@@ -9051,7 +9055,7 @@
       </c>
       <c r="S64" s="12" t="n">
         <f aca="false">S63+R64</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T64" s="15" t="n">
         <f aca="false">IF(AND($A64&gt;$B$100,S64&gt;=0),1,0)</f>
@@ -9059,7 +9063,7 @@
       </c>
       <c r="U64" s="12" t="n">
         <f aca="false">S64-SUM($E$5:E64)-(1+Premissas!$B$14)*SUM($C$5:C64)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">C64/Premissas!$B$15*Premissas!$B$17+(G64+H64)*Premissas!$B$18</f>
@@ -9103,19 +9107,19 @@
         <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <f aca="false">-G65*Premissas!$B$56*Unitário!$B$22-IF($A65-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A65-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J65" s="12" t="n">
-        <f aca="false">IF($A65-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A65-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
-        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L65" s="12" t="n">
-        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A65-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M65" s="12" t="n">
@@ -9123,11 +9127,11 @@
         <v>0</v>
       </c>
       <c r="N65" s="12" t="n">
-        <f aca="false">-H65*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A65-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A65-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O65" s="12" t="n">
-        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A65-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A65-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A65-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -9135,7 +9139,7 @@
         <v>-0</v>
       </c>
       <c r="Q65" s="12" t="n">
-        <f aca="false">IF(DAY(B65)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B65)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R65" s="12" t="n">
@@ -9144,7 +9148,7 @@
       </c>
       <c r="S65" s="12" t="n">
         <f aca="false">S64+R65</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T65" s="15" t="n">
         <f aca="false">IF(AND($A65&gt;$B$100,S65&gt;=0),1,0)</f>
@@ -9152,7 +9156,7 @@
       </c>
       <c r="U65" s="12" t="n">
         <f aca="false">S65-SUM($E$5:E65)-(1+Premissas!$B$14)*SUM($C$5:C65)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">C65/Premissas!$B$15*Premissas!$B$17+(G65+H65)*Premissas!$B$18</f>
@@ -9196,19 +9200,19 @@
         <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <f aca="false">-G66*Premissas!$B$56*Unitário!$B$22-IF($A66-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A66-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <f aca="false">IF($A66-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A66-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K66" s="12" t="n">
-        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A66-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M66" s="12" t="n">
@@ -9216,11 +9220,11 @@
         <v>0</v>
       </c>
       <c r="N66" s="12" t="n">
-        <f aca="false">-H66*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A66-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A66-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O66" s="12" t="n">
-        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A66-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A66-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A66-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P66" s="12" t="n">
@@ -9228,7 +9232,7 @@
         <v>-0</v>
       </c>
       <c r="Q66" s="12" t="n">
-        <f aca="false">IF(DAY(B66)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B66)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R66" s="12" t="n">
@@ -9237,7 +9241,7 @@
       </c>
       <c r="S66" s="12" t="n">
         <f aca="false">S65+R66</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T66" s="15" t="n">
         <f aca="false">IF(AND($A66&gt;$B$100,S66&gt;=0),1,0)</f>
@@ -9245,7 +9249,7 @@
       </c>
       <c r="U66" s="12" t="n">
         <f aca="false">S66-SUM($E$5:E66)-(1+Premissas!$B$14)*SUM($C$5:C66)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">C66/Premissas!$B$15*Premissas!$B$17+(G66+H66)*Premissas!$B$18</f>
@@ -9289,19 +9293,19 @@
         <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <f aca="false">-G67*Premissas!$B$56*Unitário!$B$22-IF($A67-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A67-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <f aca="false">IF($A67-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A67-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K67" s="12" t="n">
-        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A67-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M67" s="12" t="n">
@@ -9309,11 +9313,11 @@
         <v>0</v>
       </c>
       <c r="N67" s="12" t="n">
-        <f aca="false">-H67*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A67-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A67-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O67" s="12" t="n">
-        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A67-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A67-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A67-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -9321,7 +9325,7 @@
         <v>-0</v>
       </c>
       <c r="Q67" s="12" t="n">
-        <f aca="false">IF(DAY(B67)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B67)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R67" s="12" t="n">
@@ -9330,7 +9334,7 @@
       </c>
       <c r="S67" s="12" t="n">
         <f aca="false">S66+R67</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T67" s="15" t="n">
         <f aca="false">IF(AND($A67&gt;$B$100,S67&gt;=0),1,0)</f>
@@ -9338,7 +9342,7 @@
       </c>
       <c r="U67" s="12" t="n">
         <f aca="false">S67-SUM($E$5:E67)-(1+Premissas!$B$14)*SUM($C$5:C67)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V67" s="12" t="n">
         <f aca="false">C67/Premissas!$B$15*Premissas!$B$17+(G67+H67)*Premissas!$B$18</f>
@@ -9382,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <f aca="false">-G68*Premissas!$B$56*Unitário!$B$22-IF($A68-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A68-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J68" s="12" t="n">
-        <f aca="false">IF($A68-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A68-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
-        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L68" s="12" t="n">
-        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A68-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M68" s="12" t="n">
@@ -9402,11 +9406,11 @@
         <v>0</v>
       </c>
       <c r="N68" s="12" t="n">
-        <f aca="false">-H68*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A68-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A68-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O68" s="12" t="n">
-        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A68-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A68-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A68-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P68" s="12" t="n">
@@ -9414,7 +9418,7 @@
         <v>-0</v>
       </c>
       <c r="Q68" s="12" t="n">
-        <f aca="false">IF(DAY(B68)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B68)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R68" s="12" t="n">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="S68" s="12" t="n">
         <f aca="false">S67+R68</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T68" s="15" t="n">
         <f aca="false">IF(AND($A68&gt;$B$100,S68&gt;=0),1,0)</f>
@@ -9431,7 +9435,7 @@
       </c>
       <c r="U68" s="12" t="n">
         <f aca="false">S68-SUM($E$5:E68)-(1+Premissas!$B$14)*SUM($C$5:C68)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V68" s="12" t="n">
         <f aca="false">C68/Premissas!$B$15*Premissas!$B$17+(G68+H68)*Premissas!$B$18</f>
@@ -9475,19 +9479,19 @@
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <f aca="false">-G69*Premissas!$B$56*Unitário!$B$22-IF($A69-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A69-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <f aca="false">IF($A69-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A69-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
-        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A69-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M69" s="12" t="n">
@@ -9495,11 +9499,11 @@
         <v>0</v>
       </c>
       <c r="N69" s="12" t="n">
-        <f aca="false">-H69*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A69-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A69-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O69" s="12" t="n">
-        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A69-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A69-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A69-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -9507,7 +9511,7 @@
         <v>-0</v>
       </c>
       <c r="Q69" s="12" t="n">
-        <f aca="false">IF(DAY(B69)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B69)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R69" s="12" t="n">
@@ -9516,7 +9520,7 @@
       </c>
       <c r="S69" s="12" t="n">
         <f aca="false">S68+R69</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T69" s="15" t="n">
         <f aca="false">IF(AND($A69&gt;$B$100,S69&gt;=0),1,0)</f>
@@ -9524,7 +9528,7 @@
       </c>
       <c r="U69" s="12" t="n">
         <f aca="false">S69-SUM($E$5:E69)-(1+Premissas!$B$14)*SUM($C$5:C69)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V69" s="12" t="n">
         <f aca="false">C69/Premissas!$B$15*Premissas!$B$17+(G69+H69)*Premissas!$B$18</f>
@@ -9568,19 +9572,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <f aca="false">-G70*Premissas!$B$56*Unitário!$B$22-IF($A70-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A70-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <f aca="false">IF($A70-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A70-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K70" s="12" t="n">
-        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L70" s="12" t="n">
-        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A70-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M70" s="12" t="n">
@@ -9588,11 +9592,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="12" t="n">
-        <f aca="false">-H70*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A70-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A70-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O70" s="12" t="n">
-        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A70-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A70-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A70-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P70" s="12" t="n">
@@ -9600,7 +9604,7 @@
         <v>-0</v>
       </c>
       <c r="Q70" s="12" t="n">
-        <f aca="false">IF(DAY(B70)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B70)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R70" s="12" t="n">
@@ -9609,7 +9613,7 @@
       </c>
       <c r="S70" s="12" t="n">
         <f aca="false">S69+R70</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T70" s="15" t="n">
         <f aca="false">IF(AND($A70&gt;$B$100,S70&gt;=0),1,0)</f>
@@ -9617,7 +9621,7 @@
       </c>
       <c r="U70" s="12" t="n">
         <f aca="false">S70-SUM($E$5:E70)-(1+Premissas!$B$14)*SUM($C$5:C70)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V70" s="12" t="n">
         <f aca="false">C70/Premissas!$B$15*Premissas!$B$17+(G70+H70)*Premissas!$B$18</f>
@@ -9661,19 +9665,19 @@
         <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <f aca="false">-G71*Premissas!$B$56*Unitário!$B$22-IF($A71-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A71-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <f aca="false">IF($A71-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A71-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
-        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L71" s="12" t="n">
-        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A71-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M71" s="12" t="n">
@@ -9681,11 +9685,11 @@
         <v>0</v>
       </c>
       <c r="N71" s="12" t="n">
-        <f aca="false">-H71*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A71-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A71-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O71" s="12" t="n">
-        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A71-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A71-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A71-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -9693,7 +9697,7 @@
         <v>-0</v>
       </c>
       <c r="Q71" s="12" t="n">
-        <f aca="false">IF(DAY(B71)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B71)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R71" s="12" t="n">
@@ -9702,7 +9706,7 @@
       </c>
       <c r="S71" s="12" t="n">
         <f aca="false">S70+R71</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T71" s="15" t="n">
         <f aca="false">IF(AND($A71&gt;$B$100,S71&gt;=0),1,0)</f>
@@ -9710,7 +9714,7 @@
       </c>
       <c r="U71" s="12" t="n">
         <f aca="false">S71-SUM($E$5:E71)-(1+Premissas!$B$14)*SUM($C$5:C71)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V71" s="12" t="n">
         <f aca="false">C71/Premissas!$B$15*Premissas!$B$17+(G71+H71)*Premissas!$B$18</f>
@@ -9754,19 +9758,19 @@
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <f aca="false">-G72*Premissas!$B$56*Unitário!$B$22-IF($A72-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A72-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <f aca="false">IF($A72-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A72-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
-        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L72" s="12" t="n">
-        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A72-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M72" s="12" t="n">
@@ -9774,11 +9778,11 @@
         <v>0</v>
       </c>
       <c r="N72" s="12" t="n">
-        <f aca="false">-H72*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A72-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A72-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O72" s="12" t="n">
-        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A72-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A72-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A72-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P72" s="12" t="n">
@@ -9786,7 +9790,7 @@
         <v>-0</v>
       </c>
       <c r="Q72" s="12" t="n">
-        <f aca="false">IF(DAY(B72)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B72)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R72" s="12" t="n">
@@ -9795,7 +9799,7 @@
       </c>
       <c r="S72" s="12" t="n">
         <f aca="false">S71+R72</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T72" s="15" t="n">
         <f aca="false">IF(AND($A72&gt;$B$100,S72&gt;=0),1,0)</f>
@@ -9803,7 +9807,7 @@
       </c>
       <c r="U72" s="12" t="n">
         <f aca="false">S72-SUM($E$5:E72)-(1+Premissas!$B$14)*SUM($C$5:C72)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">C72/Premissas!$B$15*Premissas!$B$17+(G72+H72)*Premissas!$B$18</f>
@@ -9847,19 +9851,19 @@
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <f aca="false">-G73*Premissas!$B$56*Unitário!$B$22-IF($A73-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A73-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <f aca="false">IF($A73-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A73-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A73-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
@@ -9867,11 +9871,11 @@
         <v>0</v>
       </c>
       <c r="N73" s="12" t="n">
-        <f aca="false">-H73*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A73-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A73-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O73" s="12" t="n">
-        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A73-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A73-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A73-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -9879,7 +9883,7 @@
         <v>-0</v>
       </c>
       <c r="Q73" s="12" t="n">
-        <f aca="false">IF(DAY(B73)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B73)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R73" s="12" t="n">
@@ -9888,7 +9892,7 @@
       </c>
       <c r="S73" s="12" t="n">
         <f aca="false">S72+R73</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T73" s="15" t="n">
         <f aca="false">IF(AND($A73&gt;$B$100,S73&gt;=0),1,0)</f>
@@ -9896,7 +9900,7 @@
       </c>
       <c r="U73" s="12" t="n">
         <f aca="false">S73-SUM($E$5:E73)-(1+Premissas!$B$14)*SUM($C$5:C73)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">C73/Premissas!$B$15*Premissas!$B$17+(G73+H73)*Premissas!$B$18</f>
@@ -9940,19 +9944,19 @@
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <f aca="false">-G74*Premissas!$B$56*Unitário!$B$22-IF($A74-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A74-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <f aca="false">IF($A74-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A74-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
-        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A74-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
@@ -9960,11 +9964,11 @@
         <v>0</v>
       </c>
       <c r="N74" s="12" t="n">
-        <f aca="false">-H74*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A74-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A74-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O74" s="12" t="n">
-        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A74-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A74-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A74-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P74" s="12" t="n">
@@ -9972,7 +9976,7 @@
         <v>-0</v>
       </c>
       <c r="Q74" s="12" t="n">
-        <f aca="false">IF(DAY(B74)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B74)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R74" s="12" t="n">
@@ -9981,7 +9985,7 @@
       </c>
       <c r="S74" s="12" t="n">
         <f aca="false">S73+R74</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="T74" s="15" t="n">
         <f aca="false">IF(AND($A74&gt;$B$100,S74&gt;=0),1,0)</f>
@@ -9989,7 +9993,7 @@
       </c>
       <c r="U74" s="12" t="n">
         <f aca="false">S74-SUM($E$5:E74)-(1+Premissas!$B$14)*SUM($C$5:C74)</f>
-        <v>1225.2188128</v>
+        <v>990.8047813</v>
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">C74/Premissas!$B$15*Premissas!$B$17+(G74+H74)*Premissas!$B$18</f>
@@ -10033,19 +10037,19 @@
         <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <f aca="false">-G75*Premissas!$B$56*Unitário!$B$22-IF($A75-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A75-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <f aca="false">IF($A75-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A75-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K75" s="12" t="n">
-        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L75" s="12" t="n">
-        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A75-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
@@ -10053,11 +10057,11 @@
         <v>0</v>
       </c>
       <c r="N75" s="12" t="n">
-        <f aca="false">-H75*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A75-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A75-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O75" s="12" t="n">
-        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A75-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A75-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A75-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -10065,7 +10069,7 @@
         <v>-0</v>
       </c>
       <c r="Q75" s="12" t="n">
-        <f aca="false">IF(DAY(B75)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B75)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>-57.49</v>
       </c>
       <c r="R75" s="12" t="n">
@@ -10074,7 +10078,7 @@
       </c>
       <c r="S75" s="12" t="n">
         <f aca="false">S74+R75</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T75" s="15" t="n">
         <f aca="false">IF(AND($A75&gt;$B$100,S75&gt;=0),1,0)</f>
@@ -10082,7 +10086,7 @@
       </c>
       <c r="U75" s="12" t="n">
         <f aca="false">S75-SUM($E$5:E75)-(1+Premissas!$B$14)*SUM($C$5:C75)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V75" s="12" t="n">
         <f aca="false">C75/Premissas!$B$15*Premissas!$B$17+(G75+H75)*Premissas!$B$18</f>
@@ -10126,19 +10130,19 @@
         <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <f aca="false">-G76*Premissas!$B$56*Unitário!$B$22-IF($A76-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A76-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <f aca="false">IF($A76-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A76-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
-        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A76-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M76" s="12" t="n">
@@ -10146,11 +10150,11 @@
         <v>0</v>
       </c>
       <c r="N76" s="12" t="n">
-        <f aca="false">-H76*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A76-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A76-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O76" s="12" t="n">
-        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A76-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A76-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A76-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P76" s="12" t="n">
@@ -10158,7 +10162,7 @@
         <v>-0</v>
       </c>
       <c r="Q76" s="12" t="n">
-        <f aca="false">IF(DAY(B76)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B76)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R76" s="12" t="n">
@@ -10167,7 +10171,7 @@
       </c>
       <c r="S76" s="12" t="n">
         <f aca="false">S75+R76</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T76" s="15" t="n">
         <f aca="false">IF(AND($A76&gt;$B$100,S76&gt;=0),1,0)</f>
@@ -10175,7 +10179,7 @@
       </c>
       <c r="U76" s="12" t="n">
         <f aca="false">S76-SUM($E$5:E76)-(1+Premissas!$B$14)*SUM($C$5:C76)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V76" s="12" t="n">
         <f aca="false">C76/Premissas!$B$15*Premissas!$B$17+(G76+H76)*Premissas!$B$18</f>
@@ -10219,19 +10223,19 @@
         <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <f aca="false">-G77*Premissas!$B$56*Unitário!$B$22-IF($A77-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A77-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <f aca="false">IF($A77-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A77-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K77" s="12" t="n">
-        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A77-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M77" s="12" t="n">
@@ -10239,11 +10243,11 @@
         <v>0</v>
       </c>
       <c r="N77" s="12" t="n">
-        <f aca="false">-H77*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A77-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A77-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O77" s="12" t="n">
-        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A77-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A77-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A77-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -10251,7 +10255,7 @@
         <v>-0</v>
       </c>
       <c r="Q77" s="12" t="n">
-        <f aca="false">IF(DAY(B77)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B77)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R77" s="12" t="n">
@@ -10260,7 +10264,7 @@
       </c>
       <c r="S77" s="12" t="n">
         <f aca="false">S76+R77</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T77" s="15" t="n">
         <f aca="false">IF(AND($A77&gt;$B$100,S77&gt;=0),1,0)</f>
@@ -10268,7 +10272,7 @@
       </c>
       <c r="U77" s="12" t="n">
         <f aca="false">S77-SUM($E$5:E77)-(1+Premissas!$B$14)*SUM($C$5:C77)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V77" s="12" t="n">
         <f aca="false">C77/Premissas!$B$15*Premissas!$B$17+(G77+H77)*Premissas!$B$18</f>
@@ -10312,19 +10316,19 @@
         <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <f aca="false">-G78*Premissas!$B$56*Unitário!$B$22-IF($A78-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A78-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <f aca="false">IF($A78-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A78-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K78" s="12" t="n">
-        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A78-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M78" s="12" t="n">
@@ -10332,11 +10336,11 @@
         <v>0</v>
       </c>
       <c r="N78" s="12" t="n">
-        <f aca="false">-H78*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A78-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A78-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O78" s="12" t="n">
-        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A78-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A78-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A78-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P78" s="12" t="n">
@@ -10344,7 +10348,7 @@
         <v>-0</v>
       </c>
       <c r="Q78" s="12" t="n">
-        <f aca="false">IF(DAY(B78)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B78)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R78" s="12" t="n">
@@ -10353,7 +10357,7 @@
       </c>
       <c r="S78" s="12" t="n">
         <f aca="false">S77+R78</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T78" s="15" t="n">
         <f aca="false">IF(AND($A78&gt;$B$100,S78&gt;=0),1,0)</f>
@@ -10361,7 +10365,7 @@
       </c>
       <c r="U78" s="12" t="n">
         <f aca="false">S78-SUM($E$5:E78)-(1+Premissas!$B$14)*SUM($C$5:C78)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V78" s="12" t="n">
         <f aca="false">C78/Premissas!$B$15*Premissas!$B$17+(G78+H78)*Premissas!$B$18</f>
@@ -10405,19 +10409,19 @@
         <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <f aca="false">-G79*Premissas!$B$56*Unitário!$B$22-IF($A79-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A79-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <f aca="false">IF($A79-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A79-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
-        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A79-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M79" s="12" t="n">
@@ -10425,11 +10429,11 @@
         <v>0</v>
       </c>
       <c r="N79" s="12" t="n">
-        <f aca="false">-H79*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A79-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A79-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O79" s="12" t="n">
-        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A79-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A79-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A79-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -10437,7 +10441,7 @@
         <v>-0</v>
       </c>
       <c r="Q79" s="12" t="n">
-        <f aca="false">IF(DAY(B79)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B79)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R79" s="12" t="n">
@@ -10446,7 +10450,7 @@
       </c>
       <c r="S79" s="12" t="n">
         <f aca="false">S78+R79</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T79" s="15" t="n">
         <f aca="false">IF(AND($A79&gt;$B$100,S79&gt;=0),1,0)</f>
@@ -10454,7 +10458,7 @@
       </c>
       <c r="U79" s="12" t="n">
         <f aca="false">S79-SUM($E$5:E79)-(1+Premissas!$B$14)*SUM($C$5:C79)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V79" s="12" t="n">
         <f aca="false">C79/Premissas!$B$15*Premissas!$B$17+(G79+H79)*Premissas!$B$18</f>
@@ -10498,19 +10502,19 @@
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <f aca="false">-G80*Premissas!$B$56*Unitário!$B$22-IF($A80-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A80-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <f aca="false">IF($A80-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A80-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
-        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A80-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M80" s="12" t="n">
@@ -10518,11 +10522,11 @@
         <v>0</v>
       </c>
       <c r="N80" s="12" t="n">
-        <f aca="false">-H80*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A80-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A80-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O80" s="12" t="n">
-        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A80-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A80-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A80-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P80" s="12" t="n">
@@ -10530,7 +10534,7 @@
         <v>-0</v>
       </c>
       <c r="Q80" s="12" t="n">
-        <f aca="false">IF(DAY(B80)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B80)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R80" s="12" t="n">
@@ -10539,7 +10543,7 @@
       </c>
       <c r="S80" s="12" t="n">
         <f aca="false">S79+R80</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T80" s="15" t="n">
         <f aca="false">IF(AND($A80&gt;$B$100,S80&gt;=0),1,0)</f>
@@ -10547,7 +10551,7 @@
       </c>
       <c r="U80" s="12" t="n">
         <f aca="false">S80-SUM($E$5:E80)-(1+Premissas!$B$14)*SUM($C$5:C80)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V80" s="12" t="n">
         <f aca="false">C80/Premissas!$B$15*Premissas!$B$17+(G80+H80)*Premissas!$B$18</f>
@@ -10591,19 +10595,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <f aca="false">-G81*Premissas!$B$56*Unitário!$B$22-IF($A81-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A81-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <f aca="false">IF($A81-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A81-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
-        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A81-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
@@ -10611,11 +10615,11 @@
         <v>0</v>
       </c>
       <c r="N81" s="12" t="n">
-        <f aca="false">-H81*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A81-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A81-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O81" s="12" t="n">
-        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A81-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A81-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A81-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -10623,7 +10627,7 @@
         <v>-0</v>
       </c>
       <c r="Q81" s="12" t="n">
-        <f aca="false">IF(DAY(B81)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B81)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R81" s="12" t="n">
@@ -10632,7 +10636,7 @@
       </c>
       <c r="S81" s="12" t="n">
         <f aca="false">S80+R81</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T81" s="15" t="n">
         <f aca="false">IF(AND($A81&gt;$B$100,S81&gt;=0),1,0)</f>
@@ -10640,7 +10644,7 @@
       </c>
       <c r="U81" s="12" t="n">
         <f aca="false">S81-SUM($E$5:E81)-(1+Premissas!$B$14)*SUM($C$5:C81)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V81" s="12" t="n">
         <f aca="false">C81/Premissas!$B$15*Premissas!$B$17+(G81+H81)*Premissas!$B$18</f>
@@ -10684,19 +10688,19 @@
         <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <f aca="false">-G82*Premissas!$B$56*Unitário!$B$22-IF($A82-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A82-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J82" s="12" t="n">
-        <f aca="false">IF($A82-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A82-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K82" s="12" t="n">
-        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A82-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
@@ -10704,11 +10708,11 @@
         <v>0</v>
       </c>
       <c r="N82" s="12" t="n">
-        <f aca="false">-H82*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A82-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A82-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O82" s="12" t="n">
-        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A82-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A82-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A82-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P82" s="12" t="n">
@@ -10716,7 +10720,7 @@
         <v>-0</v>
       </c>
       <c r="Q82" s="12" t="n">
-        <f aca="false">IF(DAY(B82)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B82)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R82" s="12" t="n">
@@ -10725,7 +10729,7 @@
       </c>
       <c r="S82" s="12" t="n">
         <f aca="false">S81+R82</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T82" s="15" t="n">
         <f aca="false">IF(AND($A82&gt;$B$100,S82&gt;=0),1,0)</f>
@@ -10733,7 +10737,7 @@
       </c>
       <c r="U82" s="12" t="n">
         <f aca="false">S82-SUM($E$5:E82)-(1+Premissas!$B$14)*SUM($C$5:C82)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V82" s="12" t="n">
         <f aca="false">C82/Premissas!$B$15*Premissas!$B$17+(G82+H82)*Premissas!$B$18</f>
@@ -10777,19 +10781,19 @@
         <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <f aca="false">-G83*Premissas!$B$56*Unitário!$B$22-IF($A83-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A83-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <f aca="false">IF($A83-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A83-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K83" s="12" t="n">
-        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A83-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
@@ -10797,11 +10801,11 @@
         <v>0</v>
       </c>
       <c r="N83" s="12" t="n">
-        <f aca="false">-H83*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A83-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A83-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O83" s="12" t="n">
-        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A83-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A83-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A83-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -10809,7 +10813,7 @@
         <v>-0</v>
       </c>
       <c r="Q83" s="12" t="n">
-        <f aca="false">IF(DAY(B83)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B83)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R83" s="12" t="n">
@@ -10818,7 +10822,7 @@
       </c>
       <c r="S83" s="12" t="n">
         <f aca="false">S82+R83</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T83" s="15" t="n">
         <f aca="false">IF(AND($A83&gt;$B$100,S83&gt;=0),1,0)</f>
@@ -10826,7 +10830,7 @@
       </c>
       <c r="U83" s="12" t="n">
         <f aca="false">S83-SUM($E$5:E83)-(1+Premissas!$B$14)*SUM($C$5:C83)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V83" s="12" t="n">
         <f aca="false">C83/Premissas!$B$15*Premissas!$B$17+(G83+H83)*Premissas!$B$18</f>
@@ -10870,19 +10874,19 @@
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <f aca="false">-G84*Premissas!$B$56*Unitário!$B$22-IF($A84-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A84-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <f aca="false">IF($A84-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A84-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K84" s="12" t="n">
-        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A84-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
@@ -10890,11 +10894,11 @@
         <v>0</v>
       </c>
       <c r="N84" s="12" t="n">
-        <f aca="false">-H84*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A84-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A84-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O84" s="12" t="n">
-        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A84-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A84-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A84-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P84" s="12" t="n">
@@ -10902,7 +10906,7 @@
         <v>-0</v>
       </c>
       <c r="Q84" s="12" t="n">
-        <f aca="false">IF(DAY(B84)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B84)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R84" s="12" t="n">
@@ -10911,7 +10915,7 @@
       </c>
       <c r="S84" s="12" t="n">
         <f aca="false">S83+R84</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T84" s="15" t="n">
         <f aca="false">IF(AND($A84&gt;$B$100,S84&gt;=0),1,0)</f>
@@ -10919,7 +10923,7 @@
       </c>
       <c r="U84" s="12" t="n">
         <f aca="false">S84-SUM($E$5:E84)-(1+Premissas!$B$14)*SUM($C$5:C84)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V84" s="12" t="n">
         <f aca="false">C84/Premissas!$B$15*Premissas!$B$17+(G84+H84)*Premissas!$B$18</f>
@@ -10963,19 +10967,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
-        <f aca="false">-G85*Premissas!$B$56*Unitário!$B$22-IF($A85-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A85-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <f aca="false">IF($A85-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A85-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K85" s="12" t="n">
-        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A85-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M85" s="12" t="n">
@@ -10983,11 +10987,11 @@
         <v>0</v>
       </c>
       <c r="N85" s="12" t="n">
-        <f aca="false">-H85*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A85-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A85-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O85" s="12" t="n">
-        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A85-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A85-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A85-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -10995,7 +10999,7 @@
         <v>-0</v>
       </c>
       <c r="Q85" s="12" t="n">
-        <f aca="false">IF(DAY(B85)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B85)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R85" s="12" t="n">
@@ -11004,7 +11008,7 @@
       </c>
       <c r="S85" s="12" t="n">
         <f aca="false">S84+R85</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T85" s="15" t="n">
         <f aca="false">IF(AND($A85&gt;$B$100,S85&gt;=0),1,0)</f>
@@ -11012,7 +11016,7 @@
       </c>
       <c r="U85" s="12" t="n">
         <f aca="false">S85-SUM($E$5:E85)-(1+Premissas!$B$14)*SUM($C$5:C85)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V85" s="12" t="n">
         <f aca="false">C85/Premissas!$B$15*Premissas!$B$17+(G85+H85)*Premissas!$B$18</f>
@@ -11056,19 +11060,19 @@
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <f aca="false">-G86*Premissas!$B$56*Unitário!$B$22-IF($A86-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A86-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <f aca="false">IF($A86-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A86-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K86" s="12" t="n">
-        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A86-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M86" s="12" t="n">
@@ -11076,11 +11080,11 @@
         <v>0</v>
       </c>
       <c r="N86" s="12" t="n">
-        <f aca="false">-H86*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A86-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A86-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O86" s="12" t="n">
-        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A86-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A86-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A86-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P86" s="12" t="n">
@@ -11088,7 +11092,7 @@
         <v>-0</v>
       </c>
       <c r="Q86" s="12" t="n">
-        <f aca="false">IF(DAY(B86)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B86)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R86" s="12" t="n">
@@ -11097,7 +11101,7 @@
       </c>
       <c r="S86" s="12" t="n">
         <f aca="false">S85+R86</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T86" s="15" t="n">
         <f aca="false">IF(AND($A86&gt;$B$100,S86&gt;=0),1,0)</f>
@@ -11105,7 +11109,7 @@
       </c>
       <c r="U86" s="12" t="n">
         <f aca="false">S86-SUM($E$5:E86)-(1+Premissas!$B$14)*SUM($C$5:C86)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V86" s="12" t="n">
         <f aca="false">C86/Premissas!$B$15*Premissas!$B$17+(G86+H86)*Premissas!$B$18</f>
@@ -11149,19 +11153,19 @@
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <f aca="false">-G87*Premissas!$B$56*Unitário!$B$22-IF($A87-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A87-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <f aca="false">IF($A87-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A87-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K87" s="12" t="n">
-        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A87-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M87" s="12" t="n">
@@ -11169,11 +11173,11 @@
         <v>0</v>
       </c>
       <c r="N87" s="12" t="n">
-        <f aca="false">-H87*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A87-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A87-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O87" s="12" t="n">
-        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A87-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A87-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A87-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -11181,7 +11185,7 @@
         <v>-0</v>
       </c>
       <c r="Q87" s="12" t="n">
-        <f aca="false">IF(DAY(B87)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B87)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R87" s="12" t="n">
@@ -11190,7 +11194,7 @@
       </c>
       <c r="S87" s="12" t="n">
         <f aca="false">S86+R87</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T87" s="15" t="n">
         <f aca="false">IF(AND($A87&gt;$B$100,S87&gt;=0),1,0)</f>
@@ -11198,7 +11202,7 @@
       </c>
       <c r="U87" s="12" t="n">
         <f aca="false">S87-SUM($E$5:E87)-(1+Premissas!$B$14)*SUM($C$5:C87)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V87" s="12" t="n">
         <f aca="false">C87/Premissas!$B$15*Premissas!$B$17+(G87+H87)*Premissas!$B$18</f>
@@ -11242,19 +11246,19 @@
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <f aca="false">-G88*Premissas!$B$56*Unitário!$B$22-IF($A88-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A88-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <f aca="false">IF($A88-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A88-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K88" s="12" t="n">
-        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A88-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
@@ -11262,11 +11266,11 @@
         <v>0</v>
       </c>
       <c r="N88" s="12" t="n">
-        <f aca="false">-H88*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A88-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A88-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O88" s="12" t="n">
-        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A88-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A88-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A88-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P88" s="12" t="n">
@@ -11274,7 +11278,7 @@
         <v>-0</v>
       </c>
       <c r="Q88" s="12" t="n">
-        <f aca="false">IF(DAY(B88)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B88)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R88" s="12" t="n">
@@ -11283,7 +11287,7 @@
       </c>
       <c r="S88" s="12" t="n">
         <f aca="false">S87+R88</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T88" s="15" t="n">
         <f aca="false">IF(AND($A88&gt;$B$100,S88&gt;=0),1,0)</f>
@@ -11291,7 +11295,7 @@
       </c>
       <c r="U88" s="12" t="n">
         <f aca="false">S88-SUM($E$5:E88)-(1+Premissas!$B$14)*SUM($C$5:C88)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V88" s="12" t="n">
         <f aca="false">C88/Premissas!$B$15*Premissas!$B$17+(G88+H88)*Premissas!$B$18</f>
@@ -11335,19 +11339,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <f aca="false">-G89*Premissas!$B$56*Unitário!$B$22-IF($A89-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A89-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <f aca="false">IF($A89-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A89-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K89" s="12" t="n">
-        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A89-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
@@ -11355,11 +11359,11 @@
         <v>0</v>
       </c>
       <c r="N89" s="12" t="n">
-        <f aca="false">-H89*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A89-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A89-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O89" s="12" t="n">
-        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A89-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A89-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A89-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -11367,7 +11371,7 @@
         <v>-0</v>
       </c>
       <c r="Q89" s="12" t="n">
-        <f aca="false">IF(DAY(B89)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B89)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R89" s="12" t="n">
@@ -11376,7 +11380,7 @@
       </c>
       <c r="S89" s="12" t="n">
         <f aca="false">S88+R89</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T89" s="15" t="n">
         <f aca="false">IF(AND($A89&gt;$B$100,S89&gt;=0),1,0)</f>
@@ -11384,7 +11388,7 @@
       </c>
       <c r="U89" s="12" t="n">
         <f aca="false">S89-SUM($E$5:E89)-(1+Premissas!$B$14)*SUM($C$5:C89)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V89" s="12" t="n">
         <f aca="false">C89/Premissas!$B$15*Premissas!$B$17+(G89+H89)*Premissas!$B$18</f>
@@ -11428,19 +11432,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <f aca="false">-G90*Premissas!$B$56*Unitário!$B$22-IF($A90-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A90-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J90" s="12" t="n">
-        <f aca="false">IF($A90-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A90-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K90" s="12" t="n">
-        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A90-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M90" s="12" t="n">
@@ -11448,11 +11452,11 @@
         <v>0</v>
       </c>
       <c r="N90" s="12" t="n">
-        <f aca="false">-H90*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A90-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A90-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O90" s="12" t="n">
-        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A90-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A90-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A90-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P90" s="12" t="n">
@@ -11460,7 +11464,7 @@
         <v>-0</v>
       </c>
       <c r="Q90" s="12" t="n">
-        <f aca="false">IF(DAY(B90)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B90)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R90" s="12" t="n">
@@ -11469,7 +11473,7 @@
       </c>
       <c r="S90" s="12" t="n">
         <f aca="false">S89+R90</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T90" s="15" t="n">
         <f aca="false">IF(AND($A90&gt;$B$100,S90&gt;=0),1,0)</f>
@@ -11477,7 +11481,7 @@
       </c>
       <c r="U90" s="12" t="n">
         <f aca="false">S90-SUM($E$5:E90)-(1+Premissas!$B$14)*SUM($C$5:C90)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V90" s="12" t="n">
         <f aca="false">C90/Premissas!$B$15*Premissas!$B$17+(G90+H90)*Premissas!$B$18</f>
@@ -11521,19 +11525,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <f aca="false">-G91*Premissas!$B$56*Unitário!$B$22-IF($A91-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A91-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J91" s="12" t="n">
-        <f aca="false">IF($A91-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A91-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K91" s="12" t="n">
-        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A91-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M91" s="12" t="n">
@@ -11541,11 +11545,11 @@
         <v>0</v>
       </c>
       <c r="N91" s="12" t="n">
-        <f aca="false">-H91*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A91-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A91-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O91" s="12" t="n">
-        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A91-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A91-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A91-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -11553,7 +11557,7 @@
         <v>-0</v>
       </c>
       <c r="Q91" s="12" t="n">
-        <f aca="false">IF(DAY(B91)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B91)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R91" s="12" t="n">
@@ -11562,7 +11566,7 @@
       </c>
       <c r="S91" s="12" t="n">
         <f aca="false">S90+R91</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T91" s="15" t="n">
         <f aca="false">IF(AND($A91&gt;$B$100,S91&gt;=0),1,0)</f>
@@ -11570,7 +11574,7 @@
       </c>
       <c r="U91" s="12" t="n">
         <f aca="false">S91-SUM($E$5:E91)-(1+Premissas!$B$14)*SUM($C$5:C91)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V91" s="12" t="n">
         <f aca="false">C91/Premissas!$B$15*Premissas!$B$17+(G91+H91)*Premissas!$B$18</f>
@@ -11614,19 +11618,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <f aca="false">-G92*Premissas!$B$56*Unitário!$B$22-IF($A92-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A92-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <f aca="false">IF($A92-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A92-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K92" s="12" t="n">
-        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A92-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M92" s="12" t="n">
@@ -11634,11 +11638,11 @@
         <v>0</v>
       </c>
       <c r="N92" s="12" t="n">
-        <f aca="false">-H92*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A92-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A92-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O92" s="12" t="n">
-        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A92-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A92-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A92-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P92" s="12" t="n">
@@ -11646,7 +11650,7 @@
         <v>-0</v>
       </c>
       <c r="Q92" s="12" t="n">
-        <f aca="false">IF(DAY(B92)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B92)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R92" s="12" t="n">
@@ -11655,7 +11659,7 @@
       </c>
       <c r="S92" s="12" t="n">
         <f aca="false">S91+R92</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T92" s="15" t="n">
         <f aca="false">IF(AND($A92&gt;$B$100,S92&gt;=0),1,0)</f>
@@ -11663,7 +11667,7 @@
       </c>
       <c r="U92" s="12" t="n">
         <f aca="false">S92-SUM($E$5:E92)-(1+Premissas!$B$14)*SUM($C$5:C92)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V92" s="12" t="n">
         <f aca="false">C92/Premissas!$B$15*Premissas!$B$17+(G92+H92)*Premissas!$B$18</f>
@@ -11707,19 +11711,19 @@
         <v>0</v>
       </c>
       <c r="I93" s="12" t="n">
-        <f aca="false">-G93*Premissas!$B$56*Unitário!$B$22-IF($A93-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A93-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J93" s="12" t="n">
-        <f aca="false">IF($A93-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A93-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K93" s="12" t="n">
-        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A93-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M93" s="12" t="n">
@@ -11727,11 +11731,11 @@
         <v>0</v>
       </c>
       <c r="N93" s="12" t="n">
-        <f aca="false">-H93*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A93-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A93-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O93" s="12" t="n">
-        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A93-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A93-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A93-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -11739,7 +11743,7 @@
         <v>-0</v>
       </c>
       <c r="Q93" s="12" t="n">
-        <f aca="false">IF(DAY(B93)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B93)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R93" s="12" t="n">
@@ -11748,7 +11752,7 @@
       </c>
       <c r="S93" s="12" t="n">
         <f aca="false">S92+R93</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T93" s="15" t="n">
         <f aca="false">IF(AND($A93&gt;$B$100,S93&gt;=0),1,0)</f>
@@ -11756,7 +11760,7 @@
       </c>
       <c r="U93" s="12" t="n">
         <f aca="false">S93-SUM($E$5:E93)-(1+Premissas!$B$14)*SUM($C$5:C93)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V93" s="12" t="n">
         <f aca="false">C93/Premissas!$B$15*Premissas!$B$17+(G93+H93)*Premissas!$B$18</f>
@@ -11800,19 +11804,19 @@
         <v>0</v>
       </c>
       <c r="I94" s="12" t="n">
-        <f aca="false">-G94*Premissas!$B$56*Unitário!$B$22-IF($A94-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$57)),0)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25)</f>
+        <f aca="false">-IF($A94-(Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))</f>
         <v>-0</v>
       </c>
       <c r="J94" s="12" t="n">
-        <f aca="false">IF($A94-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$36)</f>
+        <f aca="false">IF($A94-(Premissas!$B$51)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51)),0)*Premissas!$B$23*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25))-Premissas!$B$36)</f>
         <v>0</v>
       </c>
       <c r="K94" s="12" t="n">
-        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*((Premissas!$B$56*Unitário!$B$22+(Premissas!$B$58*Unitário!$B$24+Premissas!$B$59*Unitário!$B$25))-Premissas!$B$38)</f>
-        <v>0</v>
+        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(Premissas!$B$56*Unitário!$B$22+(1-Premissas!$B$59)*(Premissas!$B$58*Unitário!$B$24+Premissas!$B$60*Unitário!$B$25)-Premissas!$B$59*((1-Premissas!$B$58)*Unitário!$B$24+(1-Premissas!$B$60)*Unitário!$B$25)-Premissas!$B$38)</f>
+        <v>-0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$59)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
+        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$52)&gt;=1,INDEX($G$5:$G$94,$A94-(Premissas!$B$51+Premissas!$B$52)),0)*Unitário!$B$21*(Premissas!$B$48-(1-Premissas!$B$58)*Unitário!$B$24-(1-Premissas!$B$60)*Unitário!$B$25-(1-Premissas!$B$56)*Unitário!$B$22)</f>
         <v>0</v>
       </c>
       <c r="M94" s="12" t="n">
@@ -11820,11 +11824,11 @@
         <v>0</v>
       </c>
       <c r="N94" s="12" t="n">
-        <f aca="false">-H94*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
+        <f aca="false">-IF($A94-(Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A94-(Premissas!$B$57)),0)*(Premissas!$B$56*Unitário!$B$22+Premissas!$B$28)</f>
         <v>-0</v>
       </c>
       <c r="O94" s="12" t="n">
-        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A94-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
+        <f aca="false">IF($A94-(Premissas!$B$51+Premissas!$B$54)&gt;=1,INDEX($H$5:$H$94,$A94-(Premissas!$B$51+Premissas!$B$54)),0)*Premissas!$B$24*(-Premissas!$B$49-Premissas!$B$38+(1-Premissas!$B$59)*Premissas!$B$28+Premissas!$B$56*Unitário!$B$22)</f>
         <v>-0</v>
       </c>
       <c r="P94" s="12" t="n">
@@ -11832,7 +11836,7 @@
         <v>-0</v>
       </c>
       <c r="Q94" s="12" t="n">
-        <f aca="false">IF(DAY(B94)=1,-(Premissas!$B$40+Premissas!$B$63*Premissas!$B$64),0)</f>
+        <f aca="false">IF(DAY(B94)=1,-(Premissas!$B$40+Premissas!$B$64*Premissas!$B$65),0)</f>
         <v>0</v>
       </c>
       <c r="R94" s="12" t="n">
@@ -11841,7 +11845,7 @@
       </c>
       <c r="S94" s="12" t="n">
         <f aca="false">S93+R94</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="T94" s="15" t="n">
         <f aca="false">IF(AND($A94&gt;$B$100,S94&gt;=0),1,0)</f>
@@ -11849,7 +11853,7 @@
       </c>
       <c r="U94" s="12" t="n">
         <f aca="false">S94-SUM($E$5:E94)-(1+Premissas!$B$14)*SUM($C$5:C94)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
       <c r="V94" s="12" t="n">
         <f aca="false">C94/Premissas!$B$15*Premissas!$B$17+(G94+H94)*Premissas!$B$18</f>
@@ -11862,7 +11866,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C95" s="14" t="n">
         <f aca="false">SUM(C5:C94)</f>
@@ -11894,7 +11898,7 @@
       </c>
       <c r="K95" s="14" t="n">
         <f aca="false">SUM(K5:K94)</f>
-        <v>130.9140315</v>
+        <v>-63</v>
       </c>
       <c r="L95" s="14" t="n">
         <f aca="false">SUM(L5:L94)</f>
@@ -11910,7 +11914,7 @@
       </c>
       <c r="O95" s="14" t="n">
         <f aca="false">SUM(O5:O94)</f>
-        <v>-144.3285</v>
+        <v>-184.8285</v>
       </c>
       <c r="P95" s="14" t="n">
         <f aca="false">SUM(P5:P94)</f>
@@ -11922,34 +11926,34 @@
       </c>
       <c r="R95" s="14" t="n">
         <f aca="false">SUM(R5:R94)</f>
-        <v>1167.7288128</v>
+        <v>933.3147813</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">MIN(S5:S94)</f>
-        <v>-922.58402946</v>
+        <v>-1027.3772187</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B100" s="32" t="n">
         <f aca="false">INDEX(A5:A94,MATCH(B99,S5:S94,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B101" s="32" t="n">
         <f aca="false">IFERROR(INDEX(A5:A94,MATCH(1,T5:T94,0)),"não volta em 90 dias")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11958,7 +11962,7 @@
       </c>
       <c r="B102" s="14" t="n">
         <f aca="false">MIN(U5:U94)</f>
-        <v>-1690.93652946</v>
+        <v>-1795.7297187</v>
       </c>
     </row>
   </sheetData>
@@ -11977,7 +11981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -11989,38 +11993,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E4" s="34"/>
     </row>
@@ -12029,13 +12033,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E5" s="34"/>
     </row>
@@ -12044,13 +12048,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E6" s="34"/>
     </row>
@@ -12059,13 +12063,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" s="34"/>
     </row>
@@ -12074,28 +12078,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E8" s="34"/>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E9" s="34"/>
     </row>
@@ -12104,60 +12108,30 @@
         <v>7</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="E12" s="34"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="E13" s="34"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12187,7 +12161,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12195,50 +12169,50 @@
         <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>275</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B5" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>279</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12246,220 +12220,220 @@
         <v>108</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>283</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>290</v>
-      </c>
       <c r="E7" s="33" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="B8" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>294</v>
-      </c>
       <c r="E8" s="33" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="E9" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="C10" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
+      <c r="D10" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="E10" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="C10" s="33" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="B11" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="C11" s="33" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
+      <c r="D11" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="E11" s="33" t="s">
         <v>305</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="D12" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="E12" s="33" t="s">
         <v>310</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="E13" s="33" t="s">
         <v>315</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="B14" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>322</v>
-      </c>
       <c r="E14" s="33" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="33" t="s">
         <v>323</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="E16" s="33" t="s">
         <v>328</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>335</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -12478,7 +12452,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -12492,97 +12466,97 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C5" s="35" t="n">
         <f aca="false">Premissas!$B$26*Premissas!$B$47</f>
         <v>30</v>
       </c>
       <c r="D5" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="G5" s="33" t="s">
         <v>348</v>
       </c>
-      <c r="E5" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>350</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>351</v>
-      </c>
       <c r="H5" s="33" t="s">
-        <v>352</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">Premissas!$B$27</f>
         <v>19.99</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>108</v>
@@ -12592,70 +12566,70 @@
         <v>5</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E7" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G7" s="33" t="s">
         <v>354</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="H7" s="33" t="s">
         <v>355</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">Unitário!$B$25</f>
         <v>11.57001</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C9" s="35" t="n">
         <f aca="false">Premissas!$B$35</f>
         <v>4.99</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>80</v>
@@ -12663,271 +12637,298 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">Premissas!$B$36</f>
         <v>9.99</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="35" t="n">
+        <f aca="false">Premissas!$B$38+Premissas!$B$59*(Unitário!$B$24+Unitário!$B$25)</f>
+        <v>86.56001</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>374</v>
-      </c>
-      <c r="C11" s="35" t="n">
-        <f aca="false">Premissas!$B$38</f>
-        <v>25</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>375</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>376</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>377</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C12" s="35" t="n">
         <f aca="false">Premissas!$B$26*Premissas!$B$47</f>
         <v>30</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>163</v>
+        <v>346</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <f aca="false">Premissas!$B$38+Premissas!$B$59*Premissas!$B$28+Unitário!$B$27</f>
+        <v>58.9897635</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C14" s="35" t="n">
         <f aca="false">Premissas!$B$28</f>
         <v>5</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>355</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="C14" s="35" t="n">
+      <c r="D14" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="C15" s="35" t="n">
         <f aca="false">Unitário!$B$27</f>
         <v>3.9897635</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D15" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="H15" s="33" t="s">
         <v>383</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>384</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>385</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>386</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>391</v>
+        <v>178</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>392</v>
+        <v>184</v>
       </c>
       <c r="C16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <f aca="false">Premissas!$B$15/Premissas!$B$16*(1+Premissas!$B$14)</f>
         <v>17.0745</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D17" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="H17" s="33" t="s">
         <v>393</v>
       </c>
-      <c r="E16" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="C17" s="35" t="n">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <f aca="false">Premissas!$B$17/Premissas!$B$16+Premissas!$B$18</f>
         <v>2.74</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D18" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>398</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>402</v>
-      </c>
-      <c r="C18" s="35" t="n">
+      <c r="C19" s="35" t="n">
         <f aca="false">Premissas!$B$40</f>
         <v>53.5</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D19" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="C20" s="35" t="n">
+        <f aca="false">Premissas!$B$64*Premissas!$B$65</f>
+        <v>3.99</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="H20" s="33" t="s">
         <v>403</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>404</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <f aca="false">Premissas!$B$63*Premissas!$B$64</f>
-        <v>3.99</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>406</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="H19" s="33" t="s">
-        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/docs/operacao/modelo-caixa-anuncios.xlsx
+++ b/docs/operacao/modelo-caixa-anuncios.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="415">
   <si>
     <t xml:space="preserve">Resumo — caixa necessário para o teste de anúncios</t>
   </si>
@@ -122,6 +122,18 @@
   </si>
   <si>
     <t xml:space="preserve">o que o cartão realmente cobra pela verba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leads no teste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verba ÷ CPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piso de amostra (mais de 500 leads e 50 pedidos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 item 4, assinado em 02/10</t>
   </si>
   <si>
     <t xml:space="preserve">Gasto antecipado e tempo até virar caixa — por caminho</t>
@@ -1802,7 +1814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -1999,243 +2011,267 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="B19" s="5" t="n">
+        <f aca="false">B5/Premissas!$B$18</f>
+        <v>450</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="6" t="str">
+        <f aca="false">IF(AND(B19&gt;500,B6&gt;50),"passa","abaixo do piso")</f>
+        <v>abaixo do piso</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="3" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="12" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="12" t="n">
         <f aca="false">(Premissas!$B$18*(1+Premissas!$B$17)+Premissas!$B$20)/Premissas!$B$19+Premissas!$B$21</f>
         <v>19.8145</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C24" s="12" t="n">
         <f aca="false">(Premissas!$B$18*(1+Premissas!$B$17)+Premissas!$B$20)/Premissas!$B$19+Premissas!$B$21</f>
         <v>19.8145</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="12" t="n">
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="12" t="n">
         <f aca="false">Premissas!$B$59*Unitário!$B$22</f>
         <v>30</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C25" s="12" t="n">
         <f aca="false">Premissas!$B$59*Unitário!$B$22</f>
         <v>30</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="12" t="n">
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="12" t="n">
         <f aca="false">Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25</f>
         <v>36.56001</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C26" s="12" t="n">
         <f aca="false">Premissas!$B$31</f>
         <v>5</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="12" t="n">
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="12" t="n">
         <f aca="false">-Premissas!$B$26*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))+Premissas!$B$26*Premissas!$B$39+Premissas!$B$27*Premissas!$B$41</f>
         <v>-7.6169017</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C27" s="12" t="n">
         <f aca="false">-Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*Premissas!$B$31)+Premissas!$B$27*Premissas!$B$41</f>
         <v>2</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="14" t="n">
-        <f aca="false">SUM(B22:B24)</f>
+      <c r="D27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <f aca="false">SUM(B25:B27)</f>
         <v>58.9431083</v>
       </c>
-      <c r="C25" s="14" t="n">
-        <f aca="false">SUM(C22:C24)</f>
+      <c r="C28" s="14" t="n">
+        <f aca="false">SUM(C25:C27)</f>
         <v>37</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="15" t="n">
+      <c r="D28" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="15" t="n">
         <f aca="false">Premissas!$B$54+Premissas!$B$55</f>
         <v>16</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C29" s="15" t="n">
         <f aca="false">Premissas!$B$56</f>
         <v>0</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="12" t="n">
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="12" t="n">
         <f aca="false">Unitário!$B$21*Premissas!$B$51</f>
         <v>94.827</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C30" s="12" t="n">
         <f aca="false">(1-Premissas!$B$27)*Premissas!$B$52</f>
         <v>105.219</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="3" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="17" t="n">
-        <f aca="false">A32*B5</f>
-        <v>675</v>
-      </c>
-      <c r="C32" s="17" t="n">
-        <f aca="false">A32*B9</f>
-        <v>879.4672187</v>
-      </c>
-      <c r="D32" s="17" t="n">
-        <f aca="false">$B$13-C32</f>
-        <v>195.5327813</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="17" t="n">
-        <f aca="false">A33*B5</f>
-        <v>1350</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <f aca="false">A33*B9</f>
-        <v>1758.9344374</v>
-      </c>
-      <c r="D33" s="17" t="n">
-        <f aca="false">$B$13-C33</f>
-        <v>-683.9344374</v>
-      </c>
-    </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="17" t="n">
-        <f aca="false">A34*B5</f>
-        <v>2025</v>
-      </c>
-      <c r="C34" s="17" t="n">
-        <f aca="false">A34*B9</f>
-        <v>2638.4016561</v>
-      </c>
-      <c r="D34" s="17" t="n">
-        <f aca="false">$B$13-C34</f>
-        <v>-1563.4016561</v>
+      <c r="A34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">A35*B5</f>
-        <v>3375</v>
+        <v>675</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">A35*B9</f>
-        <v>4397.3360935</v>
+        <v>879.4672187</v>
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">$B$13-C35</f>
-        <v>-3322.3360935</v>
+        <v>195.5327813</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">A36*B5</f>
-        <v>6750</v>
+        <v>1350</v>
       </c>
       <c r="C36" s="17" t="n">
         <f aca="false">A36*B9</f>
-        <v>8794.672187</v>
+        <v>1758.9344374</v>
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">$B$13-C36</f>
+        <v>-683.9344374</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="17" t="n">
+        <f aca="false">A37*B5</f>
+        <v>2025</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <f aca="false">A37*B9</f>
+        <v>2638.4016561</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <f aca="false">$B$13-C37</f>
+        <v>-1563.4016561</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="17" t="n">
+        <f aca="false">A38*B5</f>
+        <v>3375</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <f aca="false">A38*B9</f>
+        <v>4397.3360935</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <f aca="false">$B$13-C38</f>
+        <v>-3322.3360935</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="17" t="n">
+        <f aca="false">A39*B5</f>
+        <v>6750</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <f aca="false">A39*B9</f>
+        <v>8794.672187</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <f aca="false">$B$13-C39</f>
         <v>-7719.672187</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>55</v>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2264,31 +2300,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -2296,231 +2332,231 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B6" s="20" t="n">
         <v>375</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>300</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B11" s="22" t="n">
         <v>46318</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="23" t="n">
         <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>100</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B14" s="24" t="n">
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16" s="21" t="n">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B17" s="25" t="n">
         <v>0.1383</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>0.1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>0.27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>0.04</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -2528,34 +2564,34 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>0.7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B24" s="27" t="n">
         <f aca="false">1-Premissas!$B$23</f>
         <v>0.3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -2563,35 +2599,35 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0.17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>0.1</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -2599,219 +2635,219 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B29" s="24" t="n">
         <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B30" s="24" t="n">
         <v>19.99</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B31" s="24" t="n">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B32" s="28" t="n">
         <v>0.0699</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B33" s="24" t="n">
         <v>2.49</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B34" s="28" t="n">
         <v>0.0099</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B35" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B36" s="28" t="n">
         <v>0.0498</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B37" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B38" s="24" t="n">
         <v>4.99</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B39" s="12" t="n">
         <f aca="false">Premissas!$B$38+Premissas!$B$31</f>
         <v>9.99</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B40" s="20" t="n">
         <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B41" s="12" t="n">
         <f aca="false">Premissas!$B$40+Premissas!$B$31</f>
         <v>50</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B42" s="26" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B43" s="24" t="n">
         <v>53.5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -2819,21 +2855,21 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B46" s="24" t="n">
         <v>129.9</v>
@@ -2847,7 +2883,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B47" s="24" t="n">
         <v>233.82</v>
@@ -2861,7 +2897,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B48" s="24" t="n">
         <v>311.76</v>
@@ -2875,7 +2911,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D49" s="27" t="n">
         <f aca="false">SUM(D46:D48)</f>
@@ -2884,46 +2920,46 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">1*D46+2*D47+3*D48</f>
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B51" s="12" t="n">
         <f aca="false">SUMPRODUCT(B46:B48,D46:D48)</f>
         <v>129.9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B52" s="12" t="n">
         <f aca="false">SUMPRODUCT(C46:C48,D46:D48)</f>
         <v>116.91</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -2931,63 +2967,63 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B54" s="23" t="n">
         <v>2</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>14</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B57" s="23" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -2995,77 +3031,77 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B59" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B60" s="23" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B61" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B62" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B63" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -3073,58 +3109,58 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B65" s="24" t="n">
         <v>1325</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B66" s="24" t="n">
         <v>250</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B67" s="24" t="n">
         <v>3.99</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B68" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3153,26 +3189,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B4" s="12" t="n">
         <f aca="false">Premissas!$B$51</f>
@@ -3186,7 +3222,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">-Premissas!$B$29*Premissas!$B$50</f>
@@ -3197,12 +3233,12 @@
         <v>-30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">-(Premissas!$B$32*Premissas!$B$51+Premissas!$B$33)</f>
@@ -3216,7 +3252,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">-Premissas!$B$30</f>
@@ -3227,12 +3263,12 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">-Premissas!$B$31</f>
@@ -3246,7 +3282,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">SUM(B4:B8)</f>
@@ -3260,7 +3296,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">-Premissas!$B$26*(B9+Premissas!$B$39)</f>
@@ -3271,12 +3307,12 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">-Premissas!$B$27*(B9+Premissas!$B$41+Premissas!$B$62*(Premissas!$B$30+Premissas!$B$31+Premissas!$B$32*Premissas!$B$51+Premissas!$B$33))</f>
@@ -3287,12 +3323,12 @@
         <v>-13.691</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">SUM(B9:B11)</f>
@@ -3306,7 +3342,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">-Premissas!$B$18*(1+Premissas!$B$17)/Premissas!$B$19</f>
@@ -3317,12 +3353,12 @@
         <v>-17.0745</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">-Premissas!$B$20/Premissas!$B$19</f>
@@ -3336,7 +3372,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">-Premissas!$B$21</f>
@@ -3350,7 +3386,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">-Premissas!$B$42*Premissas!$B$51*(1-Premissas!$B$26-Premissas!$B$27)</f>
@@ -3364,7 +3400,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -3378,7 +3414,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">Premissas!$B$23*B17+Premissas!$B$24*C17</f>
@@ -3387,12 +3423,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B21" s="27" t="n">
         <f aca="false">1-Premissas!$B$26-Premissas!$B$27</f>
@@ -3401,7 +3437,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
@@ -3410,7 +3446,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">-(B6+B7+B8)</f>
@@ -3419,7 +3455,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">-(B7+B8)</f>
@@ -3428,7 +3464,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">-B6</f>
@@ -3437,7 +3473,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B26" s="12" t="n">
         <f aca="false">Unitário!$B$21*Unitário!$B$23+Premissas!$B$26*Premissas!$B$39+Premissas!$B$27*Premissas!$B$41</f>
@@ -3446,7 +3482,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">-C6</f>
@@ -3478,98 +3514,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13744,7 +13780,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C95" s="14" t="n">
         <f aca="false">SUM(C5:C94)</f>
@@ -13809,7 +13845,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">MIN(S5:S94)</f>
@@ -13818,7 +13854,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B100" s="32" t="n">
         <f aca="false">INDEX(A5:A94,MATCH(B99,S5:S94,0))</f>
@@ -13827,7 +13863,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B101" s="32" t="n">
         <f aca="false">IFERROR(INDEX(A5:A94,MATCH(1,T5:T94,0)),"não volta em 90 dias")</f>
@@ -13871,24 +13907,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13896,13 +13932,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E4" s="34"/>
     </row>
@@ -13911,13 +13947,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E5" s="34"/>
     </row>
@@ -13926,13 +13962,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E6" s="34"/>
     </row>
@@ -13941,13 +13977,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E7" s="34"/>
     </row>
@@ -13979,296 +14015,296 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D7" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>287</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -14301,469 +14337,469 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C5" s="35" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
         <v>30</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">Premissas!$B$30</f>
         <v>19.99</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">Premissas!$B$31</f>
         <v>5</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">Unitário!$B$25</f>
         <v>11.57001</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C9" s="35" t="n">
         <f aca="false">Premissas!$B$38</f>
         <v>4.99</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">Premissas!$B$39</f>
         <v>9.99</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">Premissas!$B$41+Premissas!$B$62*(Unitário!$B$24+Unitário!$B$25)</f>
         <v>86.56001</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C12" s="35" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
         <v>30</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C13" s="35" t="n">
         <f aca="false">Premissas!$B$41+Premissas!$B$62*Premissas!$B$31+Unitário!$B$27</f>
         <v>58.9897635</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C14" s="35" t="n">
         <f aca="false">Premissas!$B$31</f>
         <v>5</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C15" s="35" t="n">
         <f aca="false">Unitário!$B$27</f>
         <v>3.9897635</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">Premissas!$B$18/Premissas!$B$19*(1+Premissas!$B$17)</f>
         <v>17.0745</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C18" s="35" t="n">
         <f aca="false">Premissas!$B$20/Premissas!$B$19+Premissas!$B$21</f>
         <v>2.74</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F18" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="G18" s="33" t="s">
         <v>399</v>
       </c>
-      <c r="G18" s="33" t="s">
-        <v>395</v>
-      </c>
       <c r="H18" s="33" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C19" s="35" t="n">
         <f aca="false">Premissas!$B$43</f>
         <v>53.5</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C20" s="35" t="n">
         <f aca="false">Premissas!$B$67*Premissas!$B$68</f>
         <v>3.99</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/docs/operacao/modelo-caixa-anuncios.xlsx
+++ b/docs/operacao/modelo-caixa-anuncios.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="416">
   <si>
     <t xml:space="preserve">Resumo — caixa necessário para o teste de anúncios</t>
   </si>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">R$</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador: R$ 375 em 5 dias (lido como total, R$ 75/dia)</t>
+    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 55/dia (plano escolhido; antes R$ 375 em 5 dias)</t>
   </si>
   <si>
     <t xml:space="preserve">Fase 1 — dias</t>
@@ -241,138 +241,141 @@
     <t xml:space="preserve">dias</t>
   </si>
   <si>
+    <t xml:space="preserve">Operador, 09/10: 7 dias (eram 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pausa entre as fases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador: 2 dias de respiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 2 — verba total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 55/dia (plano escolhido; antes R$ 300 em 5 dias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 2 — dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data do 1º dia de anúncio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: usar 23/10 para modelar (sexta-feira)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatura do cartão: dia de fechamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dia do mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10 (gasto até o dia 22 entra na fatura do mês — confirmar se o dia 22 conta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta: limite de cobrança no cartão (ou fim do mês)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: o Ads cobra ao bater R$ 100 ou no fim do mês; limite do cartão R$ 4.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta API (IA): limite de cobrança no cartão (ou fim do mês)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10: a API da Meta cobra ao chegar em R$ 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saque do saldo até a conta: dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador: D+1 a D+2 (usei 2); o saque sai antes do vencimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatura do cartão: dia de vencimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 09/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imposto que a Meta soma à fatura no Brasil (PIS/Cofins + ISS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% sobre a verba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicado Meta: R$ 100 → R$ 113,83 no cartão. Operador, 09/10: 'deve aparecer' — conferir na 1ª fatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo por lead (CPL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador, 02/10 (faixa 1,25–1,50; ponta pessimista)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversão lead → pedido criado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador (limiar de escalar, L3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo de IA por lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medido L0.5 (p50 30/09; p95 R$ 0,546)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp (template pós-venda) por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela Meta (~US$ 0,0068)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix de vendas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% dos pedidos em pagamento na entrega (COD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador (70/30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% dos pedidos em pagamento antecipado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado do pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recusa na porta (só COD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador: faixa 12–17%, AINDA NÃO MEDIDA (ponta pessimista)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devolução pós-envio (COD e antecipado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador: faixa 5–10% (ponta pessimista)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custos por pedido (docs 06-modelo-economico, 02/10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produto, por peça</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$/peça</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operador</t>
   </si>
   <si>
-    <t xml:space="preserve">Pausa entre as fases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador: 2 dias de respiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fase 2 — verba total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador: mais R$ 300 em 5 dias (lido como total, R$ 60/dia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fase 2 — dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data do 1º dia de anúncio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10: usar 23/10 para modelar (sexta-feira)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatura do cartão: dia de fechamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dia do mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10 (gasto até o dia 22 entra na fatura do mês — confirmar se o dia 22 conta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta: limite de cobrança no cartão (ou fim do mês)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10: o Ads cobra ao bater R$ 100 ou no fim do mês; limite do cartão R$ 4.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta API (IA): limite de cobrança no cartão (ou fim do mês)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10: a API da Meta cobra ao chegar em R$ 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saque do saldo até a conta: dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador: D+1 a D+2 (usei 2); o saque sai antes do vencimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatura do cartão: dia de vencimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 09/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imposto que a Meta soma à fatura no Brasil (PIS/Cofins + ISS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre a verba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicado Meta: R$ 100 → R$ 113,83 no cartão. Operador, 09/10: 'deve aparecer' — conferir na 1ª fatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo por lead (CPL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador, 02/10 (faixa 1,25–1,50; ponta pessimista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conversão lead → pedido criado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador (limiar de escalar, L3.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo de IA por lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medido L0.5 (p50 30/09; p95 R$ 0,546)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp (template pós-venda) por pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabela Meta (~US$ 0,0068)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mix de vendas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% dos pedidos em pagamento na entrega (COD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador (70/30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% dos pedidos em pagamento antecipado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado do pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recusa na porta (só COD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador: faixa 12–17%, AINDA NÃO MEDIDA (ponta pessimista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devolução pós-envio (COD e antecipado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operador: faixa 5–10% (ponta pessimista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custos por pedido (docs 06-modelo-economico, 02/10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produto, por peça</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$/peça</t>
-  </si>
-  <si>
     <t xml:space="preserve">Taxa de entrega concluída (só COD)</t>
   </si>
   <si>
@@ -562,7 +565,7 @@
     <t xml:space="preserve">Caixa disponível</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador, 09/10 (de R$ 2.000 investidos; os outros R$ 675 = verba de anúncio no cartão)</t>
+    <t xml:space="preserve">Operador, 09/10 (dos R$ 2.000 investidos; a verba de R$ 770 vai no cartão e é paga com o repasse do COD, não com este caixa)</t>
   </si>
   <si>
     <t xml:space="preserve">Margem de segurança</t>
@@ -1498,7 +1501,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1511,10 +1514,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1531,6 +1530,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1850,7 +1853,7 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">'Fluxo diário'!C95</f>
-        <v>675</v>
+        <v>770</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -1862,7 +1865,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Fluxo diário'!G95+'Fluxo diário'!H95</f>
-        <v>45</v>
+        <v>51.3333333333333</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -1874,7 +1877,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f aca="false">TEXT('Fluxo diário'!G95,"0.0")&amp;" / "&amp;TEXT('Fluxo diário'!H95,"0.0")</f>
-        <v>31.5 / 13.5</v>
+        <v>35.9 / 15.4</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -1884,7 +1887,7 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">'Fluxo diário'!G95*Premissas!$B$51+'Fluxo diário'!H95*Premissas!$B$52</f>
-        <v>5670.135</v>
+        <v>6468.154</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -1896,7 +1899,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">-'Fluxo diário'!B99</f>
-        <v>879.4672187</v>
+        <v>827.567485873333</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
@@ -1908,7 +1911,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">'Fluxo diário'!B100</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
@@ -1920,7 +1923,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Fluxo diário'!B101</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -1932,7 +1935,7 @@
       </c>
       <c r="B12" s="4" t="n">
         <f aca="false">-'Fluxo diário'!B102</f>
-        <v>1647.8197187</v>
+        <v>1704.05848587333</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
@@ -1956,7 +1959,7 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">B13-B9</f>
-        <v>195.5327813</v>
+        <v>247.432514126667</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>23</v>
@@ -1968,7 +1971,7 @@
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">'Fluxo diário'!S94</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
@@ -1992,7 +1995,7 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">IFERROR(B13/B9,0)</f>
-        <v>1.22233094894547</v>
+        <v>1.29898771804157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2004,7 +2007,7 @@
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">B5*(1+Premissas!$B$17)</f>
-        <v>768.3525</v>
+        <v>876.491</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>31</v>
@@ -2016,7 +2019,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">B5/Premissas!$B$18</f>
-        <v>450</v>
+        <v>513.333333333333</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
@@ -2028,7 +2031,7 @@
       </c>
       <c r="B20" s="6" t="str">
         <f aca="false">IF(AND(B19&gt;500,B6&gt;50),"passa","abaixo do piso")</f>
-        <v>abaixo do piso</v>
+        <v>passa</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>35</v>
@@ -2190,15 +2193,15 @@
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">A35*B5</f>
-        <v>675</v>
+        <v>770</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">A35*B9</f>
-        <v>879.4672187</v>
+        <v>827.567485873333</v>
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">$B$13-C35</f>
-        <v>195.5327813</v>
+        <v>247.432514126667</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,15 +2210,15 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">A36*B5</f>
-        <v>1350</v>
+        <v>1540</v>
       </c>
       <c r="C36" s="17" t="n">
         <f aca="false">A36*B9</f>
-        <v>1758.9344374</v>
+        <v>1655.13497174667</v>
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">$B$13-C36</f>
-        <v>-683.9344374</v>
+        <v>-580.134971746667</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2224,15 +2227,15 @@
       </c>
       <c r="B37" s="17" t="n">
         <f aca="false">A37*B5</f>
-        <v>2025</v>
+        <v>2310</v>
       </c>
       <c r="C37" s="17" t="n">
         <f aca="false">A37*B9</f>
-        <v>2638.4016561</v>
+        <v>2482.70245762</v>
       </c>
       <c r="D37" s="17" t="n">
         <f aca="false">$B$13-C37</f>
-        <v>-1563.4016561</v>
+        <v>-1407.70245762</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2241,15 +2244,15 @@
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">A38*B5</f>
-        <v>3375</v>
+        <v>3850</v>
       </c>
       <c r="C38" s="17" t="n">
         <f aca="false">A38*B9</f>
-        <v>4397.3360935</v>
+        <v>4137.83742936667</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">$B$13-C38</f>
-        <v>-3322.3360935</v>
+        <v>-3062.83742936667</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2258,15 +2261,15 @@
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">A39*B5</f>
-        <v>6750</v>
+        <v>7700</v>
       </c>
       <c r="C39" s="17" t="n">
         <f aca="false">A39*B9</f>
-        <v>8794.672187</v>
+        <v>8275.67485873333</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">$B$13-C39</f>
-        <v>-7719.672187</v>
+        <v>-7200.67485873333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,7 +2338,7 @@
         <v>66</v>
       </c>
       <c r="B6" s="20" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>67</v>
@@ -2349,7 +2352,7 @@
         <v>69</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>70</v>
@@ -2377,7 +2380,7 @@
         <v>74</v>
       </c>
       <c r="B9" s="20" t="n">
-        <v>300</v>
+        <v>385</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>67</v>
@@ -2391,7 +2394,7 @@
         <v>76</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>70</v>
@@ -2432,7 +2435,7 @@
       <c r="A13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="20" t="n">
         <v>100</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2446,7 +2449,7 @@
       <c r="A14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="20" t="n">
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2488,7 +2491,7 @@
       <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="24" t="n">
         <v>0.1383</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2502,7 +2505,7 @@
       <c r="A18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="20" t="n">
         <v>1.5</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2516,7 +2519,7 @@
       <c r="A19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2530,7 +2533,7 @@
       <c r="A20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="20" t="n">
         <v>0.27</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2544,7 +2547,7 @@
       <c r="A21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="20" t="n">
         <v>0.04</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2566,7 +2569,7 @@
       <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="25" t="n">
         <v>0.7</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2580,7 +2583,7 @@
       <c r="A24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="26" t="n">
         <f aca="false">1-Premissas!$B$23</f>
         <v>0.3</v>
       </c>
@@ -2601,7 +2604,7 @@
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="25" t="n">
         <v>0.17</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2615,7 +2618,7 @@
       <c r="A27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2637,217 +2640,217 @@
       <c r="A29" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="20" t="n">
         <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <v>19.99</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="24" t="n">
+        <v>119</v>
+      </c>
+      <c r="B31" s="20" t="n">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" s="28" t="n">
+        <v>121</v>
+      </c>
+      <c r="B32" s="27" t="n">
         <v>0.0699</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B33" s="24" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="28" t="n">
+        <v>124</v>
+      </c>
+      <c r="B34" s="27" t="n">
         <v>0.0099</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="28" t="n">
+        <v>127</v>
+      </c>
+      <c r="B36" s="27" t="n">
         <v>0.0498</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="26" t="n">
+        <v>128</v>
+      </c>
+      <c r="B37" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="B38" s="20" t="n">
         <v>4.99</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" s="12" t="n">
         <f aca="false">Premissas!$B$38+Premissas!$B$31</f>
         <v>9.99</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B40" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="B40" s="28" t="n">
         <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B41" s="12" t="n">
         <f aca="false">Premissas!$B$40+Premissas!$B$31</f>
         <v>50</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B42" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="B42" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="24" t="n">
+        <v>140</v>
+      </c>
+      <c r="B43" s="20" t="n">
         <v>53.5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -2855,85 +2858,85 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="24" t="n">
+        <v>148</v>
+      </c>
+      <c r="B46" s="20" t="n">
         <v>129.9</v>
       </c>
-      <c r="C46" s="24" t="n">
+      <c r="C46" s="20" t="n">
         <v>116.91</v>
       </c>
-      <c r="D46" s="25" t="n">
+      <c r="D46" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" s="24" t="n">
+        <v>149</v>
+      </c>
+      <c r="B47" s="20" t="n">
         <v>233.82</v>
       </c>
-      <c r="C47" s="24" t="n">
+      <c r="C47" s="20" t="n">
         <v>207.84</v>
       </c>
-      <c r="D47" s="25" t="n">
+      <c r="D47" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="B48" s="20" t="n">
         <v>311.76</v>
       </c>
-      <c r="C48" s="24" t="n">
+      <c r="C48" s="20" t="n">
         <v>272.79</v>
       </c>
-      <c r="D48" s="25" t="n">
+      <c r="D48" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="27" t="n">
+        <v>151</v>
+      </c>
+      <c r="D49" s="26" t="n">
         <f aca="false">SUM(D46:D48)</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">1*D46+2*D47+3*D48</f>
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B51" s="12" t="n">
         <f aca="false">SUMPRODUCT(B46:B48,D46:D48)</f>
@@ -2946,7 +2949,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B52" s="12" t="n">
         <f aca="false">SUMPRODUCT(C46:C48,D46:D48)</f>
@@ -2959,7 +2962,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -2967,7 +2970,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B54" s="23" t="n">
         <v>2</v>
@@ -2976,12 +2979,12 @@
         <v>70</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>14</v>
@@ -2990,12 +2993,12 @@
         <v>70</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>0</v>
@@ -3004,12 +3007,12 @@
         <v>70</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B57" s="23" t="n">
         <v>7</v>
@@ -3018,12 +3021,12 @@
         <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -3031,21 +3034,21 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B60" s="23" t="n">
         <v>1</v>
@@ -3054,54 +3057,54 @@
         <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B61" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B62" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B63" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -3109,23 +3112,23 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B65" s="24" t="n">
+        <v>178</v>
+      </c>
+      <c r="B65" s="20" t="n">
         <v>1325</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B66" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="B66" s="20" t="n">
         <v>250</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -3137,30 +3140,30 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B67" s="24" t="n">
+        <v>181</v>
+      </c>
+      <c r="B67" s="20" t="n">
         <v>3.99</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3189,26 +3192,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B4" s="12" t="n">
         <f aca="false">Premissas!$B$51</f>
@@ -3222,7 +3225,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">-Premissas!$B$29*Premissas!$B$50</f>
@@ -3233,12 +3236,12 @@
         <v>-30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">-(Premissas!$B$32*Premissas!$B$51+Premissas!$B$33)</f>
@@ -3252,7 +3255,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">-Premissas!$B$30</f>
@@ -3263,12 +3266,12 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">-Premissas!$B$31</f>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">SUM(B4:B8)</f>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">-Premissas!$B$26*(B9+Premissas!$B$39)</f>
@@ -3307,12 +3310,12 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">-Premissas!$B$27*(B9+Premissas!$B$41+Premissas!$B$62*(Premissas!$B$30+Premissas!$B$31+Premissas!$B$32*Premissas!$B$51+Premissas!$B$33))</f>
@@ -3323,12 +3326,12 @@
         <v>-13.691</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">SUM(B9:B11)</f>
@@ -3342,7 +3345,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">-Premissas!$B$18*(1+Premissas!$B$17)/Premissas!$B$19</f>
@@ -3353,12 +3356,12 @@
         <v>-17.0745</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">-Premissas!$B$20/Premissas!$B$19</f>
@@ -3372,7 +3375,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">-Premissas!$B$21</f>
@@ -3386,7 +3389,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">-Premissas!$B$42*Premissas!$B$51*(1-Premissas!$B$26-Premissas!$B$27)</f>
@@ -3400,7 +3403,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">SUM(B12:B16)</f>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">Premissas!$B$23*B17+Premissas!$B$24*C17</f>
@@ -3423,21 +3426,21 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B21" s="27" t="n">
+        <v>212</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <f aca="false">1-Premissas!$B$26-Premissas!$B$27</f>
         <v>0.73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
@@ -3446,7 +3449,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">-(B6+B7+B8)</f>
@@ -3455,7 +3458,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">-(B7+B8)</f>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">-B6</f>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" s="12" t="n">
         <f aca="false">Unitário!$B$21*Unitário!$B$23+Premissas!$B$26*Premissas!$B$39+Premissas!$B$27*Premissas!$B$41</f>
@@ -3482,7 +3485,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">-C6</f>
@@ -3514,98 +3517,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3618,7 +3621,7 @@
       </c>
       <c r="C5" s="12" t="n">
         <f aca="false">IF(A5&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A5&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A5&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D5" s="15" t="n">
         <f aca="false">IF(Y5&gt;0,IF(DAY(B5)&lt;=Premissas!$B$12,DATE(YEAR(B5),MONTH(B5),Premissas!$B$16),DATE(YEAR(B5),MONTH(B5)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3634,11 +3637,11 @@
       </c>
       <c r="G5" s="29" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>3.5</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H5" s="29" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I5" s="12" t="n">
         <f aca="false">-IF($A5-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
@@ -3658,7 +3661,7 @@
       </c>
       <c r="M5" s="12" t="n">
         <f aca="false">IF($A5-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">-IF($A5-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
@@ -3678,11 +3681,11 @@
       </c>
       <c r="R5" s="12" t="n">
         <f aca="false">E5+F5+SUM(I5:Q5)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="S5" s="12" t="n">
         <f aca="false">R5</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="T5" s="15" t="n">
         <f aca="false">IF(AND($A5&gt;$B$100,S5&gt;=0),1,0)</f>
@@ -3690,11 +3693,11 @@
       </c>
       <c r="U5" s="12" t="n">
         <f aca="false">S5-SUM($E$5:E5)-(1+Premissas!$B$17)*SUM($C$5:C5)</f>
-        <v>84.00785475</v>
+        <v>61.60576015</v>
       </c>
       <c r="V5" s="12" t="n">
         <f aca="false">(G5+H5)*Premissas!$B$21</f>
-        <v>0.2</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W5" s="15" t="n">
         <f aca="false">IF(V5&gt;0,DATE(YEAR(B5),MONTH(B5)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3702,7 +3705,7 @@
       </c>
       <c r="X5" s="12" t="n">
         <f aca="false">C5*(1+Premissas!$B$17)</f>
-        <v>85.3725</v>
+        <v>62.6065</v>
       </c>
       <c r="Y5" s="12" t="n">
         <f aca="false">IF(OR(X5&gt;=Premissas!$B$13,B5=DATE(YEAR(B5),MONTH(B5)+1,0)),X5,0)</f>
@@ -3710,7 +3713,7 @@
       </c>
       <c r="Z5" s="12" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$20</f>
-        <v>13.5</v>
+        <v>9.9</v>
       </c>
       <c r="AA5" s="12" t="n">
         <f aca="false">IF(OR(Z5&gt;=Premissas!$B$14,B5=DATE(YEAR(B5),MONTH(B5)+1,0)),Z5,0)</f>
@@ -3731,7 +3734,7 @@
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">IF(A6&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A6&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A6&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">IF(Y6&gt;0,IF(DAY(B6)&lt;=Premissas!$B$12,DATE(YEAR(B6),MONTH(B6),Premissas!$B$16),DATE(YEAR(B6),MONTH(B6)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3747,15 +3750,15 @@
       </c>
       <c r="G6" s="29" t="n">
         <f aca="false">C6/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>3.5</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H6" s="29" t="n">
         <f aca="false">C6/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I6" s="12" t="n">
         <f aca="false">-IF($A6-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-232.960035</v>
+        <v>-170.837359</v>
       </c>
       <c r="J6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
@@ -3771,11 +3774,11 @@
       </c>
       <c r="M6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">-IF($A6-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-52.5</v>
+        <v>-38.5</v>
       </c>
       <c r="O6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -3791,11 +3794,11 @@
       </c>
       <c r="R6" s="12" t="n">
         <f aca="false">E6+F6+SUM(I6:Q6)</f>
-        <v>-116.07968025</v>
+        <v>-85.12509885</v>
       </c>
       <c r="S6" s="12" t="n">
         <f aca="false">S5+R6</f>
-        <v>53.3006745000001</v>
+        <v>39.0871613</v>
       </c>
       <c r="T6" s="15" t="n">
         <f aca="false">IF(AND($A6&gt;$B$100,S6&gt;=0),1,0)</f>
@@ -3803,11 +3806,11 @@
       </c>
       <c r="U6" s="12" t="n">
         <f aca="false">S6-SUM($E$5:E6)-(1+Premissas!$B$17)*SUM($C$5:C6)</f>
-        <v>-117.4443255</v>
+        <v>-86.1258387</v>
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">(G6+H6)*Premissas!$B$21</f>
-        <v>0.2</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W6" s="15" t="n">
         <f aca="false">IF(V6&gt;0,DATE(YEAR(B6),MONTH(B6)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3815,23 +3818,23 @@
       </c>
       <c r="X6" s="12" t="n">
         <f aca="false">X5-Y5+C6*(1+Premissas!$B$17)</f>
-        <v>170.745</v>
+        <v>125.213</v>
       </c>
       <c r="Y6" s="12" t="n">
         <f aca="false">IF(OR(X6&gt;=Premissas!$B$13,B6=DATE(YEAR(B6),MONTH(B6)+1,0)),X6,0)</f>
-        <v>170.745</v>
+        <v>125.213</v>
       </c>
       <c r="Z6" s="12" t="n">
         <f aca="false">Z5-AA5+C6/Premissas!$B$18*Premissas!$B$20</f>
-        <v>27</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" s="12" t="n">
         <f aca="false">IF(OR(Z6&gt;=Premissas!$B$14,B6=DATE(YEAR(B6),MONTH(B6)+1,0)),Z6,0)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="15" t="n">
         <f aca="false">IF(AA6&gt;0,IF(DAY(B6)&lt;=Premissas!$B$12,DATE(YEAR(B6),MONTH(B6),Premissas!$B$16),DATE(YEAR(B6),MONTH(B6)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3844,7 +3847,7 @@
       </c>
       <c r="C7" s="12" t="n">
         <f aca="false">IF(A7&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A7&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A7&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">IF(Y7&gt;0,IF(DAY(B7)&lt;=Premissas!$B$12,DATE(YEAR(B7),MONTH(B7),Premissas!$B$16),DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3860,19 +3863,19 @@
       </c>
       <c r="G7" s="29" t="n">
         <f aca="false">C7/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>3.5</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H7" s="29" t="n">
         <f aca="false">C7/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I7" s="12" t="n">
         <f aca="false">-IF($A7-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-232.960035</v>
+        <v>-170.837359</v>
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>33.65915595</v>
+        <v>24.68338103</v>
       </c>
       <c r="K7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -3884,11 +3887,11 @@
       </c>
       <c r="M7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="N7" s="12" t="n">
         <f aca="false">-IF($A7-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-52.5</v>
+        <v>-38.5</v>
       </c>
       <c r="O7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -3904,11 +3907,11 @@
       </c>
       <c r="R7" s="12" t="n">
         <f aca="false">E7+F7+SUM(I7:Q7)</f>
-        <v>-82.4205243</v>
+        <v>-60.44171782</v>
       </c>
       <c r="S7" s="12" t="n">
         <f aca="false">S6+R7</f>
-        <v>-29.1198497999999</v>
+        <v>-21.35455652</v>
       </c>
       <c r="T7" s="15" t="n">
         <f aca="false">IF(AND($A7&gt;$B$100,S7&gt;=0),1,0)</f>
@@ -3916,11 +3919,11 @@
       </c>
       <c r="U7" s="12" t="n">
         <f aca="false">S7-SUM($E$5:E7)-(1+Premissas!$B$17)*SUM($C$5:C7)</f>
-        <v>-285.2373498</v>
+        <v>-209.17405652</v>
       </c>
       <c r="V7" s="12" t="n">
         <f aca="false">(G7+H7)*Premissas!$B$21</f>
-        <v>0.2</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W7" s="15" t="n">
         <f aca="false">IF(V7&gt;0,DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3928,7 +3931,7 @@
       </c>
       <c r="X7" s="12" t="n">
         <f aca="false">X6-Y6+C7*(1+Premissas!$B$17)</f>
-        <v>85.3725</v>
+        <v>62.6065</v>
       </c>
       <c r="Y7" s="12" t="n">
         <f aca="false">IF(OR(X7&gt;=Premissas!$B$13,B7=DATE(YEAR(B7),MONTH(B7)+1,0)),X7,0)</f>
@@ -3936,15 +3939,15 @@
       </c>
       <c r="Z7" s="12" t="n">
         <f aca="false">Z6-AA6+C7/Premissas!$B$18*Premissas!$B$20</f>
-        <v>13.5</v>
+        <v>29.7</v>
       </c>
       <c r="AA7" s="12" t="n">
         <f aca="false">IF(OR(Z7&gt;=Premissas!$B$14,B7=DATE(YEAR(B7),MONTH(B7)+1,0)),Z7,0)</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AB7" s="15" t="n">
         <f aca="false">IF(AA7&gt;0,IF(DAY(B7)&lt;=Premissas!$B$12,DATE(YEAR(B7),MONTH(B7),Premissas!$B$16),DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3957,7 +3960,7 @@
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">IF(A8&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A8&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A8&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">IF(Y8&gt;0,IF(DAY(B8)&lt;=Premissas!$B$12,DATE(YEAR(B8),MONTH(B8),Premissas!$B$16),DATE(YEAR(B8),MONTH(B8)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3973,19 +3976,19 @@
       </c>
       <c r="G8" s="29" t="n">
         <f aca="false">C8/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>3.5</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H8" s="29" t="n">
         <f aca="false">C8/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">-IF($A8-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-232.960035</v>
+        <v>-170.837359</v>
       </c>
       <c r="J8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>33.65915595</v>
+        <v>24.68338103</v>
       </c>
       <c r="K8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -3997,11 +4000,11 @@
       </c>
       <c r="M8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">-IF($A8-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-52.5</v>
+        <v>-38.5</v>
       </c>
       <c r="O8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4017,11 +4020,11 @@
       </c>
       <c r="R8" s="12" t="n">
         <f aca="false">E8+F8+SUM(I8:Q8)</f>
-        <v>-82.4205243</v>
+        <v>-60.44171782</v>
       </c>
       <c r="S8" s="12" t="n">
         <f aca="false">S7+R8</f>
-        <v>-111.5403741</v>
+        <v>-81.7962743399999</v>
       </c>
       <c r="T8" s="15" t="n">
         <f aca="false">IF(AND($A8&gt;$B$100,S8&gt;=0),1,0)</f>
@@ -4029,11 +4032,11 @@
       </c>
       <c r="U8" s="12" t="n">
         <f aca="false">S8-SUM($E$5:E8)-(1+Premissas!$B$17)*SUM($C$5:C8)</f>
-        <v>-453.0303741</v>
+        <v>-332.22227434</v>
       </c>
       <c r="V8" s="12" t="n">
         <f aca="false">(G8+H8)*Premissas!$B$21</f>
-        <v>0.2</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W8" s="15" t="n">
         <f aca="false">IF(V8&gt;0,DATE(YEAR(B8),MONTH(B8)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4041,23 +4044,23 @@
       </c>
       <c r="X8" s="12" t="n">
         <f aca="false">X7-Y7+C8*(1+Premissas!$B$17)</f>
-        <v>170.745</v>
+        <v>125.213</v>
       </c>
       <c r="Y8" s="12" t="n">
         <f aca="false">IF(OR(X8&gt;=Premissas!$B$13,B8=DATE(YEAR(B8),MONTH(B8)+1,0)),X8,0)</f>
-        <v>170.745</v>
+        <v>125.213</v>
       </c>
       <c r="Z8" s="12" t="n">
         <f aca="false">Z7-AA7+C8/Premissas!$B$18*Premissas!$B$20</f>
-        <v>27</v>
+        <v>9.9</v>
       </c>
       <c r="AA8" s="12" t="n">
         <f aca="false">IF(OR(Z8&gt;=Premissas!$B$14,B8=DATE(YEAR(B8),MONTH(B8)+1,0)),Z8,0)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="15" t="n">
         <f aca="false">IF(AA8&gt;0,IF(DAY(B8)&lt;=Premissas!$B$12,DATE(YEAR(B8),MONTH(B8),Premissas!$B$16),DATE(YEAR(B8),MONTH(B8)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4070,7 +4073,7 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">IF(A9&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A9&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A9&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">IF(Y9&gt;0,IF(DAY(B9)&lt;=Premissas!$B$12,DATE(YEAR(B9),MONTH(B9),Premissas!$B$16),DATE(YEAR(B9),MONTH(B9)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4086,19 +4089,19 @@
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">C9/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>3.5</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">C9/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">-IF($A9-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-232.960035</v>
+        <v>-170.837359</v>
       </c>
       <c r="J9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>33.65915595</v>
+        <v>24.68338103</v>
       </c>
       <c r="K9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4110,11 +4113,11 @@
       </c>
       <c r="M9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>169.38035475</v>
+        <v>124.21226015</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">-IF($A9-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-52.5</v>
+        <v>-38.5</v>
       </c>
       <c r="O9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4130,11 +4133,11 @@
       </c>
       <c r="R9" s="12" t="n">
         <f aca="false">E9+F9+SUM(I9:Q9)</f>
-        <v>-82.4205243</v>
+        <v>-60.44171782</v>
       </c>
       <c r="S9" s="12" t="n">
         <f aca="false">S8+R9</f>
-        <v>-193.9608984</v>
+        <v>-142.23799216</v>
       </c>
       <c r="T9" s="15" t="n">
         <f aca="false">IF(AND($A9&gt;$B$100,S9&gt;=0),1,0)</f>
@@ -4142,11 +4145,11 @@
       </c>
       <c r="U9" s="12" t="n">
         <f aca="false">S9-SUM($E$5:E9)-(1+Premissas!$B$17)*SUM($C$5:C9)</f>
-        <v>-620.8233984</v>
+        <v>-455.27049216</v>
       </c>
       <c r="V9" s="12" t="n">
         <f aca="false">(G9+H9)*Premissas!$B$21</f>
-        <v>0.2</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W9" s="15" t="n">
         <f aca="false">IF(V9&gt;0,DATE(YEAR(B9),MONTH(B9)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4154,7 +4157,7 @@
       </c>
       <c r="X9" s="12" t="n">
         <f aca="false">X8-Y8+C9*(1+Premissas!$B$17)</f>
-        <v>85.3725</v>
+        <v>62.6065</v>
       </c>
       <c r="Y9" s="12" t="n">
         <f aca="false">IF(OR(X9&gt;=Premissas!$B$13,B9=DATE(YEAR(B9),MONTH(B9)+1,0)),X9,0)</f>
@@ -4162,7 +4165,7 @@
       </c>
       <c r="Z9" s="12" t="n">
         <f aca="false">Z8-AA8+C9/Premissas!$B$18*Premissas!$B$20</f>
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="AA9" s="12" t="n">
         <f aca="false">IF(OR(Z9&gt;=Premissas!$B$14,B9=DATE(YEAR(B9),MONTH(B9)+1,0)),Z9,0)</f>
@@ -4183,11 +4186,11 @@
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">IF(A10&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A10&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A10&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">IF(Y10&gt;0,IF(DAY(B10)&lt;=Premissas!$B$12,DATE(YEAR(B10),MONTH(B10),Premissas!$B$16),DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E10" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A10,$Y$5:$Y$94)</f>
@@ -4199,19 +4202,19 @@
       </c>
       <c r="G10" s="29" t="n">
         <f aca="false">C10/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H10" s="29" t="n">
         <f aca="false">C10/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">-IF($A10-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-232.960035</v>
+        <v>-170.837359</v>
       </c>
       <c r="J10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>33.65915595</v>
+        <v>24.68338103</v>
       </c>
       <c r="K10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4223,11 +4226,11 @@
       </c>
       <c r="M10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">-IF($A10-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-52.5</v>
+        <v>-38.5</v>
       </c>
       <c r="O10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4243,11 +4246,11 @@
       </c>
       <c r="R10" s="12" t="n">
         <f aca="false">E10+F10+SUM(I10:Q10)</f>
-        <v>-251.80087905</v>
+        <v>-60.44171782</v>
       </c>
       <c r="S10" s="12" t="n">
         <f aca="false">S9+R10</f>
-        <v>-445.76177745</v>
+        <v>-202.67970998</v>
       </c>
       <c r="T10" s="15" t="n">
         <f aca="false">IF(AND($A10&gt;$B$100,S10&gt;=0),1,0)</f>
@@ -4255,35 +4258,35 @@
       </c>
       <c r="U10" s="12" t="n">
         <f aca="false">S10-SUM($E$5:E10)-(1+Premissas!$B$17)*SUM($C$5:C10)</f>
-        <v>-872.62427745</v>
+        <v>-578.31870998</v>
       </c>
       <c r="V10" s="12" t="n">
         <f aca="false">(G10+H10)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W10" s="15" t="n">
         <f aca="false">IF(V10&gt;0,DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X10" s="12" t="n">
         <f aca="false">X9-Y9+C10*(1+Premissas!$B$17)</f>
-        <v>85.3725</v>
+        <v>125.213</v>
       </c>
       <c r="Y10" s="12" t="n">
         <f aca="false">IF(OR(X10&gt;=Premissas!$B$13,B10=DATE(YEAR(B10),MONTH(B10)+1,0)),X10,0)</f>
-        <v>0</v>
+        <v>125.213</v>
       </c>
       <c r="Z10" s="12" t="n">
         <f aca="false">Z9-AA9+C10/Premissas!$B$18*Premissas!$B$20</f>
-        <v>13.5</v>
+        <v>29.7</v>
       </c>
       <c r="AA10" s="12" t="n">
         <f aca="false">IF(OR(Z10&gt;=Premissas!$B$14,B10=DATE(YEAR(B10),MONTH(B10)+1,0)),Z10,0)</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AB10" s="15" t="n">
         <f aca="false">IF(AA10&gt;0,IF(DAY(B10)&lt;=Premissas!$B$12,DATE(YEAR(B10),MONTH(B10),Premissas!$B$16),DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4296,7 +4299,7 @@
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">IF(A11&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A11&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A11&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">IF(Y11&gt;0,IF(DAY(B11)&lt;=Premissas!$B$12,DATE(YEAR(B11),MONTH(B11),Premissas!$B$16),DATE(YEAR(B11),MONTH(B11)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4312,19 +4315,19 @@
       </c>
       <c r="G11" s="29" t="n">
         <f aca="false">C11/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H11" s="29" t="n">
         <f aca="false">C11/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">-IF($A11-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>33.65915595</v>
+        <v>24.68338103</v>
       </c>
       <c r="K11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4336,11 +4339,11 @@
       </c>
       <c r="M11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">-IF($A11-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4356,11 +4359,11 @@
       </c>
       <c r="R11" s="12" t="n">
         <f aca="false">E11+F11+SUM(I11:Q11)</f>
-        <v>33.65915595</v>
+        <v>-60.44171782</v>
       </c>
       <c r="S11" s="12" t="n">
         <f aca="false">S10+R11</f>
-        <v>-412.1026215</v>
+        <v>-263.1214278</v>
       </c>
       <c r="T11" s="15" t="n">
         <f aca="false">IF(AND($A11&gt;$B$100,S11&gt;=0),1,0)</f>
@@ -4368,19 +4371,19 @@
       </c>
       <c r="U11" s="12" t="n">
         <f aca="false">S11-SUM($E$5:E11)-(1+Premissas!$B$17)*SUM($C$5:C11)</f>
-        <v>-838.9651215</v>
+        <v>-701.3669278</v>
       </c>
       <c r="V11" s="12" t="n">
         <f aca="false">(G11+H11)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">IF(V11&gt;0,DATE(YEAR(B11),MONTH(B11)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X11" s="12" t="n">
         <f aca="false">X10-Y10+C11*(1+Premissas!$B$17)</f>
-        <v>85.3725</v>
+        <v>62.6065</v>
       </c>
       <c r="Y11" s="12" t="n">
         <f aca="false">IF(OR(X11&gt;=Premissas!$B$13,B11=DATE(YEAR(B11),MONTH(B11)+1,0)),X11,0)</f>
@@ -4388,7 +4391,7 @@
       </c>
       <c r="Z11" s="12" t="n">
         <f aca="false">Z10-AA10+C11/Premissas!$B$18*Premissas!$B$20</f>
-        <v>13.5</v>
+        <v>9.9</v>
       </c>
       <c r="AA11" s="12" t="n">
         <f aca="false">IF(OR(Z11&gt;=Premissas!$B$14,B11=DATE(YEAR(B11),MONTH(B11)+1,0)),Z11,0)</f>
@@ -4409,11 +4412,11 @@
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">IF(A12&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A12&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A12&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">IF(Y12&gt;0,IF(DAY(B12)&lt;=Premissas!$B$12,DATE(YEAR(B12),MONTH(B12),Premissas!$B$16),DATE(YEAR(B12),MONTH(B12)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A12,$Y$5:$Y$94)</f>
@@ -4425,19 +4428,19 @@
       </c>
       <c r="G12" s="29" t="n">
         <f aca="false">C12/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H12" s="29" t="n">
         <f aca="false">C12/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">-IF($A12-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4449,11 +4452,11 @@
       </c>
       <c r="M12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>135.5042838</v>
+        <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">-IF($A12-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4469,11 +4472,11 @@
       </c>
       <c r="R12" s="12" t="n">
         <f aca="false">E12+F12+SUM(I12:Q12)</f>
-        <v>135.5042838</v>
+        <v>-184.65397797</v>
       </c>
       <c r="S12" s="12" t="n">
         <f aca="false">S11+R12</f>
-        <v>-276.5983377</v>
+        <v>-447.77540577</v>
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(AND($A12&gt;$B$100,S12&gt;=0),1,0)</f>
@@ -4481,35 +4484,35 @@
       </c>
       <c r="U12" s="12" t="n">
         <f aca="false">S12-SUM($E$5:E12)-(1+Premissas!$B$17)*SUM($C$5:C12)</f>
-        <v>-771.7588377</v>
+        <v>-886.02090577</v>
       </c>
       <c r="V12" s="12" t="n">
         <f aca="false">(G12+H12)*Premissas!$B$21</f>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="W12" s="15" t="n">
         <f aca="false">IF(V12&gt;0,DATE(YEAR(B12),MONTH(B12)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="X12" s="12" t="n">
         <f aca="false">X11-Y11+C12*(1+Premissas!$B$17)</f>
-        <v>153.6705</v>
+        <v>62.6065</v>
       </c>
       <c r="Y12" s="12" t="n">
         <f aca="false">IF(OR(X12&gt;=Premissas!$B$13,B12=DATE(YEAR(B12),MONTH(B12)+1,0)),X12,0)</f>
-        <v>153.6705</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
         <f aca="false">Z11-AA11+C12/Premissas!$B$18*Premissas!$B$20</f>
-        <v>24.3</v>
+        <v>9.9</v>
       </c>
       <c r="AA12" s="12" t="n">
         <f aca="false">IF(OR(Z12&gt;=Premissas!$B$14,B12=DATE(YEAR(B12),MONTH(B12)+1,0)),Z12,0)</f>
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="15" t="n">
         <f aca="false">IF(AA12&gt;0,IF(DAY(B12)&lt;=Premissas!$B$12,DATE(YEAR(B12),MONTH(B12),Premissas!$B$16),DATE(YEAR(B12),MONTH(B12)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4522,7 +4525,7 @@
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">IF(A13&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A13&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A13&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D13" s="15" t="n">
         <f aca="false">IF(Y13&gt;0,IF(DAY(B13)&lt;=Premissas!$B$12,DATE(YEAR(B13),MONTH(B13),Premissas!$B$16),DATE(YEAR(B13),MONTH(B13)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4538,19 +4541,19 @@
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">C13/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H13" s="29" t="n">
         <f aca="false">C13/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="12" t="n">
         <f aca="false">-IF($A13-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-186.368028</v>
+        <v>-0</v>
       </c>
       <c r="J13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4562,11 +4565,11 @@
       </c>
       <c r="M13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>135.5042838</v>
+        <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
         <f aca="false">-IF($A13-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-42</v>
+        <v>-0</v>
       </c>
       <c r="O13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A13-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4582,11 +4585,11 @@
       </c>
       <c r="R13" s="12" t="n">
         <f aca="false">E13+F13+SUM(I13:Q13)</f>
-        <v>-92.8637442</v>
+        <v>24.68338103</v>
       </c>
       <c r="S13" s="12" t="n">
         <f aca="false">S12+R13</f>
-        <v>-369.4620819</v>
+        <v>-423.09202474</v>
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(AND($A13&gt;$B$100,S13&gt;=0),1,0)</f>
@@ -4594,31 +4597,31 @@
       </c>
       <c r="U13" s="12" t="n">
         <f aca="false">S13-SUM($E$5:E13)-(1+Premissas!$B$17)*SUM($C$5:C13)</f>
-        <v>-932.9205819</v>
+        <v>-861.33752474</v>
       </c>
       <c r="V13" s="12" t="n">
         <f aca="false">(G13+H13)*Premissas!$B$21</f>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="W13" s="15" t="n">
         <f aca="false">IF(V13&gt;0,DATE(YEAR(B13),MONTH(B13)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="X13" s="12" t="n">
         <f aca="false">X12-Y12+C13*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y13" s="12" t="n">
         <f aca="false">IF(OR(X13&gt;=Premissas!$B$13,B13=DATE(YEAR(B13),MONTH(B13)+1,0)),X13,0)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Z13" s="12" t="n">
         <f aca="false">Z12-AA12+C13/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA13" s="12" t="n">
         <f aca="false">IF(OR(Z13&gt;=Premissas!$B$14,B13=DATE(YEAR(B13),MONTH(B13)+1,0)),Z13,0)</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AB13" s="15" t="n">
         <f aca="false">IF(AA13&gt;0,IF(DAY(B13)&lt;=Premissas!$B$12,DATE(YEAR(B13),MONTH(B13),Premissas!$B$16),DATE(YEAR(B13),MONTH(B13)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4635,7 +4638,7 @@
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">IF(A14&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A14&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A14&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D14" s="15" t="n">
         <f aca="false">IF(Y14&gt;0,IF(DAY(B14)&lt;=Premissas!$B$12,DATE(YEAR(B14),MONTH(B14),Premissas!$B$16),DATE(YEAR(B14),MONTH(B14)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4651,23 +4654,23 @@
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">C14/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.8</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H14" s="29" t="n">
         <f aca="false">C14/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">-IF($A14-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-186.368028</v>
+        <v>-0</v>
       </c>
       <c r="J14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>26.92732476</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-7</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4675,15 +4678,15 @@
       </c>
       <c r="M14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>135.5042838</v>
+        <v>124.21226015</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">-IF($A14-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-42</v>
+        <v>-0</v>
       </c>
       <c r="O14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-20.5365</v>
+        <v>-15.0601</v>
       </c>
       <c r="P14" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A14-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A14-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4695,11 +4698,11 @@
       </c>
       <c r="R14" s="12" t="n">
         <f aca="false">E14+F14+SUM(I14:Q14)</f>
-        <v>-93.47291944</v>
+        <v>104.018826816667</v>
       </c>
       <c r="S14" s="12" t="n">
         <f aca="false">S13+R14</f>
-        <v>-462.93500134</v>
+        <v>-319.073197923333</v>
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(AND($A14&gt;$B$100,S14&gt;=0),1,0)</f>
@@ -4707,11 +4710,11 @@
       </c>
       <c r="U14" s="12" t="n">
         <f aca="false">S14-SUM($E$5:E14)-(1+Premissas!$B$17)*SUM($C$5:C14)</f>
-        <v>-1094.69150134</v>
+        <v>-819.925197923333</v>
       </c>
       <c r="V14" s="12" t="n">
         <f aca="false">(G14+H14)*Premissas!$B$21</f>
-        <v>0.16</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W14" s="15" t="n">
         <f aca="false">IF(V14&gt;0,DATE(YEAR(B14),MONTH(B14)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4719,7 +4722,7 @@
       </c>
       <c r="X14" s="12" t="n">
         <f aca="false">X13-Y13+C14*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y14" s="12" t="n">
         <f aca="false">IF(OR(X14&gt;=Premissas!$B$13,B14=DATE(YEAR(B14),MONTH(B14)+1,0)),X14,0)</f>
@@ -4727,7 +4730,7 @@
       </c>
       <c r="Z14" s="12" t="n">
         <f aca="false">Z13-AA13+C14/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA14" s="12" t="n">
         <f aca="false">IF(OR(Z14&gt;=Premissas!$B$14,B14=DATE(YEAR(B14),MONTH(B14)+1,0)),Z14,0)</f>
@@ -4748,7 +4751,7 @@
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">IF(A15&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A15&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A15&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D15" s="15" t="n">
         <f aca="false">IF(Y15&gt;0,IF(DAY(B15)&lt;=Premissas!$B$12,DATE(YEAR(B15),MONTH(B15),Premissas!$B$16),DATE(YEAR(B15),MONTH(B15)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4764,23 +4767,23 @@
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">C15/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.8</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H15" s="29" t="n">
         <f aca="false">C15/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I15" s="12" t="n">
         <f aca="false">-IF($A15-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-186.368028</v>
+        <v>-170.837359</v>
       </c>
       <c r="J15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>26.92732476</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-7</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4788,15 +4791,15 @@
       </c>
       <c r="M15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>135.5042838</v>
+        <v>124.21226015</v>
       </c>
       <c r="N15" s="12" t="n">
         <f aca="false">-IF($A15-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-42</v>
+        <v>-38.5</v>
       </c>
       <c r="O15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-20.5365</v>
+        <v>-15.0601</v>
       </c>
       <c r="P15" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A15-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A15-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4808,11 +4811,11 @@
       </c>
       <c r="R15" s="12" t="n">
         <f aca="false">E15+F15+SUM(I15:Q15)</f>
-        <v>-93.47291944</v>
+        <v>-105.318532183333</v>
       </c>
       <c r="S15" s="12" t="n">
         <f aca="false">S14+R15</f>
-        <v>-556.40792078</v>
+        <v>-424.391730106667</v>
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(AND($A15&gt;$B$100,S15&gt;=0),1,0)</f>
@@ -4820,11 +4823,11 @@
       </c>
       <c r="U15" s="12" t="n">
         <f aca="false">S15-SUM($E$5:E15)-(1+Premissas!$B$17)*SUM($C$5:C15)</f>
-        <v>-1256.46242078</v>
+        <v>-987.850230106667</v>
       </c>
       <c r="V15" s="12" t="n">
         <f aca="false">(G15+H15)*Premissas!$B$21</f>
-        <v>0.16</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W15" s="15" t="n">
         <f aca="false">IF(V15&gt;0,DATE(YEAR(B15),MONTH(B15)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4832,23 +4835,23 @@
       </c>
       <c r="X15" s="12" t="n">
         <f aca="false">X14-Y14+C15*(1+Premissas!$B$17)</f>
-        <v>136.596</v>
+        <v>125.213</v>
       </c>
       <c r="Y15" s="12" t="n">
         <f aca="false">IF(OR(X15&gt;=Premissas!$B$13,B15=DATE(YEAR(B15),MONTH(B15)+1,0)),X15,0)</f>
-        <v>136.596</v>
+        <v>125.213</v>
       </c>
       <c r="Z15" s="12" t="n">
         <f aca="false">Z14-AA14+C15/Premissas!$B$18*Premissas!$B$20</f>
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA15" s="12" t="n">
         <f aca="false">IF(OR(Z15&gt;=Premissas!$B$14,B15=DATE(YEAR(B15),MONTH(B15)+1,0)),Z15,0)</f>
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="15" t="n">
         <f aca="false">IF(AA15&gt;0,IF(DAY(B15)&lt;=Premissas!$B$12,DATE(YEAR(B15),MONTH(B15),Premissas!$B$16),DATE(YEAR(B15),MONTH(B15)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4861,7 +4864,7 @@
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">IF(A16&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A16&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A16&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D16" s="15" t="n">
         <f aca="false">IF(Y16&gt;0,IF(DAY(B16)&lt;=Premissas!$B$12,DATE(YEAR(B16),MONTH(B16),Premissas!$B$16),DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4877,23 +4880,23 @@
       </c>
       <c r="G16" s="29" t="n">
         <f aca="false">C16/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.8</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H16" s="29" t="n">
         <f aca="false">C16/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">-IF($A16-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-186.368028</v>
+        <v>-170.837359</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>26.92732476</v>
+        <v>24.68338103</v>
       </c>
       <c r="K16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-7</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4901,15 +4904,15 @@
       </c>
       <c r="M16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>135.5042838</v>
+        <v>124.21226015</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">-IF($A16-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-42</v>
+        <v>-38.5</v>
       </c>
       <c r="O16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-20.5365</v>
+        <v>-15.0601</v>
       </c>
       <c r="P16" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A16-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A16-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4921,11 +4924,11 @@
       </c>
       <c r="R16" s="12" t="n">
         <f aca="false">E16+F16+SUM(I16:Q16)</f>
-        <v>-93.47291944</v>
+        <v>-80.6351511533333</v>
       </c>
       <c r="S16" s="12" t="n">
         <f aca="false">S15+R16</f>
-        <v>-649.88084022</v>
+        <v>-505.02688126</v>
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(AND($A16&gt;$B$100,S16&gt;=0),1,0)</f>
@@ -4933,11 +4936,11 @@
       </c>
       <c r="U16" s="12" t="n">
         <f aca="false">S16-SUM($E$5:E16)-(1+Premissas!$B$17)*SUM($C$5:C16)</f>
-        <v>-1418.23334022</v>
+        <v>-1131.09188126</v>
       </c>
       <c r="V16" s="12" t="n">
         <f aca="false">(G16+H16)*Premissas!$B$21</f>
-        <v>0.16</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W16" s="15" t="n">
         <f aca="false">IF(V16&gt;0,DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4945,7 +4948,7 @@
       </c>
       <c r="X16" s="12" t="n">
         <f aca="false">X15-Y15+C16*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y16" s="12" t="n">
         <f aca="false">IF(OR(X16&gt;=Premissas!$B$13,B16=DATE(YEAR(B16),MONTH(B16)+1,0)),X16,0)</f>
@@ -4953,15 +4956,15 @@
       </c>
       <c r="Z16" s="12" t="n">
         <f aca="false">Z15-AA15+C16/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>29.7</v>
       </c>
       <c r="AA16" s="12" t="n">
         <f aca="false">IF(OR(Z16&gt;=Premissas!$B$14,B16=DATE(YEAR(B16),MONTH(B16)+1,0)),Z16,0)</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AB16" s="15" t="n">
         <f aca="false">IF(AA16&gt;0,IF(DAY(B16)&lt;=Premissas!$B$12,DATE(YEAR(B16),MONTH(B16),Premissas!$B$16),DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4974,11 +4977,11 @@
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(A17&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A17&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A17&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">IF(Y17&gt;0,IF(DAY(B17)&lt;=Premissas!$B$12,DATE(YEAR(B17),MONTH(B17),Premissas!$B$16),DATE(YEAR(B17),MONTH(B17)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E17" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A17,$Y$5:$Y$94)</f>
@@ -4990,23 +4993,23 @@
       </c>
       <c r="G17" s="29" t="n">
         <f aca="false">C17/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H17" s="29" t="n">
         <f aca="false">C17/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I17" s="12" t="n">
         <f aca="false">-IF($A17-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-186.368028</v>
+        <v>-170.837359</v>
       </c>
       <c r="J17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>26.92732476</v>
+        <v>24.68338103</v>
       </c>
       <c r="K17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-7</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5014,15 +5017,15 @@
       </c>
       <c r="M17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N17" s="12" t="n">
         <f aca="false">-IF($A17-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-42</v>
+        <v>-38.5</v>
       </c>
       <c r="O17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-20.5365</v>
+        <v>-15.0601</v>
       </c>
       <c r="P17" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A17-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A17-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5034,11 +5037,11 @@
       </c>
       <c r="R17" s="12" t="n">
         <f aca="false">E17+F17+SUM(I17:Q17)</f>
-        <v>-228.97720324</v>
+        <v>-80.6351511533333</v>
       </c>
       <c r="S17" s="12" t="n">
         <f aca="false">S16+R17</f>
-        <v>-878.85804346</v>
+        <v>-585.662032413333</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(AND($A17&gt;$B$100,S17&gt;=0),1,0)</f>
@@ -5046,27 +5049,27 @@
       </c>
       <c r="U17" s="12" t="n">
         <f aca="false">S17-SUM($E$5:E17)-(1+Premissas!$B$17)*SUM($C$5:C17)</f>
-        <v>-1647.21054346</v>
+        <v>-1274.33353241333</v>
       </c>
       <c r="V17" s="12" t="n">
         <f aca="false">(G17+H17)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">IF(V17&gt;0,DATE(YEAR(B17),MONTH(B17)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="X17" s="12" t="n">
         <f aca="false">X16-Y16+C17*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>125.213</v>
       </c>
       <c r="Y17" s="12" t="n">
         <f aca="false">IF(OR(X17&gt;=Premissas!$B$13,B17=DATE(YEAR(B17),MONTH(B17)+1,0)),X17,0)</f>
-        <v>0</v>
+        <v>125.213</v>
       </c>
       <c r="Z17" s="12" t="n">
         <f aca="false">Z16-AA16+C17/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA17" s="12" t="n">
         <f aca="false">IF(OR(Z17&gt;=Premissas!$B$14,B17=DATE(YEAR(B17),MONTH(B17)+1,0)),Z17,0)</f>
@@ -5087,7 +5090,7 @@
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">IF(A18&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A18&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A18&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">IF(Y18&gt;0,IF(DAY(B18)&lt;=Premissas!$B$12,DATE(YEAR(B18),MONTH(B18),Premissas!$B$16),DATE(YEAR(B18),MONTH(B18)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5103,23 +5106,23 @@
       </c>
       <c r="G18" s="29" t="n">
         <f aca="false">C18/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">C18/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="12" t="n">
         <f aca="false">-IF($A18-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>26.92732476</v>
+        <v>24.68338103</v>
       </c>
       <c r="K18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-7</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5127,15 +5130,15 @@
       </c>
       <c r="M18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N18" s="12" t="n">
         <f aca="false">-IF($A18-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-20.5365</v>
+        <v>-15.0601</v>
       </c>
       <c r="P18" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A18-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A18-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5147,11 +5150,11 @@
       </c>
       <c r="R18" s="12" t="n">
         <f aca="false">E18+F18+SUM(I18:Q18)</f>
-        <v>-0.609175240000003</v>
+        <v>-80.6351511533333</v>
       </c>
       <c r="S18" s="12" t="n">
         <f aca="false">S17+R18</f>
-        <v>-879.4672187</v>
+        <v>-666.297183566667</v>
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(AND($A18&gt;$B$100,S18&gt;=0),1,0)</f>
@@ -5159,19 +5162,19 @@
       </c>
       <c r="U18" s="12" t="n">
         <f aca="false">S18-SUM($E$5:E18)-(1+Premissas!$B$17)*SUM($C$5:C18)</f>
-        <v>-1647.8197187</v>
+        <v>-1417.57518356667</v>
       </c>
       <c r="V18" s="12" t="n">
         <f aca="false">(G18+H18)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">IF(V18&gt;0,DATE(YEAR(B18),MONTH(B18)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="X18" s="12" t="n">
         <f aca="false">X17-Y17+C18*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y18" s="12" t="n">
         <f aca="false">IF(OR(X18&gt;=Premissas!$B$13,B18=DATE(YEAR(B18),MONTH(B18)+1,0)),X18,0)</f>
@@ -5179,7 +5182,7 @@
       </c>
       <c r="Z18" s="12" t="n">
         <f aca="false">Z17-AA17+C18/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA18" s="12" t="n">
         <f aca="false">IF(OR(Z18&gt;=Premissas!$B$14,B18=DATE(YEAR(B18),MONTH(B18)+1,0)),Z18,0)</f>
@@ -5200,11 +5203,11 @@
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">IF(A19&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A19&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A19&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">IF(Y19&gt;0,IF(DAY(B19)&lt;=Premissas!$B$12,DATE(YEAR(B19),MONTH(B19),Premissas!$B$16),DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E19" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A19,$Y$5:$Y$94)</f>
@@ -5216,23 +5219,23 @@
       </c>
       <c r="G19" s="29" t="n">
         <f aca="false">C19/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H19" s="29" t="n">
         <f aca="false">C19/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I19" s="12" t="n">
         <f aca="false">-IF($A19-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5240,15 +5243,15 @@
       </c>
       <c r="M19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N19" s="12" t="n">
         <f aca="false">-IF($A19-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P19" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A19-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A19-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5260,11 +5263,11 @@
       </c>
       <c r="R19" s="12" t="n">
         <f aca="false">E19+F19+SUM(I19:Q19)</f>
-        <v>0</v>
+        <v>-80.6351511533333</v>
       </c>
       <c r="S19" s="12" t="n">
         <f aca="false">S18+R19</f>
-        <v>-879.4672187</v>
+        <v>-746.93233472</v>
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(AND($A19&gt;$B$100,S19&gt;=0),1,0)</f>
@@ -5272,35 +5275,35 @@
       </c>
       <c r="U19" s="12" t="n">
         <f aca="false">S19-SUM($E$5:E19)-(1+Premissas!$B$17)*SUM($C$5:C19)</f>
-        <v>-1647.8197187</v>
+        <v>-1560.81683472</v>
       </c>
       <c r="V19" s="12" t="n">
         <f aca="false">(G19+H19)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">IF(V19&gt;0,DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="X19" s="12" t="n">
         <f aca="false">X18-Y18+C19*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>125.213</v>
       </c>
       <c r="Y19" s="12" t="n">
         <f aca="false">IF(OR(X19&gt;=Premissas!$B$13,B19=DATE(YEAR(B19),MONTH(B19)+1,0)),X19,0)</f>
-        <v>0</v>
+        <v>125.213</v>
       </c>
       <c r="Z19" s="12" t="n">
         <f aca="false">Z18-AA18+C19/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>29.7</v>
       </c>
       <c r="AA19" s="12" t="n">
         <f aca="false">IF(OR(Z19&gt;=Premissas!$B$14,B19=DATE(YEAR(B19),MONTH(B19)+1,0)),Z19,0)</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AB19" s="15" t="n">
         <f aca="false">IF(AA19&gt;0,IF(DAY(B19)&lt;=Premissas!$B$12,DATE(YEAR(B19),MONTH(B19),Premissas!$B$16),DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5313,7 +5316,7 @@
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">IF(A20&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A20&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A20&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">IF(Y20&gt;0,IF(DAY(B20)&lt;=Premissas!$B$12,DATE(YEAR(B20),MONTH(B20),Premissas!$B$16),DATE(YEAR(B20),MONTH(B20)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5329,23 +5332,23 @@
       </c>
       <c r="G20" s="29" t="n">
         <f aca="false">C20/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>0</v>
+        <v>2.56666666666667</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">C20/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I20" s="12" t="n">
         <f aca="false">-IF($A20-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5353,15 +5356,15 @@
       </c>
       <c r="M20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>0</v>
+        <v>124.21226015</v>
       </c>
       <c r="N20" s="12" t="n">
         <f aca="false">-IF($A20-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P20" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A20-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A20-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5373,11 +5376,11 @@
       </c>
       <c r="R20" s="12" t="n">
         <f aca="false">E20+F20+SUM(I20:Q20)</f>
-        <v>0</v>
+        <v>-80.6351511533333</v>
       </c>
       <c r="S20" s="12" t="n">
         <f aca="false">S19+R20</f>
-        <v>-879.4672187</v>
+        <v>-827.567485873333</v>
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(AND($A20&gt;$B$100,S20&gt;=0),1,0)</f>
@@ -5385,19 +5388,19 @@
       </c>
       <c r="U20" s="12" t="n">
         <f aca="false">S20-SUM($E$5:E20)-(1+Premissas!$B$17)*SUM($C$5:C20)</f>
-        <v>-1647.8197187</v>
+        <v>-1704.05848587333</v>
       </c>
       <c r="V20" s="12" t="n">
         <f aca="false">(G20+H20)*Premissas!$B$21</f>
-        <v>0</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">IF(V20&gt;0,DATE(YEAR(B20),MONTH(B20)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="X20" s="12" t="n">
         <f aca="false">X19-Y19+C20*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y20" s="12" t="n">
         <f aca="false">IF(OR(X20&gt;=Premissas!$B$13,B20=DATE(YEAR(B20),MONTH(B20)+1,0)),X20,0)</f>
@@ -5405,7 +5408,7 @@
       </c>
       <c r="Z20" s="12" t="n">
         <f aca="false">Z19-AA19+C20/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA20" s="12" t="n">
         <f aca="false">IF(OR(Z20&gt;=Premissas!$B$14,B20=DATE(YEAR(B20),MONTH(B20)+1,0)),Z20,0)</f>
@@ -5450,19 +5453,19 @@
       </c>
       <c r="I21" s="12" t="n">
         <f aca="false">-IF($A21-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-0</v>
+        <v>-170.837359</v>
       </c>
       <c r="J21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.6</v>
+        <v>-0</v>
       </c>
       <c r="L21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>331.8945</v>
+        <v>243.3893</v>
       </c>
       <c r="M21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5470,11 +5473,11 @@
       </c>
       <c r="N21" s="12" t="n">
         <f aca="false">-IF($A21-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-0</v>
+        <v>-38.5</v>
       </c>
       <c r="O21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-16.4292</v>
+        <v>-0</v>
       </c>
       <c r="P21" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A21-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A21-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5486,11 +5489,11 @@
       </c>
       <c r="R21" s="12" t="n">
         <f aca="false">E21+F21+SUM(I21:Q21)</f>
-        <v>309.8653</v>
+        <v>58.73532203</v>
       </c>
       <c r="S21" s="12" t="n">
         <f aca="false">S20+R21</f>
-        <v>-569.6019187</v>
+        <v>-768.832163843333</v>
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(AND($A21&gt;$B$100,S21&gt;=0),1,0)</f>
@@ -5498,7 +5501,7 @@
       </c>
       <c r="U21" s="12" t="n">
         <f aca="false">S21-SUM($E$5:E21)-(1+Premissas!$B$17)*SUM($C$5:C21)</f>
-        <v>-1337.9544187</v>
+        <v>-1645.32316384333</v>
       </c>
       <c r="V21" s="12" t="n">
         <f aca="false">(G21+H21)*Premissas!$B$21</f>
@@ -5510,7 +5513,7 @@
       </c>
       <c r="X21" s="12" t="n">
         <f aca="false">X20-Y20+C21*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y21" s="12" t="n">
         <f aca="false">IF(OR(X21&gt;=Premissas!$B$13,B21=DATE(YEAR(B21),MONTH(B21)+1,0)),X21,0)</f>
@@ -5518,7 +5521,7 @@
       </c>
       <c r="Z21" s="12" t="n">
         <f aca="false">Z20-AA20+C21/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA21" s="12" t="n">
         <f aca="false">IF(OR(Z21&gt;=Premissas!$B$14,B21=DATE(YEAR(B21),MONTH(B21)+1,0)),Z21,0)</f>
@@ -5567,15 +5570,15 @@
       </c>
       <c r="J22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>0</v>
+        <v>24.68338103</v>
       </c>
       <c r="K22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.6</v>
+        <v>-0</v>
       </c>
       <c r="L22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>331.8945</v>
+        <v>243.3893</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5587,7 +5590,7 @@
       </c>
       <c r="O22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-16.4292</v>
+        <v>-0</v>
       </c>
       <c r="P22" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A22-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A22-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5599,11 +5602,11 @@
       </c>
       <c r="R22" s="12" t="n">
         <f aca="false">E22+F22+SUM(I22:Q22)</f>
-        <v>309.8653</v>
+        <v>268.07268103</v>
       </c>
       <c r="S22" s="12" t="n">
         <f aca="false">S21+R22</f>
-        <v>-259.7366187</v>
+        <v>-500.759482813333</v>
       </c>
       <c r="T22" s="15" t="n">
         <f aca="false">IF(AND($A22&gt;$B$100,S22&gt;=0),1,0)</f>
@@ -5611,7 +5614,7 @@
       </c>
       <c r="U22" s="12" t="n">
         <f aca="false">S22-SUM($E$5:E22)-(1+Premissas!$B$17)*SUM($C$5:C22)</f>
-        <v>-1028.0891187</v>
+        <v>-1377.25048281333</v>
       </c>
       <c r="V22" s="12" t="n">
         <f aca="false">(G22+H22)*Premissas!$B$21</f>
@@ -5623,7 +5626,7 @@
       </c>
       <c r="X22" s="12" t="n">
         <f aca="false">X21-Y21+C22*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y22" s="12" t="n">
         <f aca="false">IF(OR(X22&gt;=Premissas!$B$13,B22=DATE(YEAR(B22),MONTH(B22)+1,0)),X22,0)</f>
@@ -5631,7 +5634,7 @@
       </c>
       <c r="Z22" s="12" t="n">
         <f aca="false">Z21-AA21+C22/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA22" s="12" t="n">
         <f aca="false">IF(OR(Z22&gt;=Premissas!$B$14,B22=DATE(YEAR(B22),MONTH(B22)+1,0)),Z22,0)</f>
@@ -5684,11 +5687,11 @@
       </c>
       <c r="K23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.6</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>331.8945</v>
+        <v>243.3893</v>
       </c>
       <c r="M23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5700,7 +5703,7 @@
       </c>
       <c r="O23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-16.4292</v>
+        <v>-15.0601</v>
       </c>
       <c r="P23" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A23-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A23-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5712,19 +5715,19 @@
       </c>
       <c r="R23" s="12" t="n">
         <f aca="false">E23+F23+SUM(I23:Q23)</f>
-        <v>309.8653</v>
+        <v>223.195866666667</v>
       </c>
       <c r="S23" s="12" t="n">
         <f aca="false">S22+R23</f>
-        <v>50.1286813000003</v>
+        <v>-277.563616146667</v>
       </c>
       <c r="T23" s="15" t="n">
         <f aca="false">IF(AND($A23&gt;$B$100,S23&gt;=0),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="12" t="n">
         <f aca="false">S23-SUM($E$5:E23)-(1+Premissas!$B$17)*SUM($C$5:C23)</f>
-        <v>-718.2238187</v>
+        <v>-1154.05461614667</v>
       </c>
       <c r="V23" s="12" t="n">
         <f aca="false">(G23+H23)*Premissas!$B$21</f>
@@ -5736,7 +5739,7 @@
       </c>
       <c r="X23" s="12" t="n">
         <f aca="false">X22-Y22+C23*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y23" s="12" t="n">
         <f aca="false">IF(OR(X23&gt;=Premissas!$B$13,B23=DATE(YEAR(B23),MONTH(B23)+1,0)),X23,0)</f>
@@ -5744,7 +5747,7 @@
       </c>
       <c r="Z23" s="12" t="n">
         <f aca="false">Z22-AA22+C23/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA23" s="12" t="n">
         <f aca="false">IF(OR(Z23&gt;=Premissas!$B$14,B23=DATE(YEAR(B23),MONTH(B23)+1,0)),Z23,0)</f>
@@ -5797,11 +5800,11 @@
       </c>
       <c r="K24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.6</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>331.8945</v>
+        <v>243.3893</v>
       </c>
       <c r="M24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5813,7 +5816,7 @@
       </c>
       <c r="O24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-16.4292</v>
+        <v>-15.0601</v>
       </c>
       <c r="P24" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A24-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A24-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5825,19 +5828,19 @@
       </c>
       <c r="R24" s="12" t="n">
         <f aca="false">E24+F24+SUM(I24:Q24)</f>
-        <v>309.8653</v>
+        <v>223.195866666667</v>
       </c>
       <c r="S24" s="12" t="n">
         <f aca="false">S23+R24</f>
-        <v>359.9939813</v>
+        <v>-54.3677494800001</v>
       </c>
       <c r="T24" s="15" t="n">
         <f aca="false">IF(AND($A24&gt;$B$100,S24&gt;=0),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" s="12" t="n">
         <f aca="false">S24-SUM($E$5:E24)-(1+Premissas!$B$17)*SUM($C$5:C24)</f>
-        <v>-408.3585187</v>
+        <v>-930.85874948</v>
       </c>
       <c r="V24" s="12" t="n">
         <f aca="false">(G24+H24)*Premissas!$B$21</f>
@@ -5849,7 +5852,7 @@
       </c>
       <c r="X24" s="12" t="n">
         <f aca="false">X23-Y23+C24*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y24" s="12" t="n">
         <f aca="false">IF(OR(X24&gt;=Premissas!$B$13,B24=DATE(YEAR(B24),MONTH(B24)+1,0)),X24,0)</f>
@@ -5857,7 +5860,7 @@
       </c>
       <c r="Z24" s="12" t="n">
         <f aca="false">Z23-AA23+C24/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA24" s="12" t="n">
         <f aca="false">IF(OR(Z24&gt;=Premissas!$B$14,B24=DATE(YEAR(B24),MONTH(B24)+1,0)),Z24,0)</f>
@@ -5910,11 +5913,11 @@
       </c>
       <c r="K25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.6</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>331.8945</v>
+        <v>243.3893</v>
       </c>
       <c r="M25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5926,7 +5929,7 @@
       </c>
       <c r="O25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-16.4292</v>
+        <v>-15.0601</v>
       </c>
       <c r="P25" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A25-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A25-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5938,11 +5941,11 @@
       </c>
       <c r="R25" s="12" t="n">
         <f aca="false">E25+F25+SUM(I25:Q25)</f>
-        <v>309.8653</v>
+        <v>223.195866666667</v>
       </c>
       <c r="S25" s="12" t="n">
         <f aca="false">S24+R25</f>
-        <v>669.8592813</v>
+        <v>168.828117186667</v>
       </c>
       <c r="T25" s="15" t="n">
         <f aca="false">IF(AND($A25&gt;$B$100,S25&gt;=0),1,0)</f>
@@ -5950,7 +5953,7 @@
       </c>
       <c r="U25" s="12" t="n">
         <f aca="false">S25-SUM($E$5:E25)-(1+Premissas!$B$17)*SUM($C$5:C25)</f>
-        <v>-98.4932186999998</v>
+        <v>-707.662882813334</v>
       </c>
       <c r="V25" s="12" t="n">
         <f aca="false">(G25+H25)*Premissas!$B$21</f>
@@ -5962,7 +5965,7 @@
       </c>
       <c r="X25" s="12" t="n">
         <f aca="false">X24-Y24+C25*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y25" s="12" t="n">
         <f aca="false">IF(OR(X25&gt;=Premissas!$B$13,B25=DATE(YEAR(B25),MONTH(B25)+1,0)),X25,0)</f>
@@ -5970,7 +5973,7 @@
       </c>
       <c r="Z25" s="12" t="n">
         <f aca="false">Z24-AA24+C25/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA25" s="12" t="n">
         <f aca="false">IF(OR(Z25&gt;=Premissas!$B$14,B25=DATE(YEAR(B25),MONTH(B25)+1,0)),Z25,0)</f>
@@ -6023,11 +6026,11 @@
       </c>
       <c r="K26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6039,7 +6042,7 @@
       </c>
       <c r="O26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P26" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A26-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A26-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6051,11 +6054,11 @@
       </c>
       <c r="R26" s="12" t="n">
         <f aca="false">E26+F26+SUM(I26:Q26)</f>
-        <v>0</v>
+        <v>223.195866666667</v>
       </c>
       <c r="S26" s="12" t="n">
         <f aca="false">S25+R26</f>
-        <v>669.8592813</v>
+        <v>392.023983853333</v>
       </c>
       <c r="T26" s="15" t="n">
         <f aca="false">IF(AND($A26&gt;$B$100,S26&gt;=0),1,0)</f>
@@ -6063,7 +6066,7 @@
       </c>
       <c r="U26" s="12" t="n">
         <f aca="false">S26-SUM($E$5:E26)-(1+Premissas!$B$17)*SUM($C$5:C26)</f>
-        <v>-98.4932186999998</v>
+        <v>-484.467016146667</v>
       </c>
       <c r="V26" s="12" t="n">
         <f aca="false">(G26+H26)*Premissas!$B$21</f>
@@ -6075,7 +6078,7 @@
       </c>
       <c r="X26" s="12" t="n">
         <f aca="false">X25-Y25+C26*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y26" s="12" t="n">
         <f aca="false">IF(OR(X26&gt;=Premissas!$B$13,B26=DATE(YEAR(B26),MONTH(B26)+1,0)),X26,0)</f>
@@ -6083,7 +6086,7 @@
       </c>
       <c r="Z26" s="12" t="n">
         <f aca="false">Z25-AA25+C26/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA26" s="12" t="n">
         <f aca="false">IF(OR(Z26&gt;=Premissas!$B$14,B26=DATE(YEAR(B26),MONTH(B26)+1,0)),Z26,0)</f>
@@ -6136,11 +6139,11 @@
       </c>
       <c r="K27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6152,7 +6155,7 @@
       </c>
       <c r="O27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P27" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A27-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A27-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6164,11 +6167,11 @@
       </c>
       <c r="R27" s="12" t="n">
         <f aca="false">E27+F27+SUM(I27:Q27)</f>
-        <v>0</v>
+        <v>223.195866666667</v>
       </c>
       <c r="S27" s="12" t="n">
         <f aca="false">S26+R27</f>
-        <v>669.8592813</v>
+        <v>615.21985052</v>
       </c>
       <c r="T27" s="15" t="n">
         <f aca="false">IF(AND($A27&gt;$B$100,S27&gt;=0),1,0)</f>
@@ -6176,7 +6179,7 @@
       </c>
       <c r="U27" s="12" t="n">
         <f aca="false">S27-SUM($E$5:E27)-(1+Premissas!$B$17)*SUM($C$5:C27)</f>
-        <v>-98.4932186999998</v>
+        <v>-261.27114948</v>
       </c>
       <c r="V27" s="12" t="n">
         <f aca="false">(G27+H27)*Premissas!$B$21</f>
@@ -6188,7 +6191,7 @@
       </c>
       <c r="X27" s="12" t="n">
         <f aca="false">X26-Y26+C27*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y27" s="12" t="n">
         <f aca="false">IF(OR(X27&gt;=Premissas!$B$13,B27=DATE(YEAR(B27),MONTH(B27)+1,0)),X27,0)</f>
@@ -6196,7 +6199,7 @@
       </c>
       <c r="Z27" s="12" t="n">
         <f aca="false">Z26-AA26+C27/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA27" s="12" t="n">
         <f aca="false">IF(OR(Z27&gt;=Premissas!$B$14,B27=DATE(YEAR(B27),MONTH(B27)+1,0)),Z27,0)</f>
@@ -6249,11 +6252,11 @@
       </c>
       <c r="K28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>265.5156</v>
+        <v>0</v>
       </c>
       <c r="M28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6265,7 +6268,7 @@
       </c>
       <c r="O28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P28" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A28-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A28-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6277,11 +6280,11 @@
       </c>
       <c r="R28" s="12" t="n">
         <f aca="false">E28+F28+SUM(I28:Q28)</f>
-        <v>265.5156</v>
+        <v>-20.1934333333333</v>
       </c>
       <c r="S28" s="12" t="n">
         <f aca="false">S27+R28</f>
-        <v>935.3748813</v>
+        <v>595.026417186666</v>
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(AND($A28&gt;$B$100,S28&gt;=0),1,0)</f>
@@ -6289,7 +6292,7 @@
       </c>
       <c r="U28" s="12" t="n">
         <f aca="false">S28-SUM($E$5:E28)-(1+Premissas!$B$17)*SUM($C$5:C28)</f>
-        <v>167.0223813</v>
+        <v>-281.464582813334</v>
       </c>
       <c r="V28" s="12" t="n">
         <f aca="false">(G28+H28)*Premissas!$B$21</f>
@@ -6301,7 +6304,7 @@
       </c>
       <c r="X28" s="12" t="n">
         <f aca="false">X27-Y27+C28*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y28" s="12" t="n">
         <f aca="false">IF(OR(X28&gt;=Premissas!$B$13,B28=DATE(YEAR(B28),MONTH(B28)+1,0)),X28,0)</f>
@@ -6309,7 +6312,7 @@
       </c>
       <c r="Z28" s="12" t="n">
         <f aca="false">Z27-AA27+C28/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA28" s="12" t="n">
         <f aca="false">IF(OR(Z28&gt;=Premissas!$B$14,B28=DATE(YEAR(B28),MONTH(B28)+1,0)),Z28,0)</f>
@@ -6362,11 +6365,11 @@
       </c>
       <c r="K29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-0</v>
+        <v>-5.13333333333333</v>
       </c>
       <c r="L29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>265.5156</v>
+        <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6378,7 +6381,7 @@
       </c>
       <c r="O29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-0</v>
+        <v>-15.0601</v>
       </c>
       <c r="P29" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A29-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A29-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6390,11 +6393,11 @@
       </c>
       <c r="R29" s="12" t="n">
         <f aca="false">E29+F29+SUM(I29:Q29)</f>
-        <v>265.5156</v>
+        <v>-20.1934333333333</v>
       </c>
       <c r="S29" s="12" t="n">
         <f aca="false">S28+R29</f>
-        <v>1200.8904813</v>
+        <v>574.832983853333</v>
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(AND($A29&gt;$B$100,S29&gt;=0),1,0)</f>
@@ -6402,7 +6405,7 @@
       </c>
       <c r="U29" s="12" t="n">
         <f aca="false">S29-SUM($E$5:E29)-(1+Premissas!$B$17)*SUM($C$5:C29)</f>
-        <v>432.5379813</v>
+        <v>-301.658016146667</v>
       </c>
       <c r="V29" s="12" t="n">
         <f aca="false">(G29+H29)*Premissas!$B$21</f>
@@ -6414,7 +6417,7 @@
       </c>
       <c r="X29" s="12" t="n">
         <f aca="false">X28-Y28+C29*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y29" s="12" t="n">
         <f aca="false">IF(OR(X29&gt;=Premissas!$B$13,B29=DATE(YEAR(B29),MONTH(B29)+1,0)),X29,0)</f>
@@ -6422,7 +6425,7 @@
       </c>
       <c r="Z29" s="12" t="n">
         <f aca="false">Z28-AA28+C29/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA29" s="12" t="n">
         <f aca="false">IF(OR(Z29&gt;=Premissas!$B$14,B29=DATE(YEAR(B29),MONTH(B29)+1,0)),Z29,0)</f>
@@ -6479,7 +6482,7 @@
       </c>
       <c r="L30" s="12" t="n">
         <f aca="false">IF($A30-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="M30" s="12" t="n">
         <f aca="false">IF($A30-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A30-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6503,11 +6506,11 @@
       </c>
       <c r="R30" s="12" t="n">
         <f aca="false">E30+F30+SUM(I30:Q30)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="S30" s="12" t="n">
         <f aca="false">S29+R30</f>
-        <v>1466.4060813</v>
+        <v>818.222283853333</v>
       </c>
       <c r="T30" s="15" t="n">
         <f aca="false">IF(AND($A30&gt;$B$100,S30&gt;=0),1,0)</f>
@@ -6515,7 +6518,7 @@
       </c>
       <c r="U30" s="12" t="n">
         <f aca="false">S30-SUM($E$5:E30)-(1+Premissas!$B$17)*SUM($C$5:C30)</f>
-        <v>698.0535813</v>
+        <v>-58.2687161466671</v>
       </c>
       <c r="V30" s="12" t="n">
         <f aca="false">(G30+H30)*Premissas!$B$21</f>
@@ -6527,7 +6530,7 @@
       </c>
       <c r="X30" s="12" t="n">
         <f aca="false">X29-Y29+C30*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y30" s="12" t="n">
         <f aca="false">IF(OR(X30&gt;=Premissas!$B$13,B30=DATE(YEAR(B30),MONTH(B30)+1,0)),X30,0)</f>
@@ -6535,7 +6538,7 @@
       </c>
       <c r="Z30" s="12" t="n">
         <f aca="false">Z29-AA29+C30/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA30" s="12" t="n">
         <f aca="false">IF(OR(Z30&gt;=Premissas!$B$14,B30=DATE(YEAR(B30),MONTH(B30)+1,0)),Z30,0)</f>
@@ -6592,7 +6595,7 @@
       </c>
       <c r="L31" s="12" t="n">
         <f aca="false">IF($A31-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="M31" s="12" t="n">
         <f aca="false">IF($A31-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A31-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6616,11 +6619,11 @@
       </c>
       <c r="R31" s="12" t="n">
         <f aca="false">E31+F31+SUM(I31:Q31)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="S31" s="12" t="n">
         <f aca="false">S30+R31</f>
-        <v>1731.9216813</v>
+        <v>1061.61158385333</v>
       </c>
       <c r="T31" s="15" t="n">
         <f aca="false">IF(AND($A31&gt;$B$100,S31&gt;=0),1,0)</f>
@@ -6628,7 +6631,7 @@
       </c>
       <c r="U31" s="12" t="n">
         <f aca="false">S31-SUM($E$5:E31)-(1+Premissas!$B$17)*SUM($C$5:C31)</f>
-        <v>963.5691813</v>
+        <v>185.120583853333</v>
       </c>
       <c r="V31" s="12" t="n">
         <f aca="false">(G31+H31)*Premissas!$B$21</f>
@@ -6640,7 +6643,7 @@
       </c>
       <c r="X31" s="12" t="n">
         <f aca="false">X30-Y30+C31*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y31" s="12" t="n">
         <f aca="false">IF(OR(X31&gt;=Premissas!$B$13,B31=DATE(YEAR(B31),MONTH(B31)+1,0)),X31,0)</f>
@@ -6648,7 +6651,7 @@
       </c>
       <c r="Z31" s="12" t="n">
         <f aca="false">Z30-AA30+C31/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA31" s="12" t="n">
         <f aca="false">IF(OR(Z31&gt;=Premissas!$B$14,B31=DATE(YEAR(B31),MONTH(B31)+1,0)),Z31,0)</f>
@@ -6705,7 +6708,7 @@
       </c>
       <c r="L32" s="12" t="n">
         <f aca="false">IF($A32-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="M32" s="12" t="n">
         <f aca="false">IF($A32-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A32-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6729,11 +6732,11 @@
       </c>
       <c r="R32" s="12" t="n">
         <f aca="false">E32+F32+SUM(I32:Q32)</f>
-        <v>265.5156</v>
+        <v>243.3893</v>
       </c>
       <c r="S32" s="12" t="n">
         <f aca="false">S31+R32</f>
-        <v>1997.4372813</v>
+        <v>1305.00088385333</v>
       </c>
       <c r="T32" s="15" t="n">
         <f aca="false">IF(AND($A32&gt;$B$100,S32&gt;=0),1,0)</f>
@@ -6741,7 +6744,7 @@
       </c>
       <c r="U32" s="12" t="n">
         <f aca="false">S32-SUM($E$5:E32)-(1+Premissas!$B$17)*SUM($C$5:C32)</f>
-        <v>1229.0847813</v>
+        <v>428.509883853333</v>
       </c>
       <c r="V32" s="12" t="n">
         <f aca="false">(G32+H32)*Premissas!$B$21</f>
@@ -6753,7 +6756,7 @@
       </c>
       <c r="X32" s="12" t="n">
         <f aca="false">X31-Y31+C32*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y32" s="12" t="n">
         <f aca="false">IF(OR(X32&gt;=Premissas!$B$13,B32=DATE(YEAR(B32),MONTH(B32)+1,0)),X32,0)</f>
@@ -6761,7 +6764,7 @@
       </c>
       <c r="Z32" s="12" t="n">
         <f aca="false">Z31-AA31+C32/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA32" s="12" t="n">
         <f aca="false">IF(OR(Z32&gt;=Premissas!$B$14,B32=DATE(YEAR(B32),MONTH(B32)+1,0)),Z32,0)</f>
@@ -6818,7 +6821,7 @@
       </c>
       <c r="L33" s="12" t="n">
         <f aca="false">IF($A33-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M33" s="12" t="n">
         <f aca="false">IF($A33-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A33-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6842,11 +6845,11 @@
       </c>
       <c r="R33" s="12" t="n">
         <f aca="false">E33+F33+SUM(I33:Q33)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="S33" s="12" t="n">
         <f aca="false">S32+R33</f>
-        <v>1997.4372813</v>
+        <v>1548.39018385333</v>
       </c>
       <c r="T33" s="15" t="n">
         <f aca="false">IF(AND($A33&gt;$B$100,S33&gt;=0),1,0)</f>
@@ -6854,7 +6857,7 @@
       </c>
       <c r="U33" s="12" t="n">
         <f aca="false">S33-SUM($E$5:E33)-(1+Premissas!$B$17)*SUM($C$5:C33)</f>
-        <v>1229.0847813</v>
+        <v>671.899183853333</v>
       </c>
       <c r="V33" s="12" t="n">
         <f aca="false">(G33+H33)*Premissas!$B$21</f>
@@ -6866,7 +6869,7 @@
       </c>
       <c r="X33" s="12" t="n">
         <f aca="false">X32-Y32+C33*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y33" s="12" t="n">
         <f aca="false">IF(OR(X33&gt;=Premissas!$B$13,B33=DATE(YEAR(B33),MONTH(B33)+1,0)),X33,0)</f>
@@ -6874,7 +6877,7 @@
       </c>
       <c r="Z33" s="12" t="n">
         <f aca="false">Z32-AA32+C33/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA33" s="12" t="n">
         <f aca="false">IF(OR(Z33&gt;=Premissas!$B$14,B33=DATE(YEAR(B33),MONTH(B33)+1,0)),Z33,0)</f>
@@ -6931,7 +6934,7 @@
       </c>
       <c r="L34" s="12" t="n">
         <f aca="false">IF($A34-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M34" s="12" t="n">
         <f aca="false">IF($A34-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A34-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6955,11 +6958,11 @@
       </c>
       <c r="R34" s="12" t="n">
         <f aca="false">E34+F34+SUM(I34:Q34)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="S34" s="12" t="n">
         <f aca="false">S33+R34</f>
-        <v>1997.4372813</v>
+        <v>1791.77948385333</v>
       </c>
       <c r="T34" s="15" t="n">
         <f aca="false">IF(AND($A34&gt;$B$100,S34&gt;=0),1,0)</f>
@@ -6967,7 +6970,7 @@
       </c>
       <c r="U34" s="12" t="n">
         <f aca="false">S34-SUM($E$5:E34)-(1+Premissas!$B$17)*SUM($C$5:C34)</f>
-        <v>1229.0847813</v>
+        <v>915.288483853333</v>
       </c>
       <c r="V34" s="12" t="n">
         <f aca="false">(G34+H34)*Premissas!$B$21</f>
@@ -6979,7 +6982,7 @@
       </c>
       <c r="X34" s="12" t="n">
         <f aca="false">X33-Y33+C34*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y34" s="12" t="n">
         <f aca="false">IF(OR(X34&gt;=Premissas!$B$13,B34=DATE(YEAR(B34),MONTH(B34)+1,0)),X34,0)</f>
@@ -6987,7 +6990,7 @@
       </c>
       <c r="Z34" s="12" t="n">
         <f aca="false">Z33-AA33+C34/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA34" s="12" t="n">
         <f aca="false">IF(OR(Z34&gt;=Premissas!$B$14,B34=DATE(YEAR(B34),MONTH(B34)+1,0)),Z34,0)</f>
@@ -7044,7 +7047,7 @@
       </c>
       <c r="L35" s="12" t="n">
         <f aca="false">IF($A35-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M35" s="12" t="n">
         <f aca="false">IF($A35-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A35-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -7068,11 +7071,11 @@
       </c>
       <c r="R35" s="12" t="n">
         <f aca="false">E35+F35+SUM(I35:Q35)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="S35" s="12" t="n">
         <f aca="false">S34+R35</f>
-        <v>1997.4372813</v>
+        <v>2035.16878385333</v>
       </c>
       <c r="T35" s="15" t="n">
         <f aca="false">IF(AND($A35&gt;$B$100,S35&gt;=0),1,0)</f>
@@ -7080,7 +7083,7 @@
       </c>
       <c r="U35" s="12" t="n">
         <f aca="false">S35-SUM($E$5:E35)-(1+Premissas!$B$17)*SUM($C$5:C35)</f>
-        <v>1229.0847813</v>
+        <v>1158.67778385333</v>
       </c>
       <c r="V35" s="12" t="n">
         <f aca="false">(G35+H35)*Premissas!$B$21</f>
@@ -7092,7 +7095,7 @@
       </c>
       <c r="X35" s="12" t="n">
         <f aca="false">X34-Y34+C35*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y35" s="12" t="n">
         <f aca="false">IF(OR(X35&gt;=Premissas!$B$13,B35=DATE(YEAR(B35),MONTH(B35)+1,0)),X35,0)</f>
@@ -7100,7 +7103,7 @@
       </c>
       <c r="Z35" s="12" t="n">
         <f aca="false">Z34-AA34+C35/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA35" s="12" t="n">
         <f aca="false">IF(OR(Z35&gt;=Premissas!$B$14,B35=DATE(YEAR(B35),MONTH(B35)+1,0)),Z35,0)</f>
@@ -7157,7 +7160,7 @@
       </c>
       <c r="L36" s="12" t="n">
         <f aca="false">IF($A36-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="M36" s="12" t="n">
         <f aca="false">IF($A36-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A36-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -7181,11 +7184,11 @@
       </c>
       <c r="R36" s="12" t="n">
         <f aca="false">E36+F36+SUM(I36:Q36)</f>
-        <v>0</v>
+        <v>243.3893</v>
       </c>
       <c r="S36" s="12" t="n">
         <f aca="false">S35+R36</f>
-        <v>1997.4372813</v>
+        <v>2278.55808385333</v>
       </c>
       <c r="T36" s="15" t="n">
         <f aca="false">IF(AND($A36&gt;$B$100,S36&gt;=0),1,0)</f>
@@ -7193,7 +7196,7 @@
       </c>
       <c r="U36" s="12" t="n">
         <f aca="false">S36-SUM($E$5:E36)-(1+Premissas!$B$17)*SUM($C$5:C36)</f>
-        <v>1229.0847813</v>
+        <v>1402.06708385333</v>
       </c>
       <c r="V36" s="12" t="n">
         <f aca="false">(G36+H36)*Premissas!$B$21</f>
@@ -7205,7 +7208,7 @@
       </c>
       <c r="X36" s="12" t="n">
         <f aca="false">X35-Y35+C36*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y36" s="12" t="n">
         <f aca="false">IF(OR(X36&gt;=Premissas!$B$13,B36=DATE(YEAR(B36),MONTH(B36)+1,0)),X36,0)</f>
@@ -7213,7 +7216,7 @@
       </c>
       <c r="Z36" s="12" t="n">
         <f aca="false">Z35-AA35+C36/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA36" s="12" t="n">
         <f aca="false">IF(OR(Z36&gt;=Premissas!$B$14,B36=DATE(YEAR(B36),MONTH(B36)+1,0)),Z36,0)</f>
@@ -7298,7 +7301,7 @@
       </c>
       <c r="S37" s="12" t="n">
         <f aca="false">S36+R37</f>
-        <v>1997.4372813</v>
+        <v>2278.55808385333</v>
       </c>
       <c r="T37" s="15" t="n">
         <f aca="false">IF(AND($A37&gt;$B$100,S37&gt;=0),1,0)</f>
@@ -7306,7 +7309,7 @@
       </c>
       <c r="U37" s="12" t="n">
         <f aca="false">S37-SUM($E$5:E37)-(1+Premissas!$B$17)*SUM($C$5:C37)</f>
-        <v>1229.0847813</v>
+        <v>1402.06708385333</v>
       </c>
       <c r="V37" s="12" t="n">
         <f aca="false">(G37+H37)*Premissas!$B$21</f>
@@ -7318,7 +7321,7 @@
       </c>
       <c r="X37" s="12" t="n">
         <f aca="false">X36-Y36+C37*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y37" s="12" t="n">
         <f aca="false">IF(OR(X37&gt;=Premissas!$B$13,B37=DATE(YEAR(B37),MONTH(B37)+1,0)),X37,0)</f>
@@ -7326,7 +7329,7 @@
       </c>
       <c r="Z37" s="12" t="n">
         <f aca="false">Z36-AA36+C37/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA37" s="12" t="n">
         <f aca="false">IF(OR(Z37&gt;=Premissas!$B$14,B37=DATE(YEAR(B37),MONTH(B37)+1,0)),Z37,0)</f>
@@ -7411,7 +7414,7 @@
       </c>
       <c r="S38" s="12" t="n">
         <f aca="false">S37+R38</f>
-        <v>1997.4372813</v>
+        <v>2278.55808385333</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">IF(AND($A38&gt;$B$100,S38&gt;=0),1,0)</f>
@@ -7419,7 +7422,7 @@
       </c>
       <c r="U38" s="12" t="n">
         <f aca="false">S38-SUM($E$5:E38)-(1+Premissas!$B$17)*SUM($C$5:C38)</f>
-        <v>1229.0847813</v>
+        <v>1402.06708385333</v>
       </c>
       <c r="V38" s="12" t="n">
         <f aca="false">(G38+H38)*Premissas!$B$21</f>
@@ -7431,7 +7434,7 @@
       </c>
       <c r="X38" s="12" t="n">
         <f aca="false">X37-Y37+C38*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y38" s="12" t="n">
         <f aca="false">IF(OR(X38&gt;=Premissas!$B$13,B38=DATE(YEAR(B38),MONTH(B38)+1,0)),X38,0)</f>
@@ -7439,7 +7442,7 @@
       </c>
       <c r="Z38" s="12" t="n">
         <f aca="false">Z37-AA37+C38/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA38" s="12" t="n">
         <f aca="false">IF(OR(Z38&gt;=Premissas!$B$14,B38=DATE(YEAR(B38),MONTH(B38)+1,0)),Z38,0)</f>
@@ -7524,7 +7527,7 @@
       </c>
       <c r="S39" s="12" t="n">
         <f aca="false">S38+R39</f>
-        <v>1997.4372813</v>
+        <v>2278.55808385333</v>
       </c>
       <c r="T39" s="15" t="n">
         <f aca="false">IF(AND($A39&gt;$B$100,S39&gt;=0),1,0)</f>
@@ -7532,7 +7535,7 @@
       </c>
       <c r="U39" s="12" t="n">
         <f aca="false">S39-SUM($E$5:E39)-(1+Premissas!$B$17)*SUM($C$5:C39)</f>
-        <v>1229.0847813</v>
+        <v>1402.06708385333</v>
       </c>
       <c r="V39" s="12" t="n">
         <f aca="false">(G39+H39)*Premissas!$B$21</f>
@@ -7544,7 +7547,7 @@
       </c>
       <c r="X39" s="12" t="n">
         <f aca="false">X38-Y38+C39*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y39" s="12" t="n">
         <f aca="false">IF(OR(X39&gt;=Premissas!$B$13,B39=DATE(YEAR(B39),MONTH(B39)+1,0)),X39,0)</f>
@@ -7552,7 +7555,7 @@
       </c>
       <c r="Z39" s="12" t="n">
         <f aca="false">Z38-AA38+C39/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA39" s="12" t="n">
         <f aca="false">IF(OR(Z39&gt;=Premissas!$B$14,B39=DATE(YEAR(B39),MONTH(B39)+1,0)),Z39,0)</f>
@@ -7581,11 +7584,11 @@
       </c>
       <c r="E40" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A40,$Y$5:$Y$94)</f>
-        <v>-700.0545</v>
+        <v>-813.8845</v>
       </c>
       <c r="F40" s="12" t="n">
         <f aca="false">-SUMIF($W$5:$W$94,A40,$V$5:$V$94)-SUMIF($AB$5:$AB$94,A40,$AA$5:$AA$94)</f>
-        <v>-112.02</v>
+        <v>-129.726666666667</v>
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">C40/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
@@ -7633,11 +7636,11 @@
       </c>
       <c r="R40" s="12" t="n">
         <f aca="false">E40+F40+SUM(I40:Q40)</f>
-        <v>-869.5645</v>
+        <v>-1001.10116666667</v>
       </c>
       <c r="S40" s="12" t="n">
         <f aca="false">S39+R40</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T40" s="15" t="n">
         <f aca="false">IF(AND($A40&gt;$B$100,S40&gt;=0),1,0)</f>
@@ -7645,7 +7648,7 @@
       </c>
       <c r="U40" s="12" t="n">
         <f aca="false">S40-SUM($E$5:E40)-(1+Premissas!$B$17)*SUM($C$5:C40)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V40" s="12" t="n">
         <f aca="false">(G40+H40)*Premissas!$B$21</f>
@@ -7657,7 +7660,7 @@
       </c>
       <c r="X40" s="12" t="n">
         <f aca="false">X39-Y39+C40*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y40" s="12" t="n">
         <f aca="false">IF(OR(X40&gt;=Premissas!$B$13,B40=DATE(YEAR(B40),MONTH(B40)+1,0)),X40,0)</f>
@@ -7665,7 +7668,7 @@
       </c>
       <c r="Z40" s="12" t="n">
         <f aca="false">Z39-AA39+C40/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA40" s="12" t="n">
         <f aca="false">IF(OR(Z40&gt;=Premissas!$B$14,B40=DATE(YEAR(B40),MONTH(B40)+1,0)),Z40,0)</f>
@@ -7750,7 +7753,7 @@
       </c>
       <c r="S41" s="12" t="n">
         <f aca="false">S40+R41</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T41" s="15" t="n">
         <f aca="false">IF(AND($A41&gt;$B$100,S41&gt;=0),1,0)</f>
@@ -7758,7 +7761,7 @@
       </c>
       <c r="U41" s="12" t="n">
         <f aca="false">S41-SUM($E$5:E41)-(1+Premissas!$B$17)*SUM($C$5:C41)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V41" s="12" t="n">
         <f aca="false">(G41+H41)*Premissas!$B$21</f>
@@ -7770,7 +7773,7 @@
       </c>
       <c r="X41" s="12" t="n">
         <f aca="false">X40-Y40+C41*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y41" s="12" t="n">
         <f aca="false">IF(OR(X41&gt;=Premissas!$B$13,B41=DATE(YEAR(B41),MONTH(B41)+1,0)),X41,0)</f>
@@ -7778,7 +7781,7 @@
       </c>
       <c r="Z41" s="12" t="n">
         <f aca="false">Z40-AA40+C41/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA41" s="12" t="n">
         <f aca="false">IF(OR(Z41&gt;=Premissas!$B$14,B41=DATE(YEAR(B41),MONTH(B41)+1,0)),Z41,0)</f>
@@ -7863,7 +7866,7 @@
       </c>
       <c r="S42" s="12" t="n">
         <f aca="false">S41+R42</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T42" s="15" t="n">
         <f aca="false">IF(AND($A42&gt;$B$100,S42&gt;=0),1,0)</f>
@@ -7871,7 +7874,7 @@
       </c>
       <c r="U42" s="12" t="n">
         <f aca="false">S42-SUM($E$5:E42)-(1+Premissas!$B$17)*SUM($C$5:C42)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V42" s="12" t="n">
         <f aca="false">(G42+H42)*Premissas!$B$21</f>
@@ -7883,7 +7886,7 @@
       </c>
       <c r="X42" s="12" t="n">
         <f aca="false">X41-Y41+C42*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y42" s="12" t="n">
         <f aca="false">IF(OR(X42&gt;=Premissas!$B$13,B42=DATE(YEAR(B42),MONTH(B42)+1,0)),X42,0)</f>
@@ -7891,7 +7894,7 @@
       </c>
       <c r="Z42" s="12" t="n">
         <f aca="false">Z41-AA41+C42/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA42" s="12" t="n">
         <f aca="false">IF(OR(Z42&gt;=Premissas!$B$14,B42=DATE(YEAR(B42),MONTH(B42)+1,0)),Z42,0)</f>
@@ -7976,7 +7979,7 @@
       </c>
       <c r="S43" s="12" t="n">
         <f aca="false">S42+R43</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T43" s="15" t="n">
         <f aca="false">IF(AND($A43&gt;$B$100,S43&gt;=0),1,0)</f>
@@ -7984,7 +7987,7 @@
       </c>
       <c r="U43" s="12" t="n">
         <f aca="false">S43-SUM($E$5:E43)-(1+Premissas!$B$17)*SUM($C$5:C43)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V43" s="12" t="n">
         <f aca="false">(G43+H43)*Premissas!$B$21</f>
@@ -7996,19 +7999,19 @@
       </c>
       <c r="X43" s="12" t="n">
         <f aca="false">X42-Y42+C43*(1+Premissas!$B$17)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Y43" s="12" t="n">
         <f aca="false">IF(OR(X43&gt;=Premissas!$B$13,B43=DATE(YEAR(B43),MONTH(B43)+1,0)),X43,0)</f>
-        <v>68.298</v>
+        <v>62.6065</v>
       </c>
       <c r="Z43" s="12" t="n">
         <f aca="false">Z42-AA42+C43/Premissas!$B$18*Premissas!$B$20</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA43" s="12" t="n">
         <f aca="false">IF(OR(Z43&gt;=Premissas!$B$14,B43=DATE(YEAR(B43),MONTH(B43)+1,0)),Z43,0)</f>
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="AB43" s="15" t="n">
         <f aca="false">IF(AA43&gt;0,IF(DAY(B43)&lt;=Premissas!$B$12,DATE(YEAR(B43),MONTH(B43),Premissas!$B$16),DATE(YEAR(B43),MONTH(B43)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -8089,7 +8092,7 @@
       </c>
       <c r="S44" s="12" t="n">
         <f aca="false">S43+R44</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">IF(AND($A44&gt;$B$100,S44&gt;=0),1,0)</f>
@@ -8097,7 +8100,7 @@
       </c>
       <c r="U44" s="12" t="n">
         <f aca="false">S44-SUM($E$5:E44)-(1+Premissas!$B$17)*SUM($C$5:C44)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V44" s="12" t="n">
         <f aca="false">(G44+H44)*Premissas!$B$21</f>
@@ -8202,7 +8205,7 @@
       </c>
       <c r="S45" s="12" t="n">
         <f aca="false">S44+R45</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T45" s="15" t="n">
         <f aca="false">IF(AND($A45&gt;$B$100,S45&gt;=0),1,0)</f>
@@ -8210,7 +8213,7 @@
       </c>
       <c r="U45" s="12" t="n">
         <f aca="false">S45-SUM($E$5:E45)-(1+Premissas!$B$17)*SUM($C$5:C45)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V45" s="12" t="n">
         <f aca="false">(G45+H45)*Premissas!$B$21</f>
@@ -8315,7 +8318,7 @@
       </c>
       <c r="S46" s="12" t="n">
         <f aca="false">S45+R46</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">IF(AND($A46&gt;$B$100,S46&gt;=0),1,0)</f>
@@ -8323,7 +8326,7 @@
       </c>
       <c r="U46" s="12" t="n">
         <f aca="false">S46-SUM($E$5:E46)-(1+Premissas!$B$17)*SUM($C$5:C46)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V46" s="12" t="n">
         <f aca="false">(G46+H46)*Premissas!$B$21</f>
@@ -8428,7 +8431,7 @@
       </c>
       <c r="S47" s="12" t="n">
         <f aca="false">S46+R47</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">IF(AND($A47&gt;$B$100,S47&gt;=0),1,0)</f>
@@ -8436,7 +8439,7 @@
       </c>
       <c r="U47" s="12" t="n">
         <f aca="false">S47-SUM($E$5:E47)-(1+Premissas!$B$17)*SUM($C$5:C47)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V47" s="12" t="n">
         <f aca="false">(G47+H47)*Premissas!$B$21</f>
@@ -8541,7 +8544,7 @@
       </c>
       <c r="S48" s="12" t="n">
         <f aca="false">S47+R48</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">IF(AND($A48&gt;$B$100,S48&gt;=0),1,0)</f>
@@ -8549,7 +8552,7 @@
       </c>
       <c r="U48" s="12" t="n">
         <f aca="false">S48-SUM($E$5:E48)-(1+Premissas!$B$17)*SUM($C$5:C48)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V48" s="12" t="n">
         <f aca="false">(G48+H48)*Premissas!$B$21</f>
@@ -8654,7 +8657,7 @@
       </c>
       <c r="S49" s="12" t="n">
         <f aca="false">S48+R49</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">IF(AND($A49&gt;$B$100,S49&gt;=0),1,0)</f>
@@ -8662,7 +8665,7 @@
       </c>
       <c r="U49" s="12" t="n">
         <f aca="false">S49-SUM($E$5:E49)-(1+Premissas!$B$17)*SUM($C$5:C49)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V49" s="12" t="n">
         <f aca="false">(G49+H49)*Premissas!$B$21</f>
@@ -8767,7 +8770,7 @@
       </c>
       <c r="S50" s="12" t="n">
         <f aca="false">S49+R50</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T50" s="15" t="n">
         <f aca="false">IF(AND($A50&gt;$B$100,S50&gt;=0),1,0)</f>
@@ -8775,7 +8778,7 @@
       </c>
       <c r="U50" s="12" t="n">
         <f aca="false">S50-SUM($E$5:E50)-(1+Premissas!$B$17)*SUM($C$5:C50)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V50" s="12" t="n">
         <f aca="false">(G50+H50)*Premissas!$B$21</f>
@@ -8880,7 +8883,7 @@
       </c>
       <c r="S51" s="12" t="n">
         <f aca="false">S50+R51</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T51" s="15" t="n">
         <f aca="false">IF(AND($A51&gt;$B$100,S51&gt;=0),1,0)</f>
@@ -8888,7 +8891,7 @@
       </c>
       <c r="U51" s="12" t="n">
         <f aca="false">S51-SUM($E$5:E51)-(1+Premissas!$B$17)*SUM($C$5:C51)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V51" s="12" t="n">
         <f aca="false">(G51+H51)*Premissas!$B$21</f>
@@ -8993,7 +8996,7 @@
       </c>
       <c r="S52" s="12" t="n">
         <f aca="false">S51+R52</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T52" s="15" t="n">
         <f aca="false">IF(AND($A52&gt;$B$100,S52&gt;=0),1,0)</f>
@@ -9001,7 +9004,7 @@
       </c>
       <c r="U52" s="12" t="n">
         <f aca="false">S52-SUM($E$5:E52)-(1+Premissas!$B$17)*SUM($C$5:C52)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V52" s="12" t="n">
         <f aca="false">(G52+H52)*Premissas!$B$21</f>
@@ -9106,7 +9109,7 @@
       </c>
       <c r="S53" s="12" t="n">
         <f aca="false">S52+R53</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T53" s="15" t="n">
         <f aca="false">IF(AND($A53&gt;$B$100,S53&gt;=0),1,0)</f>
@@ -9114,7 +9117,7 @@
       </c>
       <c r="U53" s="12" t="n">
         <f aca="false">S53-SUM($E$5:E53)-(1+Premissas!$B$17)*SUM($C$5:C53)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V53" s="12" t="n">
         <f aca="false">(G53+H53)*Premissas!$B$21</f>
@@ -9219,7 +9222,7 @@
       </c>
       <c r="S54" s="12" t="n">
         <f aca="false">S53+R54</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T54" s="15" t="n">
         <f aca="false">IF(AND($A54&gt;$B$100,S54&gt;=0),1,0)</f>
@@ -9227,7 +9230,7 @@
       </c>
       <c r="U54" s="12" t="n">
         <f aca="false">S54-SUM($E$5:E54)-(1+Premissas!$B$17)*SUM($C$5:C54)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V54" s="12" t="n">
         <f aca="false">(G54+H54)*Premissas!$B$21</f>
@@ -9332,7 +9335,7 @@
       </c>
       <c r="S55" s="12" t="n">
         <f aca="false">S54+R55</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T55" s="15" t="n">
         <f aca="false">IF(AND($A55&gt;$B$100,S55&gt;=0),1,0)</f>
@@ -9340,7 +9343,7 @@
       </c>
       <c r="U55" s="12" t="n">
         <f aca="false">S55-SUM($E$5:E55)-(1+Premissas!$B$17)*SUM($C$5:C55)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V55" s="12" t="n">
         <f aca="false">(G55+H55)*Premissas!$B$21</f>
@@ -9445,7 +9448,7 @@
       </c>
       <c r="S56" s="12" t="n">
         <f aca="false">S55+R56</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T56" s="15" t="n">
         <f aca="false">IF(AND($A56&gt;$B$100,S56&gt;=0),1,0)</f>
@@ -9453,7 +9456,7 @@
       </c>
       <c r="U56" s="12" t="n">
         <f aca="false">S56-SUM($E$5:E56)-(1+Premissas!$B$17)*SUM($C$5:C56)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V56" s="12" t="n">
         <f aca="false">(G56+H56)*Premissas!$B$21</f>
@@ -9558,7 +9561,7 @@
       </c>
       <c r="S57" s="12" t="n">
         <f aca="false">S56+R57</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T57" s="15" t="n">
         <f aca="false">IF(AND($A57&gt;$B$100,S57&gt;=0),1,0)</f>
@@ -9566,7 +9569,7 @@
       </c>
       <c r="U57" s="12" t="n">
         <f aca="false">S57-SUM($E$5:E57)-(1+Premissas!$B$17)*SUM($C$5:C57)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V57" s="12" t="n">
         <f aca="false">(G57+H57)*Premissas!$B$21</f>
@@ -9671,7 +9674,7 @@
       </c>
       <c r="S58" s="12" t="n">
         <f aca="false">S57+R58</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T58" s="15" t="n">
         <f aca="false">IF(AND($A58&gt;$B$100,S58&gt;=0),1,0)</f>
@@ -9679,7 +9682,7 @@
       </c>
       <c r="U58" s="12" t="n">
         <f aca="false">S58-SUM($E$5:E58)-(1+Premissas!$B$17)*SUM($C$5:C58)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V58" s="12" t="n">
         <f aca="false">(G58+H58)*Premissas!$B$21</f>
@@ -9784,7 +9787,7 @@
       </c>
       <c r="S59" s="12" t="n">
         <f aca="false">S58+R59</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T59" s="15" t="n">
         <f aca="false">IF(AND($A59&gt;$B$100,S59&gt;=0),1,0)</f>
@@ -9792,7 +9795,7 @@
       </c>
       <c r="U59" s="12" t="n">
         <f aca="false">S59-SUM($E$5:E59)-(1+Premissas!$B$17)*SUM($C$5:C59)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V59" s="12" t="n">
         <f aca="false">(G59+H59)*Premissas!$B$21</f>
@@ -9897,7 +9900,7 @@
       </c>
       <c r="S60" s="12" t="n">
         <f aca="false">S59+R60</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T60" s="15" t="n">
         <f aca="false">IF(AND($A60&gt;$B$100,S60&gt;=0),1,0)</f>
@@ -9905,7 +9908,7 @@
       </c>
       <c r="U60" s="12" t="n">
         <f aca="false">S60-SUM($E$5:E60)-(1+Premissas!$B$17)*SUM($C$5:C60)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V60" s="12" t="n">
         <f aca="false">(G60+H60)*Premissas!$B$21</f>
@@ -10010,7 +10013,7 @@
       </c>
       <c r="S61" s="12" t="n">
         <f aca="false">S60+R61</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T61" s="15" t="n">
         <f aca="false">IF(AND($A61&gt;$B$100,S61&gt;=0),1,0)</f>
@@ -10018,7 +10021,7 @@
       </c>
       <c r="U61" s="12" t="n">
         <f aca="false">S61-SUM($E$5:E61)-(1+Premissas!$B$17)*SUM($C$5:C61)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V61" s="12" t="n">
         <f aca="false">(G61+H61)*Premissas!$B$21</f>
@@ -10123,7 +10126,7 @@
       </c>
       <c r="S62" s="12" t="n">
         <f aca="false">S61+R62</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T62" s="15" t="n">
         <f aca="false">IF(AND($A62&gt;$B$100,S62&gt;=0),1,0)</f>
@@ -10131,7 +10134,7 @@
       </c>
       <c r="U62" s="12" t="n">
         <f aca="false">S62-SUM($E$5:E62)-(1+Premissas!$B$17)*SUM($C$5:C62)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V62" s="12" t="n">
         <f aca="false">(G62+H62)*Premissas!$B$21</f>
@@ -10236,7 +10239,7 @@
       </c>
       <c r="S63" s="12" t="n">
         <f aca="false">S62+R63</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T63" s="15" t="n">
         <f aca="false">IF(AND($A63&gt;$B$100,S63&gt;=0),1,0)</f>
@@ -10244,7 +10247,7 @@
       </c>
       <c r="U63" s="12" t="n">
         <f aca="false">S63-SUM($E$5:E63)-(1+Premissas!$B$17)*SUM($C$5:C63)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">(G63+H63)*Premissas!$B$21</f>
@@ -10349,7 +10352,7 @@
       </c>
       <c r="S64" s="12" t="n">
         <f aca="false">S63+R64</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T64" s="15" t="n">
         <f aca="false">IF(AND($A64&gt;$B$100,S64&gt;=0),1,0)</f>
@@ -10357,7 +10360,7 @@
       </c>
       <c r="U64" s="12" t="n">
         <f aca="false">S64-SUM($E$5:E64)-(1+Premissas!$B$17)*SUM($C$5:C64)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">(G64+H64)*Premissas!$B$21</f>
@@ -10462,7 +10465,7 @@
       </c>
       <c r="S65" s="12" t="n">
         <f aca="false">S64+R65</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T65" s="15" t="n">
         <f aca="false">IF(AND($A65&gt;$B$100,S65&gt;=0),1,0)</f>
@@ -10470,7 +10473,7 @@
       </c>
       <c r="U65" s="12" t="n">
         <f aca="false">S65-SUM($E$5:E65)-(1+Premissas!$B$17)*SUM($C$5:C65)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">(G65+H65)*Premissas!$B$21</f>
@@ -10575,7 +10578,7 @@
       </c>
       <c r="S66" s="12" t="n">
         <f aca="false">S65+R66</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T66" s="15" t="n">
         <f aca="false">IF(AND($A66&gt;$B$100,S66&gt;=0),1,0)</f>
@@ -10583,7 +10586,7 @@
       </c>
       <c r="U66" s="12" t="n">
         <f aca="false">S66-SUM($E$5:E66)-(1+Premissas!$B$17)*SUM($C$5:C66)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">(G66+H66)*Premissas!$B$21</f>
@@ -10688,7 +10691,7 @@
       </c>
       <c r="S67" s="12" t="n">
         <f aca="false">S66+R67</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T67" s="15" t="n">
         <f aca="false">IF(AND($A67&gt;$B$100,S67&gt;=0),1,0)</f>
@@ -10696,7 +10699,7 @@
       </c>
       <c r="U67" s="12" t="n">
         <f aca="false">S67-SUM($E$5:E67)-(1+Premissas!$B$17)*SUM($C$5:C67)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V67" s="12" t="n">
         <f aca="false">(G67+H67)*Premissas!$B$21</f>
@@ -10801,7 +10804,7 @@
       </c>
       <c r="S68" s="12" t="n">
         <f aca="false">S67+R68</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T68" s="15" t="n">
         <f aca="false">IF(AND($A68&gt;$B$100,S68&gt;=0),1,0)</f>
@@ -10809,7 +10812,7 @@
       </c>
       <c r="U68" s="12" t="n">
         <f aca="false">S68-SUM($E$5:E68)-(1+Premissas!$B$17)*SUM($C$5:C68)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V68" s="12" t="n">
         <f aca="false">(G68+H68)*Premissas!$B$21</f>
@@ -10914,7 +10917,7 @@
       </c>
       <c r="S69" s="12" t="n">
         <f aca="false">S68+R69</f>
-        <v>1127.8727813</v>
+        <v>1277.45691718667</v>
       </c>
       <c r="T69" s="15" t="n">
         <f aca="false">IF(AND($A69&gt;$B$100,S69&gt;=0),1,0)</f>
@@ -10922,7 +10925,7 @@
       </c>
       <c r="U69" s="12" t="n">
         <f aca="false">S69-SUM($E$5:E69)-(1+Premissas!$B$17)*SUM($C$5:C69)</f>
-        <v>1059.5747813</v>
+        <v>1214.85041718667</v>
       </c>
       <c r="V69" s="12" t="n">
         <f aca="false">(G69+H69)*Premissas!$B$21</f>
@@ -10971,11 +10974,11 @@
       </c>
       <c r="E70" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A70,$Y$5:$Y$94)</f>
-        <v>-68.298</v>
+        <v>-62.6065</v>
       </c>
       <c r="F70" s="12" t="n">
         <f aca="false">-SUMIF($W$5:$W$94,A70,$V$5:$V$94)-SUMIF($AB$5:$AB$94,A70,$AA$5:$AA$94)</f>
-        <v>-11.28</v>
+        <v>-10.9266666666667</v>
       </c>
       <c r="G70" s="29" t="n">
         <f aca="false">C70/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
@@ -11023,11 +11026,11 @@
       </c>
       <c r="R70" s="12" t="n">
         <f aca="false">E70+F70+SUM(I70:Q70)</f>
-        <v>-137.068</v>
+        <v>-131.023166666667</v>
       </c>
       <c r="S70" s="12" t="n">
         <f aca="false">S69+R70</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T70" s="15" t="n">
         <f aca="false">IF(AND($A70&gt;$B$100,S70&gt;=0),1,0)</f>
@@ -11035,7 +11038,7 @@
       </c>
       <c r="U70" s="12" t="n">
         <f aca="false">S70-SUM($E$5:E70)-(1+Premissas!$B$17)*SUM($C$5:C70)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V70" s="12" t="n">
         <f aca="false">(G70+H70)*Premissas!$B$21</f>
@@ -11140,7 +11143,7 @@
       </c>
       <c r="S71" s="12" t="n">
         <f aca="false">S70+R71</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T71" s="15" t="n">
         <f aca="false">IF(AND($A71&gt;$B$100,S71&gt;=0),1,0)</f>
@@ -11148,7 +11151,7 @@
       </c>
       <c r="U71" s="12" t="n">
         <f aca="false">S71-SUM($E$5:E71)-(1+Premissas!$B$17)*SUM($C$5:C71)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V71" s="12" t="n">
         <f aca="false">(G71+H71)*Premissas!$B$21</f>
@@ -11253,7 +11256,7 @@
       </c>
       <c r="S72" s="12" t="n">
         <f aca="false">S71+R72</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T72" s="15" t="n">
         <f aca="false">IF(AND($A72&gt;$B$100,S72&gt;=0),1,0)</f>
@@ -11261,7 +11264,7 @@
       </c>
       <c r="U72" s="12" t="n">
         <f aca="false">S72-SUM($E$5:E72)-(1+Premissas!$B$17)*SUM($C$5:C72)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">(G72+H72)*Premissas!$B$21</f>
@@ -11366,7 +11369,7 @@
       </c>
       <c r="S73" s="12" t="n">
         <f aca="false">S72+R73</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T73" s="15" t="n">
         <f aca="false">IF(AND($A73&gt;$B$100,S73&gt;=0),1,0)</f>
@@ -11374,7 +11377,7 @@
       </c>
       <c r="U73" s="12" t="n">
         <f aca="false">S73-SUM($E$5:E73)-(1+Premissas!$B$17)*SUM($C$5:C73)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">(G73+H73)*Premissas!$B$21</f>
@@ -11479,7 +11482,7 @@
       </c>
       <c r="S74" s="12" t="n">
         <f aca="false">S73+R74</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T74" s="15" t="n">
         <f aca="false">IF(AND($A74&gt;$B$100,S74&gt;=0),1,0)</f>
@@ -11487,7 +11490,7 @@
       </c>
       <c r="U74" s="12" t="n">
         <f aca="false">S74-SUM($E$5:E74)-(1+Premissas!$B$17)*SUM($C$5:C74)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">(G74+H74)*Premissas!$B$21</f>
@@ -11592,7 +11595,7 @@
       </c>
       <c r="S75" s="12" t="n">
         <f aca="false">S74+R75</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T75" s="15" t="n">
         <f aca="false">IF(AND($A75&gt;$B$100,S75&gt;=0),1,0)</f>
@@ -11600,7 +11603,7 @@
       </c>
       <c r="U75" s="12" t="n">
         <f aca="false">S75-SUM($E$5:E75)-(1+Premissas!$B$17)*SUM($C$5:C75)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V75" s="12" t="n">
         <f aca="false">(G75+H75)*Premissas!$B$21</f>
@@ -11705,7 +11708,7 @@
       </c>
       <c r="S76" s="12" t="n">
         <f aca="false">S75+R76</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T76" s="15" t="n">
         <f aca="false">IF(AND($A76&gt;$B$100,S76&gt;=0),1,0)</f>
@@ -11713,7 +11716,7 @@
       </c>
       <c r="U76" s="12" t="n">
         <f aca="false">S76-SUM($E$5:E76)-(1+Premissas!$B$17)*SUM($C$5:C76)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V76" s="12" t="n">
         <f aca="false">(G76+H76)*Premissas!$B$21</f>
@@ -11818,7 +11821,7 @@
       </c>
       <c r="S77" s="12" t="n">
         <f aca="false">S76+R77</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T77" s="15" t="n">
         <f aca="false">IF(AND($A77&gt;$B$100,S77&gt;=0),1,0)</f>
@@ -11826,7 +11829,7 @@
       </c>
       <c r="U77" s="12" t="n">
         <f aca="false">S77-SUM($E$5:E77)-(1+Premissas!$B$17)*SUM($C$5:C77)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V77" s="12" t="n">
         <f aca="false">(G77+H77)*Premissas!$B$21</f>
@@ -11931,7 +11934,7 @@
       </c>
       <c r="S78" s="12" t="n">
         <f aca="false">S77+R78</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T78" s="15" t="n">
         <f aca="false">IF(AND($A78&gt;$B$100,S78&gt;=0),1,0)</f>
@@ -11939,7 +11942,7 @@
       </c>
       <c r="U78" s="12" t="n">
         <f aca="false">S78-SUM($E$5:E78)-(1+Premissas!$B$17)*SUM($C$5:C78)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V78" s="12" t="n">
         <f aca="false">(G78+H78)*Premissas!$B$21</f>
@@ -12044,7 +12047,7 @@
       </c>
       <c r="S79" s="12" t="n">
         <f aca="false">S78+R79</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T79" s="15" t="n">
         <f aca="false">IF(AND($A79&gt;$B$100,S79&gt;=0),1,0)</f>
@@ -12052,7 +12055,7 @@
       </c>
       <c r="U79" s="12" t="n">
         <f aca="false">S79-SUM($E$5:E79)-(1+Premissas!$B$17)*SUM($C$5:C79)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V79" s="12" t="n">
         <f aca="false">(G79+H79)*Premissas!$B$21</f>
@@ -12157,7 +12160,7 @@
       </c>
       <c r="S80" s="12" t="n">
         <f aca="false">S79+R80</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T80" s="15" t="n">
         <f aca="false">IF(AND($A80&gt;$B$100,S80&gt;=0),1,0)</f>
@@ -12165,7 +12168,7 @@
       </c>
       <c r="U80" s="12" t="n">
         <f aca="false">S80-SUM($E$5:E80)-(1+Premissas!$B$17)*SUM($C$5:C80)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V80" s="12" t="n">
         <f aca="false">(G80+H80)*Premissas!$B$21</f>
@@ -12270,7 +12273,7 @@
       </c>
       <c r="S81" s="12" t="n">
         <f aca="false">S80+R81</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T81" s="15" t="n">
         <f aca="false">IF(AND($A81&gt;$B$100,S81&gt;=0),1,0)</f>
@@ -12278,7 +12281,7 @@
       </c>
       <c r="U81" s="12" t="n">
         <f aca="false">S81-SUM($E$5:E81)-(1+Premissas!$B$17)*SUM($C$5:C81)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V81" s="12" t="n">
         <f aca="false">(G81+H81)*Premissas!$B$21</f>
@@ -12383,7 +12386,7 @@
       </c>
       <c r="S82" s="12" t="n">
         <f aca="false">S81+R82</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T82" s="15" t="n">
         <f aca="false">IF(AND($A82&gt;$B$100,S82&gt;=0),1,0)</f>
@@ -12391,7 +12394,7 @@
       </c>
       <c r="U82" s="12" t="n">
         <f aca="false">S82-SUM($E$5:E82)-(1+Premissas!$B$17)*SUM($C$5:C82)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V82" s="12" t="n">
         <f aca="false">(G82+H82)*Premissas!$B$21</f>
@@ -12496,7 +12499,7 @@
       </c>
       <c r="S83" s="12" t="n">
         <f aca="false">S82+R83</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T83" s="15" t="n">
         <f aca="false">IF(AND($A83&gt;$B$100,S83&gt;=0),1,0)</f>
@@ -12504,7 +12507,7 @@
       </c>
       <c r="U83" s="12" t="n">
         <f aca="false">S83-SUM($E$5:E83)-(1+Premissas!$B$17)*SUM($C$5:C83)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V83" s="12" t="n">
         <f aca="false">(G83+H83)*Premissas!$B$21</f>
@@ -12609,7 +12612,7 @@
       </c>
       <c r="S84" s="12" t="n">
         <f aca="false">S83+R84</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T84" s="15" t="n">
         <f aca="false">IF(AND($A84&gt;$B$100,S84&gt;=0),1,0)</f>
@@ -12617,7 +12620,7 @@
       </c>
       <c r="U84" s="12" t="n">
         <f aca="false">S84-SUM($E$5:E84)-(1+Premissas!$B$17)*SUM($C$5:C84)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V84" s="12" t="n">
         <f aca="false">(G84+H84)*Premissas!$B$21</f>
@@ -12722,7 +12725,7 @@
       </c>
       <c r="S85" s="12" t="n">
         <f aca="false">S84+R85</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T85" s="15" t="n">
         <f aca="false">IF(AND($A85&gt;$B$100,S85&gt;=0),1,0)</f>
@@ -12730,7 +12733,7 @@
       </c>
       <c r="U85" s="12" t="n">
         <f aca="false">S85-SUM($E$5:E85)-(1+Premissas!$B$17)*SUM($C$5:C85)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V85" s="12" t="n">
         <f aca="false">(G85+H85)*Premissas!$B$21</f>
@@ -12835,7 +12838,7 @@
       </c>
       <c r="S86" s="12" t="n">
         <f aca="false">S85+R86</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T86" s="15" t="n">
         <f aca="false">IF(AND($A86&gt;$B$100,S86&gt;=0),1,0)</f>
@@ -12843,7 +12846,7 @@
       </c>
       <c r="U86" s="12" t="n">
         <f aca="false">S86-SUM($E$5:E86)-(1+Premissas!$B$17)*SUM($C$5:C86)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V86" s="12" t="n">
         <f aca="false">(G86+H86)*Premissas!$B$21</f>
@@ -12948,7 +12951,7 @@
       </c>
       <c r="S87" s="12" t="n">
         <f aca="false">S86+R87</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T87" s="15" t="n">
         <f aca="false">IF(AND($A87&gt;$B$100,S87&gt;=0),1,0)</f>
@@ -12956,7 +12959,7 @@
       </c>
       <c r="U87" s="12" t="n">
         <f aca="false">S87-SUM($E$5:E87)-(1+Premissas!$B$17)*SUM($C$5:C87)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V87" s="12" t="n">
         <f aca="false">(G87+H87)*Premissas!$B$21</f>
@@ -13061,7 +13064,7 @@
       </c>
       <c r="S88" s="12" t="n">
         <f aca="false">S87+R88</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T88" s="15" t="n">
         <f aca="false">IF(AND($A88&gt;$B$100,S88&gt;=0),1,0)</f>
@@ -13069,7 +13072,7 @@
       </c>
       <c r="U88" s="12" t="n">
         <f aca="false">S88-SUM($E$5:E88)-(1+Premissas!$B$17)*SUM($C$5:C88)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V88" s="12" t="n">
         <f aca="false">(G88+H88)*Premissas!$B$21</f>
@@ -13174,7 +13177,7 @@
       </c>
       <c r="S89" s="12" t="n">
         <f aca="false">S88+R89</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T89" s="15" t="n">
         <f aca="false">IF(AND($A89&gt;$B$100,S89&gt;=0),1,0)</f>
@@ -13182,7 +13185,7 @@
       </c>
       <c r="U89" s="12" t="n">
         <f aca="false">S89-SUM($E$5:E89)-(1+Premissas!$B$17)*SUM($C$5:C89)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V89" s="12" t="n">
         <f aca="false">(G89+H89)*Premissas!$B$21</f>
@@ -13287,7 +13290,7 @@
       </c>
       <c r="S90" s="12" t="n">
         <f aca="false">S89+R90</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T90" s="15" t="n">
         <f aca="false">IF(AND($A90&gt;$B$100,S90&gt;=0),1,0)</f>
@@ -13295,7 +13298,7 @@
       </c>
       <c r="U90" s="12" t="n">
         <f aca="false">S90-SUM($E$5:E90)-(1+Premissas!$B$17)*SUM($C$5:C90)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V90" s="12" t="n">
         <f aca="false">(G90+H90)*Premissas!$B$21</f>
@@ -13400,7 +13403,7 @@
       </c>
       <c r="S91" s="12" t="n">
         <f aca="false">S90+R91</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T91" s="15" t="n">
         <f aca="false">IF(AND($A91&gt;$B$100,S91&gt;=0),1,0)</f>
@@ -13408,7 +13411,7 @@
       </c>
       <c r="U91" s="12" t="n">
         <f aca="false">S91-SUM($E$5:E91)-(1+Premissas!$B$17)*SUM($C$5:C91)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V91" s="12" t="n">
         <f aca="false">(G91+H91)*Premissas!$B$21</f>
@@ -13513,7 +13516,7 @@
       </c>
       <c r="S92" s="12" t="n">
         <f aca="false">S91+R92</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T92" s="15" t="n">
         <f aca="false">IF(AND($A92&gt;$B$100,S92&gt;=0),1,0)</f>
@@ -13521,7 +13524,7 @@
       </c>
       <c r="U92" s="12" t="n">
         <f aca="false">S92-SUM($E$5:E92)-(1+Premissas!$B$17)*SUM($C$5:C92)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V92" s="12" t="n">
         <f aca="false">(G92+H92)*Premissas!$B$21</f>
@@ -13626,7 +13629,7 @@
       </c>
       <c r="S93" s="12" t="n">
         <f aca="false">S92+R93</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T93" s="15" t="n">
         <f aca="false">IF(AND($A93&gt;$B$100,S93&gt;=0),1,0)</f>
@@ -13634,7 +13637,7 @@
       </c>
       <c r="U93" s="12" t="n">
         <f aca="false">S93-SUM($E$5:E93)-(1+Premissas!$B$17)*SUM($C$5:C93)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V93" s="12" t="n">
         <f aca="false">(G93+H93)*Premissas!$B$21</f>
@@ -13739,7 +13742,7 @@
       </c>
       <c r="S94" s="12" t="n">
         <f aca="false">S93+R94</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="T94" s="15" t="n">
         <f aca="false">IF(AND($A94&gt;$B$100,S94&gt;=0),1,0)</f>
@@ -13747,7 +13750,7 @@
       </c>
       <c r="U94" s="12" t="n">
         <f aca="false">S94-SUM($E$5:E94)-(1+Premissas!$B$17)*SUM($C$5:C94)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
       <c r="V94" s="12" t="n">
         <f aca="false">(G94+H94)*Premissas!$B$21</f>
@@ -13780,55 +13783,55 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C95" s="14" t="n">
         <f aca="false">SUM(C5:C94)</f>
-        <v>675</v>
+        <v>770</v>
       </c>
       <c r="E95" s="14" t="n">
         <f aca="false">SUM(E5:E94)</f>
-        <v>-768.3525</v>
+        <v>-876.491</v>
       </c>
       <c r="F95" s="14" t="n">
         <f aca="false">SUM(F5:F94)</f>
-        <v>-123.3</v>
+        <v>-140.653333333333</v>
       </c>
       <c r="G95" s="31" t="n">
         <f aca="false">SUM(G5:G94)</f>
-        <v>31.5</v>
+        <v>35.9333333333333</v>
       </c>
       <c r="H95" s="31" t="n">
         <f aca="false">SUM(H5:H94)</f>
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="I95" s="14" t="n">
         <f aca="false">SUM(I5:I94)</f>
-        <v>-2096.640315</v>
+        <v>-2391.723026</v>
       </c>
       <c r="J95" s="14" t="n">
         <f aca="false">SUM(J5:J94)</f>
-        <v>302.93240355</v>
+        <v>345.56733442</v>
       </c>
       <c r="K95" s="14" t="n">
         <f aca="false">SUM(K5:K94)</f>
-        <v>-63</v>
+        <v>-71.8666666666667</v>
       </c>
       <c r="L95" s="14" t="n">
         <f aca="false">SUM(L5:L94)</f>
-        <v>2987.0505</v>
+        <v>3407.4502</v>
       </c>
       <c r="M95" s="14" t="n">
         <f aca="false">SUM(M5:M94)</f>
-        <v>1524.42319275</v>
+        <v>1738.9716421</v>
       </c>
       <c r="N95" s="14" t="n">
         <f aca="false">SUM(N5:N94)</f>
-        <v>-472.5</v>
+        <v>-539</v>
       </c>
       <c r="O95" s="14" t="n">
         <f aca="false">SUM(O5:O94)</f>
-        <v>-184.8285</v>
+        <v>-210.8414</v>
       </c>
       <c r="P95" s="14" t="n">
         <f aca="false">SUM(P5:P94)</f>
@@ -13840,34 +13843,34 @@
       </c>
       <c r="R95" s="14" t="n">
         <f aca="false">SUM(R5:R94)</f>
-        <v>990.8047813</v>
+        <v>1146.43375052</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">MIN(S5:S94)</f>
-        <v>-879.4672187</v>
+        <v>-827.567485873333</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B100" s="32" t="n">
         <f aca="false">INDEX(A5:A94,MATCH(B99,S5:S94,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B101" s="32" t="n">
         <f aca="false">IFERROR(INDEX(A5:A94,MATCH(1,T5:T94,0)),"não volta em 90 dias")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13876,7 +13879,7 @@
       </c>
       <c r="B102" s="14" t="n">
         <f aca="false">MIN(U5:U94)</f>
-        <v>-1647.8197187</v>
+        <v>-1704.05848587333</v>
       </c>
     </row>
   </sheetData>
@@ -13907,24 +13910,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13932,13 +13935,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E4" s="34"/>
     </row>
@@ -13947,13 +13950,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E5" s="34"/>
     </row>
@@ -13962,13 +13965,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E6" s="34"/>
     </row>
@@ -13977,13 +13980,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E7" s="34"/>
     </row>
@@ -14015,7 +14018,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14023,288 +14026,288 @@
         <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>288</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>90</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -14337,62 +14340,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="35" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
         <v>30</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>90</v>
@@ -14400,107 +14403,107 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">Premissas!$B$30</f>
         <v>19.99</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">Premissas!$B$31</f>
         <v>5</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">Unitário!$B$25</f>
         <v>11.57001</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C9" s="35" t="n">
         <f aca="false">Premissas!$B$38</f>
         <v>4.99</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>90</v>
@@ -14508,26 +14511,26 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">Premissas!$B$39</f>
         <v>9.99</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>90</v>
@@ -14535,53 +14538,53 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">Premissas!$B$41+Premissas!$B$62*(Unitário!$B$24+Unitário!$B$25)</f>
         <v>86.56001</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" s="35" t="n">
         <f aca="false">Premissas!$B$29*Premissas!$B$50</f>
         <v>30</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>90</v>
@@ -14589,26 +14592,26 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C13" s="35" t="n">
         <f aca="false">Premissas!$B$41+Premissas!$B$62*Premissas!$B$31+Unitário!$B$27</f>
         <v>58.9897635</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>90</v>
@@ -14616,160 +14619,160 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="35" t="n">
         <f aca="false">Premissas!$B$31</f>
         <v>5</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C15" s="35" t="n">
         <f aca="false">Unitário!$B$27</f>
         <v>3.9897635</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">Premissas!$B$18/Premissas!$B$19*(1+Premissas!$B$17)</f>
         <v>17.0745</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C18" s="35" t="n">
         <f aca="false">Premissas!$B$20/Premissas!$B$19+Premissas!$B$21</f>
         <v>2.74</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C19" s="35" t="n">
         <f aca="false">Premissas!$B$43</f>
         <v>53.5</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H19" s="33" t="s">
         <v>90</v>
@@ -14777,29 +14780,29 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C20" s="35" t="n">
         <f aca="false">Premissas!$B$67*Premissas!$B$68</f>
         <v>3.99</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/docs/operacao/modelo-caixa-anuncios.xlsx
+++ b/docs/operacao/modelo-caixa-anuncios.xlsx
@@ -232,7 +232,7 @@
     <t xml:space="preserve">R$</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 55/dia (plano escolhido; antes R$ 375 em 5 dias)</t>
+    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 50/dia (antes R$ 55/dia; antes ainda R$ 375 em 5 dias)</t>
   </si>
   <si>
     <t xml:space="preserve">Fase 1 — dias</t>
@@ -253,7 +253,7 @@
     <t xml:space="preserve">Fase 2 — verba total</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 55/dia (plano escolhido; antes R$ 300 em 5 dias)</t>
+    <t xml:space="preserve">Operador, 09/10: 7 dias a R$ 50/dia (antes R$ 55/dia; antes ainda R$ 300 em 5 dias)</t>
   </si>
   <si>
     <t xml:space="preserve">Fase 2 — dias</t>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">Caixa disponível</t>
   </si>
   <si>
-    <t xml:space="preserve">Operador, 09/10 (dos R$ 2.000 investidos; a verba de R$ 770 vai no cartão e é paga com o repasse do COD, não com este caixa)</t>
+    <t xml:space="preserve">Operador, 09/10 (dos R$ 2.000 investidos; a verba de R$ 700 vai no cartão e é paga com o repasse do COD, não com este caixa)</t>
   </si>
   <si>
     <t xml:space="preserve">Margem de segurança</t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">'Fluxo diário'!C95</f>
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Fluxo diário'!G95+'Fluxo diário'!H95</f>
-        <v>51.3333333333333</v>
+        <v>46.6666666666667</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f aca="false">TEXT('Fluxo diário'!G95,"0.0")&amp;" / "&amp;TEXT('Fluxo diário'!H95,"0.0")</f>
-        <v>35.9 / 15.4</v>
+        <v>32.7 / 14.0</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">'Fluxo diário'!G95*Premissas!$B$51+'Fluxo diário'!H95*Premissas!$B$52</f>
-        <v>6468.154</v>
+        <v>5880.14</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">-'Fluxo diário'!B99</f>
-        <v>827.567485873333</v>
+        <v>752.334078066667</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B12" s="4" t="n">
         <f aca="false">-'Fluxo diário'!B102</f>
-        <v>1704.05848587333</v>
+        <v>1549.14407806667</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">B13-B9</f>
-        <v>247.432514126667</v>
+        <v>322.665921933333</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>23</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">'Fluxo diário'!S94</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">IFERROR(B13/B9,0)</f>
-        <v>1.29898771804157</v>
+        <v>1.42888648984573</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">B5*(1+Premissas!$B$17)</f>
-        <v>876.491</v>
+        <v>796.81</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>31</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">B5/Premissas!$B$18</f>
-        <v>513.333333333333</v>
+        <v>466.666666666667</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B20" s="6" t="str">
         <f aca="false">IF(AND(B19&gt;500,B6&gt;50),"passa","abaixo do piso")</f>
-        <v>passa</v>
+        <v>abaixo do piso</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>35</v>
@@ -2193,15 +2193,15 @@
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">A35*B5</f>
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">A35*B9</f>
-        <v>827.567485873333</v>
+        <v>752.334078066667</v>
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">$B$13-C35</f>
-        <v>247.432514126667</v>
+        <v>322.665921933333</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,15 +2210,15 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">A36*B5</f>
-        <v>1540</v>
+        <v>1400</v>
       </c>
       <c r="C36" s="17" t="n">
         <f aca="false">A36*B9</f>
-        <v>1655.13497174667</v>
+        <v>1504.66815613333</v>
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">$B$13-C36</f>
-        <v>-580.134971746667</v>
+        <v>-429.668156133333</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2227,15 +2227,15 @@
       </c>
       <c r="B37" s="17" t="n">
         <f aca="false">A37*B5</f>
-        <v>2310</v>
+        <v>2100</v>
       </c>
       <c r="C37" s="17" t="n">
         <f aca="false">A37*B9</f>
-        <v>2482.70245762</v>
+        <v>2257.0022342</v>
       </c>
       <c r="D37" s="17" t="n">
         <f aca="false">$B$13-C37</f>
-        <v>-1407.70245762</v>
+        <v>-1182.0022342</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2244,15 +2244,15 @@
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">A38*B5</f>
-        <v>3850</v>
+        <v>3500</v>
       </c>
       <c r="C38" s="17" t="n">
         <f aca="false">A38*B9</f>
-        <v>4137.83742936667</v>
+        <v>3761.67039033333</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">$B$13-C38</f>
-        <v>-3062.83742936667</v>
+        <v>-2686.67039033333</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2261,15 +2261,15 @@
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">A39*B5</f>
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="C39" s="17" t="n">
         <f aca="false">A39*B9</f>
-        <v>8275.67485873333</v>
+        <v>7523.34078066667</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">$B$13-C39</f>
-        <v>-7200.67485873333</v>
+        <v>-6448.34078066667</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2338,7 +2338,7 @@
         <v>66</v>
       </c>
       <c r="B6" s="20" t="n">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>67</v>
@@ -2380,7 +2380,7 @@
         <v>74</v>
       </c>
       <c r="B9" s="20" t="n">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>67</v>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C5" s="12" t="n">
         <f aca="false">IF(A5&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A5&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A5&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D5" s="15" t="n">
         <f aca="false">IF(Y5&gt;0,IF(DAY(B5)&lt;=Premissas!$B$12,DATE(YEAR(B5),MONTH(B5),Premissas!$B$16),DATE(YEAR(B5),MONTH(B5)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3637,11 +3637,11 @@
       </c>
       <c r="G5" s="29" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H5" s="29" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I5" s="12" t="n">
         <f aca="false">-IF($A5-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A5-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M5" s="12" t="n">
         <f aca="false">IF($A5-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">-IF($A5-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A5-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
@@ -3681,11 +3681,11 @@
       </c>
       <c r="R5" s="12" t="n">
         <f aca="false">E5+F5+SUM(I5:Q5)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="S5" s="12" t="n">
         <f aca="false">R5</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="T5" s="15" t="n">
         <f aca="false">IF(AND($A5&gt;$B$100,S5&gt;=0),1,0)</f>
@@ -3693,11 +3693,11 @@
       </c>
       <c r="U5" s="12" t="n">
         <f aca="false">S5-SUM($E$5:E5)-(1+Premissas!$B$17)*SUM($C$5:C5)</f>
-        <v>61.60576015</v>
+        <v>56.0052365</v>
       </c>
       <c r="V5" s="12" t="n">
         <f aca="false">(G5+H5)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W5" s="15" t="n">
         <f aca="false">IF(V5&gt;0,DATE(YEAR(B5),MONTH(B5)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="X5" s="12" t="n">
         <f aca="false">C5*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y5" s="12" t="n">
         <f aca="false">IF(OR(X5&gt;=Premissas!$B$13,B5=DATE(YEAR(B5),MONTH(B5)+1,0)),X5,0)</f>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="Z5" s="12" t="n">
         <f aca="false">C5/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA5" s="12" t="n">
         <f aca="false">IF(OR(Z5&gt;=Premissas!$B$14,B5=DATE(YEAR(B5),MONTH(B5)+1,0)),Z5,0)</f>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">IF(A6&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A6&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A6&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">IF(Y6&gt;0,IF(DAY(B6)&lt;=Premissas!$B$12,DATE(YEAR(B6),MONTH(B6),Premissas!$B$16),DATE(YEAR(B6),MONTH(B6)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3750,15 +3750,15 @@
       </c>
       <c r="G6" s="29" t="n">
         <f aca="false">C6/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H6" s="29" t="n">
         <f aca="false">C6/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I6" s="12" t="n">
         <f aca="false">-IF($A6-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A6-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
@@ -3774,11 +3774,11 @@
       </c>
       <c r="M6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">-IF($A6-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O6" s="12" t="n">
         <f aca="false">IF($A6-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A6-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -3794,11 +3794,11 @@
       </c>
       <c r="R6" s="12" t="n">
         <f aca="false">E6+F6+SUM(I6:Q6)</f>
-        <v>-85.12509885</v>
+        <v>-77.3864535</v>
       </c>
       <c r="S6" s="12" t="n">
         <f aca="false">S5+R6</f>
-        <v>39.0871613</v>
+        <v>35.533783</v>
       </c>
       <c r="T6" s="15" t="n">
         <f aca="false">IF(AND($A6&gt;$B$100,S6&gt;=0),1,0)</f>
@@ -3806,11 +3806,11 @@
       </c>
       <c r="U6" s="12" t="n">
         <f aca="false">S6-SUM($E$5:E6)-(1+Premissas!$B$17)*SUM($C$5:C6)</f>
-        <v>-86.1258387</v>
+        <v>-78.296217</v>
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">(G6+H6)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W6" s="15" t="n">
         <f aca="false">IF(V6&gt;0,DATE(YEAR(B6),MONTH(B6)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3818,15 +3818,15 @@
       </c>
       <c r="X6" s="12" t="n">
         <f aca="false">X5-Y5+C6*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y6" s="12" t="n">
         <f aca="false">IF(OR(X6&gt;=Premissas!$B$13,B6=DATE(YEAR(B6),MONTH(B6)+1,0)),X6,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z6" s="12" t="n">
         <f aca="false">Z5-AA5+C6/Premissas!$B$18*Premissas!$B$20</f>
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="AA6" s="12" t="n">
         <f aca="false">IF(OR(Z6&gt;=Premissas!$B$14,B6=DATE(YEAR(B6),MONTH(B6)+1,0)),Z6,0)</f>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C7" s="12" t="n">
         <f aca="false">IF(A7&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A7&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A7&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">IF(Y7&gt;0,IF(DAY(B7)&lt;=Premissas!$B$12,DATE(YEAR(B7),MONTH(B7),Premissas!$B$16),DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3863,19 +3863,19 @@
       </c>
       <c r="G7" s="29" t="n">
         <f aca="false">C7/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H7" s="29" t="n">
         <f aca="false">C7/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I7" s="12" t="n">
         <f aca="false">-IF($A7-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A7-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -3887,11 +3887,11 @@
       </c>
       <c r="M7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N7" s="12" t="n">
         <f aca="false">-IF($A7-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O7" s="12" t="n">
         <f aca="false">IF($A7-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A7-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="R7" s="12" t="n">
         <f aca="false">E7+F7+SUM(I7:Q7)</f>
-        <v>-60.44171782</v>
+        <v>-54.9470162</v>
       </c>
       <c r="S7" s="12" t="n">
         <f aca="false">S6+R7</f>
-        <v>-21.35455652</v>
+        <v>-19.4132332</v>
       </c>
       <c r="T7" s="15" t="n">
         <f aca="false">IF(AND($A7&gt;$B$100,S7&gt;=0),1,0)</f>
@@ -3919,11 +3919,11 @@
       </c>
       <c r="U7" s="12" t="n">
         <f aca="false">S7-SUM($E$5:E7)-(1+Premissas!$B$17)*SUM($C$5:C7)</f>
-        <v>-209.17405652</v>
+        <v>-190.1582332</v>
       </c>
       <c r="V7" s="12" t="n">
         <f aca="false">(G7+H7)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W7" s="15" t="n">
         <f aca="false">IF(V7&gt;0,DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X7" s="12" t="n">
         <f aca="false">X6-Y6+C7*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y7" s="12" t="n">
         <f aca="false">IF(OR(X7&gt;=Premissas!$B$13,B7=DATE(YEAR(B7),MONTH(B7)+1,0)),X7,0)</f>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="Z7" s="12" t="n">
         <f aca="false">Z6-AA6+C7/Premissas!$B$18*Premissas!$B$20</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AA7" s="12" t="n">
         <f aca="false">IF(OR(Z7&gt;=Premissas!$B$14,B7=DATE(YEAR(B7),MONTH(B7)+1,0)),Z7,0)</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AB7" s="15" t="n">
         <f aca="false">IF(AA7&gt;0,IF(DAY(B7)&lt;=Premissas!$B$12,DATE(YEAR(B7),MONTH(B7),Premissas!$B$16),DATE(YEAR(B7),MONTH(B7)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">IF(A8&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A8&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A8&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">IF(Y8&gt;0,IF(DAY(B8)&lt;=Premissas!$B$12,DATE(YEAR(B8),MONTH(B8),Premissas!$B$16),DATE(YEAR(B8),MONTH(B8)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -3976,19 +3976,19 @@
       </c>
       <c r="G8" s="29" t="n">
         <f aca="false">C8/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H8" s="29" t="n">
         <f aca="false">C8/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">-IF($A8-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A8-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="M8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">-IF($A8-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O8" s="12" t="n">
         <f aca="false">IF($A8-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A8-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="R8" s="12" t="n">
         <f aca="false">E8+F8+SUM(I8:Q8)</f>
-        <v>-60.44171782</v>
+        <v>-54.9470162</v>
       </c>
       <c r="S8" s="12" t="n">
         <f aca="false">S7+R8</f>
-        <v>-81.7962743399999</v>
+        <v>-74.3602494</v>
       </c>
       <c r="T8" s="15" t="n">
         <f aca="false">IF(AND($A8&gt;$B$100,S8&gt;=0),1,0)</f>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="U8" s="12" t="n">
         <f aca="false">S8-SUM($E$5:E8)-(1+Premissas!$B$17)*SUM($C$5:C8)</f>
-        <v>-332.22227434</v>
+        <v>-302.0202494</v>
       </c>
       <c r="V8" s="12" t="n">
         <f aca="false">(G8+H8)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W8" s="15" t="n">
         <f aca="false">IF(V8&gt;0,DATE(YEAR(B8),MONTH(B8)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4044,15 +4044,15 @@
       </c>
       <c r="X8" s="12" t="n">
         <f aca="false">X7-Y7+C8*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y8" s="12" t="n">
         <f aca="false">IF(OR(X8&gt;=Premissas!$B$13,B8=DATE(YEAR(B8),MONTH(B8)+1,0)),X8,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z8" s="12" t="n">
         <f aca="false">Z7-AA7+C8/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="12" t="n">
         <f aca="false">IF(OR(Z8&gt;=Premissas!$B$14,B8=DATE(YEAR(B8),MONTH(B8)+1,0)),Z8,0)</f>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">IF(A9&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A9&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A9&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">IF(Y9&gt;0,IF(DAY(B9)&lt;=Premissas!$B$12,DATE(YEAR(B9),MONTH(B9),Premissas!$B$16),DATE(YEAR(B9),MONTH(B9)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4089,19 +4089,19 @@
       </c>
       <c r="G9" s="29" t="n">
         <f aca="false">C9/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">C9/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">-IF($A9-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A9-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4113,11 +4113,11 @@
       </c>
       <c r="M9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">-IF($A9-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O9" s="12" t="n">
         <f aca="false">IF($A9-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A9-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4133,11 +4133,11 @@
       </c>
       <c r="R9" s="12" t="n">
         <f aca="false">E9+F9+SUM(I9:Q9)</f>
-        <v>-60.44171782</v>
+        <v>-54.9470162</v>
       </c>
       <c r="S9" s="12" t="n">
         <f aca="false">S8+R9</f>
-        <v>-142.23799216</v>
+        <v>-129.3072656</v>
       </c>
       <c r="T9" s="15" t="n">
         <f aca="false">IF(AND($A9&gt;$B$100,S9&gt;=0),1,0)</f>
@@ -4145,11 +4145,11 @@
       </c>
       <c r="U9" s="12" t="n">
         <f aca="false">S9-SUM($E$5:E9)-(1+Premissas!$B$17)*SUM($C$5:C9)</f>
-        <v>-455.27049216</v>
+        <v>-413.8822656</v>
       </c>
       <c r="V9" s="12" t="n">
         <f aca="false">(G9+H9)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W9" s="15" t="n">
         <f aca="false">IF(V9&gt;0,DATE(YEAR(B9),MONTH(B9)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="X9" s="12" t="n">
         <f aca="false">X8-Y8+C9*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y9" s="12" t="n">
         <f aca="false">IF(OR(X9&gt;=Premissas!$B$13,B9=DATE(YEAR(B9),MONTH(B9)+1,0)),X9,0)</f>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="Z9" s="12" t="n">
         <f aca="false">Z8-AA8+C9/Premissas!$B$18*Premissas!$B$20</f>
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="AA9" s="12" t="n">
         <f aca="false">IF(OR(Z9&gt;=Premissas!$B$14,B9=DATE(YEAR(B9),MONTH(B9)+1,0)),Z9,0)</f>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">IF(A10&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A10&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A10&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">IF(Y10&gt;0,IF(DAY(B10)&lt;=Premissas!$B$12,DATE(YEAR(B10),MONTH(B10),Premissas!$B$16),DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4202,19 +4202,19 @@
       </c>
       <c r="G10" s="29" t="n">
         <f aca="false">C10/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H10" s="29" t="n">
         <f aca="false">C10/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">-IF($A10-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A10-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4226,11 +4226,11 @@
       </c>
       <c r="M10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">-IF($A10-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O10" s="12" t="n">
         <f aca="false">IF($A10-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A10-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4246,11 +4246,11 @@
       </c>
       <c r="R10" s="12" t="n">
         <f aca="false">E10+F10+SUM(I10:Q10)</f>
-        <v>-60.44171782</v>
+        <v>-54.9470162</v>
       </c>
       <c r="S10" s="12" t="n">
         <f aca="false">S9+R10</f>
-        <v>-202.67970998</v>
+        <v>-184.2542818</v>
       </c>
       <c r="T10" s="15" t="n">
         <f aca="false">IF(AND($A10&gt;$B$100,S10&gt;=0),1,0)</f>
@@ -4258,11 +4258,11 @@
       </c>
       <c r="U10" s="12" t="n">
         <f aca="false">S10-SUM($E$5:E10)-(1+Premissas!$B$17)*SUM($C$5:C10)</f>
-        <v>-578.31870998</v>
+        <v>-525.7442818</v>
       </c>
       <c r="V10" s="12" t="n">
         <f aca="false">(G10+H10)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W10" s="15" t="n">
         <f aca="false">IF(V10&gt;0,DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4270,19 +4270,19 @@
       </c>
       <c r="X10" s="12" t="n">
         <f aca="false">X9-Y9+C10*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y10" s="12" t="n">
         <f aca="false">IF(OR(X10&gt;=Premissas!$B$13,B10=DATE(YEAR(B10),MONTH(B10)+1,0)),X10,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z10" s="12" t="n">
         <f aca="false">Z9-AA9+C10/Premissas!$B$18*Premissas!$B$20</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AA10" s="12" t="n">
         <f aca="false">IF(OR(Z10&gt;=Premissas!$B$14,B10=DATE(YEAR(B10),MONTH(B10)+1,0)),Z10,0)</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AB10" s="15" t="n">
         <f aca="false">IF(AA10&gt;0,IF(DAY(B10)&lt;=Premissas!$B$12,DATE(YEAR(B10),MONTH(B10),Premissas!$B$16),DATE(YEAR(B10),MONTH(B10)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">IF(A11&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A11&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A11&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">IF(Y11&gt;0,IF(DAY(B11)&lt;=Premissas!$B$12,DATE(YEAR(B11),MONTH(B11),Premissas!$B$16),DATE(YEAR(B11),MONTH(B11)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4315,19 +4315,19 @@
       </c>
       <c r="G11" s="29" t="n">
         <f aca="false">C11/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H11" s="29" t="n">
         <f aca="false">C11/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">-IF($A11-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A11-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="M11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">-IF($A11-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O11" s="12" t="n">
         <f aca="false">IF($A11-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A11-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4359,11 +4359,11 @@
       </c>
       <c r="R11" s="12" t="n">
         <f aca="false">E11+F11+SUM(I11:Q11)</f>
-        <v>-60.44171782</v>
+        <v>-54.9470162</v>
       </c>
       <c r="S11" s="12" t="n">
         <f aca="false">S10+R11</f>
-        <v>-263.1214278</v>
+        <v>-239.201298</v>
       </c>
       <c r="T11" s="15" t="n">
         <f aca="false">IF(AND($A11&gt;$B$100,S11&gt;=0),1,0)</f>
@@ -4371,11 +4371,11 @@
       </c>
       <c r="U11" s="12" t="n">
         <f aca="false">S11-SUM($E$5:E11)-(1+Premissas!$B$17)*SUM($C$5:C11)</f>
-        <v>-701.3669278</v>
+        <v>-637.606298</v>
       </c>
       <c r="V11" s="12" t="n">
         <f aca="false">(G11+H11)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">IF(V11&gt;0,DATE(YEAR(B11),MONTH(B11)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="X11" s="12" t="n">
         <f aca="false">X10-Y10+C11*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y11" s="12" t="n">
         <f aca="false">IF(OR(X11&gt;=Premissas!$B$13,B11=DATE(YEAR(B11),MONTH(B11)+1,0)),X11,0)</f>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="Z11" s="12" t="n">
         <f aca="false">Z10-AA10+C11/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="12" t="n">
         <f aca="false">IF(OR(Z11&gt;=Premissas!$B$14,B11=DATE(YEAR(B11),MONTH(B11)+1,0)),Z11,0)</f>
@@ -4436,11 +4436,11 @@
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">-IF($A12-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A12-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">-IF($A12-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O12" s="12" t="n">
         <f aca="false">IF($A12-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A12-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="R12" s="12" t="n">
         <f aca="false">E12+F12+SUM(I12:Q12)</f>
-        <v>-184.65397797</v>
+        <v>-167.8672527</v>
       </c>
       <c r="S12" s="12" t="n">
         <f aca="false">S11+R12</f>
-        <v>-447.77540577</v>
+        <v>-407.0685507</v>
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(AND($A12&gt;$B$100,S12&gt;=0),1,0)</f>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="U12" s="12" t="n">
         <f aca="false">S12-SUM($E$5:E12)-(1+Premissas!$B$17)*SUM($C$5:C12)</f>
-        <v>-886.02090577</v>
+        <v>-805.4735507</v>
       </c>
       <c r="V12" s="12" t="n">
         <f aca="false">(G12+H12)*Premissas!$B$21</f>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="X12" s="12" t="n">
         <f aca="false">X11-Y11+C12*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y12" s="12" t="n">
         <f aca="false">IF(OR(X12&gt;=Premissas!$B$13,B12=DATE(YEAR(B12),MONTH(B12)+1,0)),X12,0)</f>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z12" s="12" t="n">
         <f aca="false">Z11-AA11+C12/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA12" s="12" t="n">
         <f aca="false">IF(OR(Z12&gt;=Premissas!$B$14,B12=DATE(YEAR(B12),MONTH(B12)+1,0)),Z12,0)</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K13" s="12" t="n">
         <f aca="false">IF($A13-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A13-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -4585,11 +4585,11 @@
       </c>
       <c r="R13" s="12" t="n">
         <f aca="false">E13+F13+SUM(I13:Q13)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="S13" s="12" t="n">
         <f aca="false">S12+R13</f>
-        <v>-423.09202474</v>
+        <v>-384.6291134</v>
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(AND($A13&gt;$B$100,S13&gt;=0),1,0)</f>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="U13" s="12" t="n">
         <f aca="false">S13-SUM($E$5:E13)-(1+Premissas!$B$17)*SUM($C$5:C13)</f>
-        <v>-861.33752474</v>
+        <v>-783.0341134</v>
       </c>
       <c r="V13" s="12" t="n">
         <f aca="false">(G13+H13)*Premissas!$B$21</f>
@@ -4609,19 +4609,19 @@
       </c>
       <c r="X13" s="12" t="n">
         <f aca="false">X12-Y12+C13*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y13" s="12" t="n">
         <f aca="false">IF(OR(X13&gt;=Premissas!$B$13,B13=DATE(YEAR(B13),MONTH(B13)+1,0)),X13,0)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Z13" s="12" t="n">
         <f aca="false">Z12-AA12+C13/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA13" s="12" t="n">
         <f aca="false">IF(OR(Z13&gt;=Premissas!$B$14,B13=DATE(YEAR(B13),MONTH(B13)+1,0)),Z13,0)</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AB13" s="15" t="n">
         <f aca="false">IF(AA13&gt;0,IF(DAY(B13)&lt;=Premissas!$B$12,DATE(YEAR(B13),MONTH(B13),Premissas!$B$16),DATE(YEAR(B13),MONTH(B13)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">IF(A14&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A14&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A14&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D14" s="15" t="n">
         <f aca="false">IF(Y14&gt;0,IF(DAY(B14)&lt;=Premissas!$B$12,DATE(YEAR(B14),MONTH(B14),Premissas!$B$16),DATE(YEAR(B14),MONTH(B14)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4654,11 +4654,11 @@
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">C14/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H14" s="29" t="n">
         <f aca="false">C14/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">-IF($A14-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="K14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="M14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">-IF($A14-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O14" s="12" t="n">
         <f aca="false">IF($A14-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P14" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A14-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A14-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A14-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A14-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="R14" s="12" t="n">
         <f aca="false">E14+F14+SUM(I14:Q14)</f>
-        <v>104.018826816667</v>
+        <v>94.5625698333334</v>
       </c>
       <c r="S14" s="12" t="n">
         <f aca="false">S13+R14</f>
-        <v>-319.073197923333</v>
+        <v>-290.066543566667</v>
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(AND($A14&gt;$B$100,S14&gt;=0),1,0)</f>
@@ -4710,11 +4710,11 @@
       </c>
       <c r="U14" s="12" t="n">
         <f aca="false">S14-SUM($E$5:E14)-(1+Premissas!$B$17)*SUM($C$5:C14)</f>
-        <v>-819.925197923333</v>
+        <v>-745.386543566667</v>
       </c>
       <c r="V14" s="12" t="n">
         <f aca="false">(G14+H14)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W14" s="15" t="n">
         <f aca="false">IF(V14&gt;0,DATE(YEAR(B14),MONTH(B14)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="X14" s="12" t="n">
         <f aca="false">X13-Y13+C14*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y14" s="12" t="n">
         <f aca="false">IF(OR(X14&gt;=Premissas!$B$13,B14=DATE(YEAR(B14),MONTH(B14)+1,0)),X14,0)</f>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z14" s="12" t="n">
         <f aca="false">Z13-AA13+C14/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA14" s="12" t="n">
         <f aca="false">IF(OR(Z14&gt;=Premissas!$B$14,B14=DATE(YEAR(B14),MONTH(B14)+1,0)),Z14,0)</f>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">IF(A15&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A15&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A15&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D15" s="15" t="n">
         <f aca="false">IF(Y15&gt;0,IF(DAY(B15)&lt;=Premissas!$B$12,DATE(YEAR(B15),MONTH(B15),Premissas!$B$16),DATE(YEAR(B15),MONTH(B15)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4767,15 +4767,15 @@
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">C15/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H15" s="29" t="n">
         <f aca="false">C15/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
         <f aca="false">-IF($A15-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="K15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4791,15 +4791,15 @@
       </c>
       <c r="M15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N15" s="12" t="n">
         <f aca="false">-IF($A15-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O15" s="12" t="n">
         <f aca="false">IF($A15-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P15" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A15-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A15-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A15-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A15-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4811,11 +4811,11 @@
       </c>
       <c r="R15" s="12" t="n">
         <f aca="false">E15+F15+SUM(I15:Q15)</f>
-        <v>-105.318532183333</v>
+        <v>-95.7441201666667</v>
       </c>
       <c r="S15" s="12" t="n">
         <f aca="false">S14+R15</f>
-        <v>-424.391730106667</v>
+        <v>-385.810663733333</v>
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(AND($A15&gt;$B$100,S15&gt;=0),1,0)</f>
@@ -4823,11 +4823,11 @@
       </c>
       <c r="U15" s="12" t="n">
         <f aca="false">S15-SUM($E$5:E15)-(1+Premissas!$B$17)*SUM($C$5:C15)</f>
-        <v>-987.850230106667</v>
+        <v>-898.045663733333</v>
       </c>
       <c r="V15" s="12" t="n">
         <f aca="false">(G15+H15)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W15" s="15" t="n">
         <f aca="false">IF(V15&gt;0,DATE(YEAR(B15),MONTH(B15)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4835,15 +4835,15 @@
       </c>
       <c r="X15" s="12" t="n">
         <f aca="false">X14-Y14+C15*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y15" s="12" t="n">
         <f aca="false">IF(OR(X15&gt;=Premissas!$B$13,B15=DATE(YEAR(B15),MONTH(B15)+1,0)),X15,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z15" s="12" t="n">
         <f aca="false">Z14-AA14+C15/Premissas!$B$18*Premissas!$B$20</f>
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="AA15" s="12" t="n">
         <f aca="false">IF(OR(Z15&gt;=Premissas!$B$14,B15=DATE(YEAR(B15),MONTH(B15)+1,0)),Z15,0)</f>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">IF(A16&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A16&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A16&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D16" s="15" t="n">
         <f aca="false">IF(Y16&gt;0,IF(DAY(B16)&lt;=Premissas!$B$12,DATE(YEAR(B16),MONTH(B16),Premissas!$B$16),DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4880,23 +4880,23 @@
       </c>
       <c r="G16" s="29" t="n">
         <f aca="false">C16/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H16" s="29" t="n">
         <f aca="false">C16/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">-IF($A16-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -4904,15 +4904,15 @@
       </c>
       <c r="M16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">-IF($A16-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O16" s="12" t="n">
         <f aca="false">IF($A16-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P16" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A16-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A16-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A16-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A16-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -4924,11 +4924,11 @@
       </c>
       <c r="R16" s="12" t="n">
         <f aca="false">E16+F16+SUM(I16:Q16)</f>
-        <v>-80.6351511533333</v>
+        <v>-73.3046828666667</v>
       </c>
       <c r="S16" s="12" t="n">
         <f aca="false">S15+R16</f>
-        <v>-505.02688126</v>
+        <v>-459.1153466</v>
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(AND($A16&gt;$B$100,S16&gt;=0),1,0)</f>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="U16" s="12" t="n">
         <f aca="false">S16-SUM($E$5:E16)-(1+Premissas!$B$17)*SUM($C$5:C16)</f>
-        <v>-1131.09188126</v>
+        <v>-1028.2653466</v>
       </c>
       <c r="V16" s="12" t="n">
         <f aca="false">(G16+H16)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W16" s="15" t="n">
         <f aca="false">IF(V16&gt;0,DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="X16" s="12" t="n">
         <f aca="false">X15-Y15+C16*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y16" s="12" t="n">
         <f aca="false">IF(OR(X16&gt;=Premissas!$B$13,B16=DATE(YEAR(B16),MONTH(B16)+1,0)),X16,0)</f>
@@ -4956,11 +4956,11 @@
       </c>
       <c r="Z16" s="12" t="n">
         <f aca="false">Z15-AA15+C16/Premissas!$B$18*Premissas!$B$20</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AA16" s="12" t="n">
         <f aca="false">IF(OR(Z16&gt;=Premissas!$B$14,B16=DATE(YEAR(B16),MONTH(B16)+1,0)),Z16,0)</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AB16" s="15" t="n">
         <f aca="false">IF(AA16&gt;0,IF(DAY(B16)&lt;=Premissas!$B$12,DATE(YEAR(B16),MONTH(B16),Premissas!$B$16),DATE(YEAR(B16),MONTH(B16)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(A17&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A17&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A17&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">IF(Y17&gt;0,IF(DAY(B17)&lt;=Premissas!$B$12,DATE(YEAR(B17),MONTH(B17),Premissas!$B$16),DATE(YEAR(B17),MONTH(B17)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -4993,23 +4993,23 @@
       </c>
       <c r="G17" s="29" t="n">
         <f aca="false">C17/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H17" s="29" t="n">
         <f aca="false">C17/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I17" s="12" t="n">
         <f aca="false">-IF($A17-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5017,15 +5017,15 @@
       </c>
       <c r="M17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N17" s="12" t="n">
         <f aca="false">-IF($A17-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O17" s="12" t="n">
         <f aca="false">IF($A17-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P17" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A17-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A17-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A17-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A17-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5037,11 +5037,11 @@
       </c>
       <c r="R17" s="12" t="n">
         <f aca="false">E17+F17+SUM(I17:Q17)</f>
-        <v>-80.6351511533333</v>
+        <v>-73.3046828666667</v>
       </c>
       <c r="S17" s="12" t="n">
         <f aca="false">S16+R17</f>
-        <v>-585.662032413333</v>
+        <v>-532.420029466667</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(AND($A17&gt;$B$100,S17&gt;=0),1,0)</f>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="U17" s="12" t="n">
         <f aca="false">S17-SUM($E$5:E17)-(1+Premissas!$B$17)*SUM($C$5:C17)</f>
-        <v>-1274.33353241333</v>
+        <v>-1158.48502946667</v>
       </c>
       <c r="V17" s="12" t="n">
         <f aca="false">(G17+H17)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">IF(V17&gt;0,DATE(YEAR(B17),MONTH(B17)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5061,15 +5061,15 @@
       </c>
       <c r="X17" s="12" t="n">
         <f aca="false">X16-Y16+C17*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y17" s="12" t="n">
         <f aca="false">IF(OR(X17&gt;=Premissas!$B$13,B17=DATE(YEAR(B17),MONTH(B17)+1,0)),X17,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z17" s="12" t="n">
         <f aca="false">Z16-AA16+C17/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA17" s="12" t="n">
         <f aca="false">IF(OR(Z17&gt;=Premissas!$B$14,B17=DATE(YEAR(B17),MONTH(B17)+1,0)),Z17,0)</f>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">IF(A18&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A18&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A18&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">IF(Y18&gt;0,IF(DAY(B18)&lt;=Premissas!$B$12,DATE(YEAR(B18),MONTH(B18),Premissas!$B$16),DATE(YEAR(B18),MONTH(B18)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5106,23 +5106,23 @@
       </c>
       <c r="G18" s="29" t="n">
         <f aca="false">C18/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">C18/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
         <f aca="false">-IF($A18-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5130,15 +5130,15 @@
       </c>
       <c r="M18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N18" s="12" t="n">
         <f aca="false">-IF($A18-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O18" s="12" t="n">
         <f aca="false">IF($A18-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P18" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A18-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A18-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A18-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A18-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5150,11 +5150,11 @@
       </c>
       <c r="R18" s="12" t="n">
         <f aca="false">E18+F18+SUM(I18:Q18)</f>
-        <v>-80.6351511533333</v>
+        <v>-73.3046828666667</v>
       </c>
       <c r="S18" s="12" t="n">
         <f aca="false">S17+R18</f>
-        <v>-666.297183566667</v>
+        <v>-605.724712333333</v>
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(AND($A18&gt;$B$100,S18&gt;=0),1,0)</f>
@@ -5162,11 +5162,11 @@
       </c>
       <c r="U18" s="12" t="n">
         <f aca="false">S18-SUM($E$5:E18)-(1+Premissas!$B$17)*SUM($C$5:C18)</f>
-        <v>-1417.57518356667</v>
+        <v>-1288.70471233333</v>
       </c>
       <c r="V18" s="12" t="n">
         <f aca="false">(G18+H18)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">IF(V18&gt;0,DATE(YEAR(B18),MONTH(B18)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="X18" s="12" t="n">
         <f aca="false">X17-Y17+C18*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y18" s="12" t="n">
         <f aca="false">IF(OR(X18&gt;=Premissas!$B$13,B18=DATE(YEAR(B18),MONTH(B18)+1,0)),X18,0)</f>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z18" s="12" t="n">
         <f aca="false">Z17-AA17+C18/Premissas!$B$18*Premissas!$B$20</f>
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="AA18" s="12" t="n">
         <f aca="false">IF(OR(Z18&gt;=Premissas!$B$14,B18=DATE(YEAR(B18),MONTH(B18)+1,0)),Z18,0)</f>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">IF(A19&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A19&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A19&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">IF(Y19&gt;0,IF(DAY(B19)&lt;=Premissas!$B$12,DATE(YEAR(B19),MONTH(B19),Premissas!$B$16),DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5219,23 +5219,23 @@
       </c>
       <c r="G19" s="29" t="n">
         <f aca="false">C19/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H19" s="29" t="n">
         <f aca="false">C19/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
         <f aca="false">-IF($A19-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5243,15 +5243,15 @@
       </c>
       <c r="M19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N19" s="12" t="n">
         <f aca="false">-IF($A19-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O19" s="12" t="n">
         <f aca="false">IF($A19-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P19" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A19-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A19-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A19-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A19-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5263,11 +5263,11 @@
       </c>
       <c r="R19" s="12" t="n">
         <f aca="false">E19+F19+SUM(I19:Q19)</f>
-        <v>-80.6351511533333</v>
+        <v>-73.3046828666667</v>
       </c>
       <c r="S19" s="12" t="n">
         <f aca="false">S18+R19</f>
-        <v>-746.93233472</v>
+        <v>-679.0293952</v>
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(AND($A19&gt;$B$100,S19&gt;=0),1,0)</f>
@@ -5275,11 +5275,11 @@
       </c>
       <c r="U19" s="12" t="n">
         <f aca="false">S19-SUM($E$5:E19)-(1+Premissas!$B$17)*SUM($C$5:C19)</f>
-        <v>-1560.81683472</v>
+        <v>-1418.9243952</v>
       </c>
       <c r="V19" s="12" t="n">
         <f aca="false">(G19+H19)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">IF(V19&gt;0,DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5287,19 +5287,19 @@
       </c>
       <c r="X19" s="12" t="n">
         <f aca="false">X18-Y18+C19*(1+Premissas!$B$17)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Y19" s="12" t="n">
         <f aca="false">IF(OR(X19&gt;=Premissas!$B$13,B19=DATE(YEAR(B19),MONTH(B19)+1,0)),X19,0)</f>
-        <v>125.213</v>
+        <v>113.83</v>
       </c>
       <c r="Z19" s="12" t="n">
         <f aca="false">Z18-AA18+C19/Premissas!$B$18*Premissas!$B$20</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AA19" s="12" t="n">
         <f aca="false">IF(OR(Z19&gt;=Premissas!$B$14,B19=DATE(YEAR(B19),MONTH(B19)+1,0)),Z19,0)</f>
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="AB19" s="15" t="n">
         <f aca="false">IF(AA19&gt;0,IF(DAY(B19)&lt;=Premissas!$B$12,DATE(YEAR(B19),MONTH(B19),Premissas!$B$16),DATE(YEAR(B19),MONTH(B19)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">IF(A20&lt;=Premissas!$B$7,Premissas!$B$6/Premissas!$B$7,IF(A20&lt;=Premissas!$B$7+Premissas!$B$8,0,IF(A20&lt;=Premissas!$B$7+Premissas!$B$8+Premissas!$B$10,Premissas!$B$9/Premissas!$B$10,0)))</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">IF(Y20&gt;0,IF(DAY(B20)&lt;=Premissas!$B$12,DATE(YEAR(B20),MONTH(B20),Premissas!$B$16),DATE(YEAR(B20),MONTH(B20)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5332,23 +5332,23 @@
       </c>
       <c r="G20" s="29" t="n">
         <f aca="false">C20/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
-        <v>2.56666666666667</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">C20/Premissas!$B$18*Premissas!$B$19*Premissas!$B$24</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
         <f aca="false">-IF($A20-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -5356,15 +5356,15 @@
       </c>
       <c r="M20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
-        <v>124.21226015</v>
+        <v>112.9202365</v>
       </c>
       <c r="N20" s="12" t="n">
         <f aca="false">-IF($A20-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O20" s="12" t="n">
         <f aca="false">IF($A20-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P20" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A20-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A20-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A20-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A20-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5376,11 +5376,11 @@
       </c>
       <c r="R20" s="12" t="n">
         <f aca="false">E20+F20+SUM(I20:Q20)</f>
-        <v>-80.6351511533333</v>
+        <v>-73.3046828666667</v>
       </c>
       <c r="S20" s="12" t="n">
         <f aca="false">S19+R20</f>
-        <v>-827.567485873333</v>
+        <v>-752.334078066667</v>
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(AND($A20&gt;$B$100,S20&gt;=0),1,0)</f>
@@ -5388,11 +5388,11 @@
       </c>
       <c r="U20" s="12" t="n">
         <f aca="false">S20-SUM($E$5:E20)-(1+Premissas!$B$17)*SUM($C$5:C20)</f>
-        <v>-1704.05848587333</v>
+        <v>-1549.14407806667</v>
       </c>
       <c r="V20" s="12" t="n">
         <f aca="false">(G20+H20)*Premissas!$B$21</f>
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">IF(V20&gt;0,DATE(YEAR(B20),MONTH(B20)+1,Premissas!$B$16)-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="X20" s="12" t="n">
         <f aca="false">X19-Y19+C20*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y20" s="12" t="n">
         <f aca="false">IF(OR(X20&gt;=Premissas!$B$13,B20=DATE(YEAR(B20),MONTH(B20)+1,0)),X20,0)</f>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="Z20" s="12" t="n">
         <f aca="false">Z19-AA19+C20/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA20" s="12" t="n">
         <f aca="false">IF(OR(Z20&gt;=Premissas!$B$14,B20=DATE(YEAR(B20),MONTH(B20)+1,0)),Z20,0)</f>
@@ -5453,11 +5453,11 @@
       </c>
       <c r="I21" s="12" t="n">
         <f aca="false">-IF($A21-(Premissas!$B$60)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))</f>
-        <v>-170.837359</v>
+        <v>-155.30669</v>
       </c>
       <c r="J21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="L21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A21-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="N21" s="12" t="n">
         <f aca="false">-IF($A21-(Premissas!$B$60)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$60)),0)*(Premissas!$B$59*Unitário!$B$22+Premissas!$B$31)</f>
-        <v>-38.5</v>
+        <v>-35</v>
       </c>
       <c r="O21" s="12" t="n">
         <f aca="false">IF($A21-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A21-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
@@ -5489,11 +5489,11 @@
       </c>
       <c r="R21" s="12" t="n">
         <f aca="false">E21+F21+SUM(I21:Q21)</f>
-        <v>58.73532203</v>
+        <v>53.3957473</v>
       </c>
       <c r="S21" s="12" t="n">
         <f aca="false">S20+R21</f>
-        <v>-768.832163843333</v>
+        <v>-698.938330766667</v>
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(AND($A21&gt;$B$100,S21&gt;=0),1,0)</f>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="U21" s="12" t="n">
         <f aca="false">S21-SUM($E$5:E21)-(1+Premissas!$B$17)*SUM($C$5:C21)</f>
-        <v>-1645.32316384333</v>
+        <v>-1495.74833076667</v>
       </c>
       <c r="V21" s="12" t="n">
         <f aca="false">(G21+H21)*Premissas!$B$21</f>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="X21" s="12" t="n">
         <f aca="false">X20-Y20+C21*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y21" s="12" t="n">
         <f aca="false">IF(OR(X21&gt;=Premissas!$B$13,B21=DATE(YEAR(B21),MONTH(B21)+1,0)),X21,0)</f>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="Z21" s="12" t="n">
         <f aca="false">Z20-AA20+C21/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="12" t="n">
         <f aca="false">IF(OR(Z21&gt;=Premissas!$B$14,B21=DATE(YEAR(B21),MONTH(B21)+1,0)),Z21,0)</f>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="J22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54)),0)*Premissas!$B$26*((Premissas!$B$59*Unitário!$B$22+(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25))-Premissas!$B$39)</f>
-        <v>24.68338103</v>
+        <v>22.4394373</v>
       </c>
       <c r="K22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="L22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A22-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF($A22-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A22-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5602,11 +5602,11 @@
       </c>
       <c r="R22" s="12" t="n">
         <f aca="false">E22+F22+SUM(I22:Q22)</f>
-        <v>268.07268103</v>
+        <v>243.7024373</v>
       </c>
       <c r="S22" s="12" t="n">
         <f aca="false">S21+R22</f>
-        <v>-500.759482813333</v>
+        <v>-455.235893466667</v>
       </c>
       <c r="T22" s="15" t="n">
         <f aca="false">IF(AND($A22&gt;$B$100,S22&gt;=0),1,0)</f>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="U22" s="12" t="n">
         <f aca="false">S22-SUM($E$5:E22)-(1+Premissas!$B$17)*SUM($C$5:C22)</f>
-        <v>-1377.25048281333</v>
+        <v>-1252.04589346667</v>
       </c>
       <c r="V22" s="12" t="n">
         <f aca="false">(G22+H22)*Premissas!$B$21</f>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="X22" s="12" t="n">
         <f aca="false">X21-Y21+C22*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y22" s="12" t="n">
         <f aca="false">IF(OR(X22&gt;=Premissas!$B$13,B22=DATE(YEAR(B22),MONTH(B22)+1,0)),X22,0)</f>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Z22" s="12" t="n">
         <f aca="false">Z21-AA21+C22/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA22" s="12" t="n">
         <f aca="false">IF(OR(Z22&gt;=Premissas!$B$14,B22=DATE(YEAR(B22),MONTH(B22)+1,0)),Z22,0)</f>
@@ -5687,11 +5687,11 @@
       </c>
       <c r="K23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="O23" s="12" t="n">
         <f aca="false">IF($A23-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P23" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A23-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A23-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A23-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A23-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5715,11 +5715,11 @@
       </c>
       <c r="R23" s="12" t="n">
         <f aca="false">E23+F23+SUM(I23:Q23)</f>
-        <v>223.195866666667</v>
+        <v>202.905333333333</v>
       </c>
       <c r="S23" s="12" t="n">
         <f aca="false">S22+R23</f>
-        <v>-277.563616146667</v>
+        <v>-252.330560133333</v>
       </c>
       <c r="T23" s="15" t="n">
         <f aca="false">IF(AND($A23&gt;$B$100,S23&gt;=0),1,0)</f>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="U23" s="12" t="n">
         <f aca="false">S23-SUM($E$5:E23)-(1+Premissas!$B$17)*SUM($C$5:C23)</f>
-        <v>-1154.05461614667</v>
+        <v>-1049.14056013333</v>
       </c>
       <c r="V23" s="12" t="n">
         <f aca="false">(G23+H23)*Premissas!$B$21</f>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="X23" s="12" t="n">
         <f aca="false">X22-Y22+C23*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y23" s="12" t="n">
         <f aca="false">IF(OR(X23&gt;=Premissas!$B$13,B23=DATE(YEAR(B23),MONTH(B23)+1,0)),X23,0)</f>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="Z23" s="12" t="n">
         <f aca="false">Z22-AA22+C23/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA23" s="12" t="n">
         <f aca="false">IF(OR(Z23&gt;=Premissas!$B$14,B23=DATE(YEAR(B23),MONTH(B23)+1,0)),Z23,0)</f>
@@ -5800,11 +5800,11 @@
       </c>
       <c r="K24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="O24" s="12" t="n">
         <f aca="false">IF($A24-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P24" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A24-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A24-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A24-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A24-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="R24" s="12" t="n">
         <f aca="false">E24+F24+SUM(I24:Q24)</f>
-        <v>223.195866666667</v>
+        <v>202.905333333333</v>
       </c>
       <c r="S24" s="12" t="n">
         <f aca="false">S23+R24</f>
-        <v>-54.3677494800001</v>
+        <v>-49.4252268000001</v>
       </c>
       <c r="T24" s="15" t="n">
         <f aca="false">IF(AND($A24&gt;$B$100,S24&gt;=0),1,0)</f>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="U24" s="12" t="n">
         <f aca="false">S24-SUM($E$5:E24)-(1+Premissas!$B$17)*SUM($C$5:C24)</f>
-        <v>-930.85874948</v>
+        <v>-846.2352268</v>
       </c>
       <c r="V24" s="12" t="n">
         <f aca="false">(G24+H24)*Premissas!$B$21</f>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="X24" s="12" t="n">
         <f aca="false">X23-Y23+C24*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y24" s="12" t="n">
         <f aca="false">IF(OR(X24&gt;=Premissas!$B$13,B24=DATE(YEAR(B24),MONTH(B24)+1,0)),X24,0)</f>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Z24" s="12" t="n">
         <f aca="false">Z23-AA23+C24/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA24" s="12" t="n">
         <f aca="false">IF(OR(Z24&gt;=Premissas!$B$14,B24=DATE(YEAR(B24),MONTH(B24)+1,0)),Z24,0)</f>
@@ -5913,11 +5913,11 @@
       </c>
       <c r="K25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="O25" s="12" t="n">
         <f aca="false">IF($A25-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P25" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A25-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A25-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A25-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A25-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -5941,11 +5941,11 @@
       </c>
       <c r="R25" s="12" t="n">
         <f aca="false">E25+F25+SUM(I25:Q25)</f>
-        <v>223.195866666667</v>
+        <v>202.905333333333</v>
       </c>
       <c r="S25" s="12" t="n">
         <f aca="false">S24+R25</f>
-        <v>168.828117186667</v>
+        <v>153.480106533333</v>
       </c>
       <c r="T25" s="15" t="n">
         <f aca="false">IF(AND($A25&gt;$B$100,S25&gt;=0),1,0)</f>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="U25" s="12" t="n">
         <f aca="false">S25-SUM($E$5:E25)-(1+Premissas!$B$17)*SUM($C$5:C25)</f>
-        <v>-707.662882813334</v>
+        <v>-643.329893466667</v>
       </c>
       <c r="V25" s="12" t="n">
         <f aca="false">(G25+H25)*Premissas!$B$21</f>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="X25" s="12" t="n">
         <f aca="false">X24-Y24+C25*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y25" s="12" t="n">
         <f aca="false">IF(OR(X25&gt;=Premissas!$B$13,B25=DATE(YEAR(B25),MONTH(B25)+1,0)),X25,0)</f>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z25" s="12" t="n">
         <f aca="false">Z24-AA24+C25/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA25" s="12" t="n">
         <f aca="false">IF(OR(Z25&gt;=Premissas!$B$14,B25=DATE(YEAR(B25),MONTH(B25)+1,0)),Z25,0)</f>
@@ -6026,11 +6026,11 @@
       </c>
       <c r="K26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="O26" s="12" t="n">
         <f aca="false">IF($A26-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P26" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A26-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A26-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A26-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A26-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6054,11 +6054,11 @@
       </c>
       <c r="R26" s="12" t="n">
         <f aca="false">E26+F26+SUM(I26:Q26)</f>
-        <v>223.195866666667</v>
+        <v>202.905333333333</v>
       </c>
       <c r="S26" s="12" t="n">
         <f aca="false">S25+R26</f>
-        <v>392.023983853333</v>
+        <v>356.385439866667</v>
       </c>
       <c r="T26" s="15" t="n">
         <f aca="false">IF(AND($A26&gt;$B$100,S26&gt;=0),1,0)</f>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="U26" s="12" t="n">
         <f aca="false">S26-SUM($E$5:E26)-(1+Premissas!$B$17)*SUM($C$5:C26)</f>
-        <v>-484.467016146667</v>
+        <v>-440.424560133333</v>
       </c>
       <c r="V26" s="12" t="n">
         <f aca="false">(G26+H26)*Premissas!$B$21</f>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="X26" s="12" t="n">
         <f aca="false">X25-Y25+C26*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y26" s="12" t="n">
         <f aca="false">IF(OR(X26&gt;=Premissas!$B$13,B26=DATE(YEAR(B26),MONTH(B26)+1,0)),X26,0)</f>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="Z26" s="12" t="n">
         <f aca="false">Z25-AA25+C26/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA26" s="12" t="n">
         <f aca="false">IF(OR(Z26&gt;=Premissas!$B$14,B26=DATE(YEAR(B26),MONTH(B26)+1,0)),Z26,0)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="K27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O27" s="12" t="n">
         <f aca="false">IF($A27-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P27" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A27-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A27-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A27-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A27-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6167,11 +6167,11 @@
       </c>
       <c r="R27" s="12" t="n">
         <f aca="false">E27+F27+SUM(I27:Q27)</f>
-        <v>223.195866666667</v>
+        <v>202.905333333333</v>
       </c>
       <c r="S27" s="12" t="n">
         <f aca="false">S26+R27</f>
-        <v>615.21985052</v>
+        <v>559.2907732</v>
       </c>
       <c r="T27" s="15" t="n">
         <f aca="false">IF(AND($A27&gt;$B$100,S27&gt;=0),1,0)</f>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="U27" s="12" t="n">
         <f aca="false">S27-SUM($E$5:E27)-(1+Premissas!$B$17)*SUM($C$5:C27)</f>
-        <v>-261.27114948</v>
+        <v>-237.5192268</v>
       </c>
       <c r="V27" s="12" t="n">
         <f aca="false">(G27+H27)*Premissas!$B$21</f>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="X27" s="12" t="n">
         <f aca="false">X26-Y26+C27*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y27" s="12" t="n">
         <f aca="false">IF(OR(X27&gt;=Premissas!$B$13,B27=DATE(YEAR(B27),MONTH(B27)+1,0)),X27,0)</f>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="Z27" s="12" t="n">
         <f aca="false">Z26-AA26+C27/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA27" s="12" t="n">
         <f aca="false">IF(OR(Z27&gt;=Premissas!$B$14,B27=DATE(YEAR(B27),MONTH(B27)+1,0)),Z27,0)</f>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="K28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="O28" s="12" t="n">
         <f aca="false">IF($A28-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P28" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A28-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A28-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A28-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A28-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6280,11 +6280,11 @@
       </c>
       <c r="R28" s="12" t="n">
         <f aca="false">E28+F28+SUM(I28:Q28)</f>
-        <v>-20.1934333333333</v>
+        <v>-18.3576666666667</v>
       </c>
       <c r="S28" s="12" t="n">
         <f aca="false">S27+R28</f>
-        <v>595.026417186666</v>
+        <v>540.933106533333</v>
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(AND($A28&gt;$B$100,S28&gt;=0),1,0)</f>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="U28" s="12" t="n">
         <f aca="false">S28-SUM($E$5:E28)-(1+Premissas!$B$17)*SUM($C$5:C28)</f>
-        <v>-281.464582813334</v>
+        <v>-255.876893466667</v>
       </c>
       <c r="V28" s="12" t="n">
         <f aca="false">(G28+H28)*Premissas!$B$21</f>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="X28" s="12" t="n">
         <f aca="false">X27-Y27+C28*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y28" s="12" t="n">
         <f aca="false">IF(OR(X28&gt;=Premissas!$B$13,B28=DATE(YEAR(B28),MONTH(B28)+1,0)),X28,0)</f>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="Z28" s="12" t="n">
         <f aca="false">Z27-AA27+C28/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA28" s="12" t="n">
         <f aca="false">IF(OR(Z28&gt;=Premissas!$B$14,B28=DATE(YEAR(B28),MONTH(B28)+1,0)),Z28,0)</f>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="K29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(Premissas!$B$59*Unitário!$B$22+(1-Premissas!$B$62)*(Premissas!$B$61*Unitário!$B$24+Premissas!$B$63*Unitário!$B$25)-Premissas!$B$62*((1-Premissas!$B$61)*Unitário!$B$24+(1-Premissas!$B$63)*Unitário!$B$25)-Premissas!$B$41)</f>
-        <v>-5.13333333333333</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="L29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O29" s="12" t="n">
         <f aca="false">IF($A29-(Premissas!$B$54+Premissas!$B$57)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$54+Premissas!$B$57)),0)*Premissas!$B$27*(-Premissas!$B$52-Premissas!$B$41+(1-Premissas!$B$62)*Premissas!$B$31+Premissas!$B$59*Unitário!$B$22)</f>
-        <v>-15.0601</v>
+        <v>-13.691</v>
       </c>
       <c r="P29" s="12" t="n">
         <f aca="false">-Premissas!$B$42*(IF($A29-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A29-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*Premissas!$B$51+IF($A29-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A29-(Premissas!$B$56)),0)*(1-Premissas!$B$27)*Premissas!$B$52)</f>
@@ -6393,11 +6393,11 @@
       </c>
       <c r="R29" s="12" t="n">
         <f aca="false">E29+F29+SUM(I29:Q29)</f>
-        <v>-20.1934333333333</v>
+        <v>-18.3576666666667</v>
       </c>
       <c r="S29" s="12" t="n">
         <f aca="false">S28+R29</f>
-        <v>574.832983853333</v>
+        <v>522.575439866667</v>
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(AND($A29&gt;$B$100,S29&gt;=0),1,0)</f>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="U29" s="12" t="n">
         <f aca="false">S29-SUM($E$5:E29)-(1+Premissas!$B$17)*SUM($C$5:C29)</f>
-        <v>-301.658016146667</v>
+        <v>-274.234560133333</v>
       </c>
       <c r="V29" s="12" t="n">
         <f aca="false">(G29+H29)*Premissas!$B$21</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="X29" s="12" t="n">
         <f aca="false">X28-Y28+C29*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y29" s="12" t="n">
         <f aca="false">IF(OR(X29&gt;=Premissas!$B$13,B29=DATE(YEAR(B29),MONTH(B29)+1,0)),X29,0)</f>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="Z29" s="12" t="n">
         <f aca="false">Z28-AA28+C29/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA29" s="12" t="n">
         <f aca="false">IF(OR(Z29&gt;=Premissas!$B$14,B29=DATE(YEAR(B29),MONTH(B29)+1,0)),Z29,0)</f>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L30" s="12" t="n">
         <f aca="false">IF($A30-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A30-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M30" s="12" t="n">
         <f aca="false">IF($A30-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A30-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="R30" s="12" t="n">
         <f aca="false">E30+F30+SUM(I30:Q30)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S30" s="12" t="n">
         <f aca="false">S29+R30</f>
-        <v>818.222283853333</v>
+        <v>743.838439866667</v>
       </c>
       <c r="T30" s="15" t="n">
         <f aca="false">IF(AND($A30&gt;$B$100,S30&gt;=0),1,0)</f>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="U30" s="12" t="n">
         <f aca="false">S30-SUM($E$5:E30)-(1+Premissas!$B$17)*SUM($C$5:C30)</f>
-        <v>-58.2687161466671</v>
+        <v>-52.9715601333334</v>
       </c>
       <c r="V30" s="12" t="n">
         <f aca="false">(G30+H30)*Premissas!$B$21</f>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="X30" s="12" t="n">
         <f aca="false">X29-Y29+C30*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y30" s="12" t="n">
         <f aca="false">IF(OR(X30&gt;=Premissas!$B$13,B30=DATE(YEAR(B30),MONTH(B30)+1,0)),X30,0)</f>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="Z30" s="12" t="n">
         <f aca="false">Z29-AA29+C30/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA30" s="12" t="n">
         <f aca="false">IF(OR(Z30&gt;=Premissas!$B$14,B30=DATE(YEAR(B30),MONTH(B30)+1,0)),Z30,0)</f>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="L31" s="12" t="n">
         <f aca="false">IF($A31-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A31-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M31" s="12" t="n">
         <f aca="false">IF($A31-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A31-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6619,11 +6619,11 @@
       </c>
       <c r="R31" s="12" t="n">
         <f aca="false">E31+F31+SUM(I31:Q31)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S31" s="12" t="n">
         <f aca="false">S30+R31</f>
-        <v>1061.61158385333</v>
+        <v>965.101439866667</v>
       </c>
       <c r="T31" s="15" t="n">
         <f aca="false">IF(AND($A31&gt;$B$100,S31&gt;=0),1,0)</f>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="U31" s="12" t="n">
         <f aca="false">S31-SUM($E$5:E31)-(1+Premissas!$B$17)*SUM($C$5:C31)</f>
-        <v>185.120583853333</v>
+        <v>168.291439866667</v>
       </c>
       <c r="V31" s="12" t="n">
         <f aca="false">(G31+H31)*Premissas!$B$21</f>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="X31" s="12" t="n">
         <f aca="false">X30-Y30+C31*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y31" s="12" t="n">
         <f aca="false">IF(OR(X31&gt;=Premissas!$B$13,B31=DATE(YEAR(B31),MONTH(B31)+1,0)),X31,0)</f>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="Z31" s="12" t="n">
         <f aca="false">Z30-AA30+C31/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA31" s="12" t="n">
         <f aca="false">IF(OR(Z31&gt;=Premissas!$B$14,B31=DATE(YEAR(B31),MONTH(B31)+1,0)),Z31,0)</f>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="L32" s="12" t="n">
         <f aca="false">IF($A32-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A32-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M32" s="12" t="n">
         <f aca="false">IF($A32-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A32-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6732,11 +6732,11 @@
       </c>
       <c r="R32" s="12" t="n">
         <f aca="false">E32+F32+SUM(I32:Q32)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S32" s="12" t="n">
         <f aca="false">S31+R32</f>
-        <v>1305.00088385333</v>
+        <v>1186.36443986667</v>
       </c>
       <c r="T32" s="15" t="n">
         <f aca="false">IF(AND($A32&gt;$B$100,S32&gt;=0),1,0)</f>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="U32" s="12" t="n">
         <f aca="false">S32-SUM($E$5:E32)-(1+Premissas!$B$17)*SUM($C$5:C32)</f>
-        <v>428.509883853333</v>
+        <v>389.554439866667</v>
       </c>
       <c r="V32" s="12" t="n">
         <f aca="false">(G32+H32)*Premissas!$B$21</f>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="X32" s="12" t="n">
         <f aca="false">X31-Y31+C32*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y32" s="12" t="n">
         <f aca="false">IF(OR(X32&gt;=Premissas!$B$13,B32=DATE(YEAR(B32),MONTH(B32)+1,0)),X32,0)</f>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="Z32" s="12" t="n">
         <f aca="false">Z31-AA31+C32/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA32" s="12" t="n">
         <f aca="false">IF(OR(Z32&gt;=Premissas!$B$14,B32=DATE(YEAR(B32),MONTH(B32)+1,0)),Z32,0)</f>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="L33" s="12" t="n">
         <f aca="false">IF($A33-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A33-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M33" s="12" t="n">
         <f aca="false">IF($A33-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A33-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6845,11 +6845,11 @@
       </c>
       <c r="R33" s="12" t="n">
         <f aca="false">E33+F33+SUM(I33:Q33)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S33" s="12" t="n">
         <f aca="false">S32+R33</f>
-        <v>1548.39018385333</v>
+        <v>1407.62743986667</v>
       </c>
       <c r="T33" s="15" t="n">
         <f aca="false">IF(AND($A33&gt;$B$100,S33&gt;=0),1,0)</f>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="U33" s="12" t="n">
         <f aca="false">S33-SUM($E$5:E33)-(1+Premissas!$B$17)*SUM($C$5:C33)</f>
-        <v>671.899183853333</v>
+        <v>610.817439866667</v>
       </c>
       <c r="V33" s="12" t="n">
         <f aca="false">(G33+H33)*Premissas!$B$21</f>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="X33" s="12" t="n">
         <f aca="false">X32-Y32+C33*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y33" s="12" t="n">
         <f aca="false">IF(OR(X33&gt;=Premissas!$B$13,B33=DATE(YEAR(B33),MONTH(B33)+1,0)),X33,0)</f>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z33" s="12" t="n">
         <f aca="false">Z32-AA32+C33/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA33" s="12" t="n">
         <f aca="false">IF(OR(Z33&gt;=Premissas!$B$14,B33=DATE(YEAR(B33),MONTH(B33)+1,0)),Z33,0)</f>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L34" s="12" t="n">
         <f aca="false">IF($A34-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A34-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M34" s="12" t="n">
         <f aca="false">IF($A34-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A34-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -6958,11 +6958,11 @@
       </c>
       <c r="R34" s="12" t="n">
         <f aca="false">E34+F34+SUM(I34:Q34)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S34" s="12" t="n">
         <f aca="false">S33+R34</f>
-        <v>1791.77948385333</v>
+        <v>1628.89043986667</v>
       </c>
       <c r="T34" s="15" t="n">
         <f aca="false">IF(AND($A34&gt;$B$100,S34&gt;=0),1,0)</f>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="U34" s="12" t="n">
         <f aca="false">S34-SUM($E$5:E34)-(1+Premissas!$B$17)*SUM($C$5:C34)</f>
-        <v>915.288483853333</v>
+        <v>832.080439866667</v>
       </c>
       <c r="V34" s="12" t="n">
         <f aca="false">(G34+H34)*Premissas!$B$21</f>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="X34" s="12" t="n">
         <f aca="false">X33-Y33+C34*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y34" s="12" t="n">
         <f aca="false">IF(OR(X34&gt;=Premissas!$B$13,B34=DATE(YEAR(B34),MONTH(B34)+1,0)),X34,0)</f>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="Z34" s="12" t="n">
         <f aca="false">Z33-AA33+C34/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA34" s="12" t="n">
         <f aca="false">IF(OR(Z34&gt;=Premissas!$B$14,B34=DATE(YEAR(B34),MONTH(B34)+1,0)),Z34,0)</f>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="L35" s="12" t="n">
         <f aca="false">IF($A35-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A35-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M35" s="12" t="n">
         <f aca="false">IF($A35-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A35-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -7071,11 +7071,11 @@
       </c>
       <c r="R35" s="12" t="n">
         <f aca="false">E35+F35+SUM(I35:Q35)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S35" s="12" t="n">
         <f aca="false">S34+R35</f>
-        <v>2035.16878385333</v>
+        <v>1850.15343986667</v>
       </c>
       <c r="T35" s="15" t="n">
         <f aca="false">IF(AND($A35&gt;$B$100,S35&gt;=0),1,0)</f>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="U35" s="12" t="n">
         <f aca="false">S35-SUM($E$5:E35)-(1+Premissas!$B$17)*SUM($C$5:C35)</f>
-        <v>1158.67778385333</v>
+        <v>1053.34343986667</v>
       </c>
       <c r="V35" s="12" t="n">
         <f aca="false">(G35+H35)*Premissas!$B$21</f>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="X35" s="12" t="n">
         <f aca="false">X34-Y34+C35*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y35" s="12" t="n">
         <f aca="false">IF(OR(X35&gt;=Premissas!$B$13,B35=DATE(YEAR(B35),MONTH(B35)+1,0)),X35,0)</f>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z35" s="12" t="n">
         <f aca="false">Z34-AA34+C35/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA35" s="12" t="n">
         <f aca="false">IF(OR(Z35&gt;=Premissas!$B$14,B35=DATE(YEAR(B35),MONTH(B35)+1,0)),Z35,0)</f>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L36" s="12" t="n">
         <f aca="false">IF($A36-(Premissas!$B$54+Premissas!$B$55)&gt;=1,INDEX($G$5:$G$94,$A36-(Premissas!$B$54+Premissas!$B$55)),0)*Unitário!$B$21*(Premissas!$B$51-(1-Premissas!$B$61)*Unitário!$B$24-(1-Premissas!$B$63)*Unitário!$B$25-(1-Premissas!$B$59)*Unitário!$B$22)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="M36" s="12" t="n">
         <f aca="false">IF($A36-(Premissas!$B$56)&gt;=1,INDEX($H$5:$H$94,$A36-(Premissas!$B$56)),0)*(Premissas!$B$52-Unitário!$B$27)</f>
@@ -7184,11 +7184,11 @@
       </c>
       <c r="R36" s="12" t="n">
         <f aca="false">E36+F36+SUM(I36:Q36)</f>
-        <v>243.3893</v>
+        <v>221.263</v>
       </c>
       <c r="S36" s="12" t="n">
         <f aca="false">S35+R36</f>
-        <v>2278.55808385333</v>
+        <v>2071.41643986667</v>
       </c>
       <c r="T36" s="15" t="n">
         <f aca="false">IF(AND($A36&gt;$B$100,S36&gt;=0),1,0)</f>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="U36" s="12" t="n">
         <f aca="false">S36-SUM($E$5:E36)-(1+Premissas!$B$17)*SUM($C$5:C36)</f>
-        <v>1402.06708385333</v>
+        <v>1274.60643986667</v>
       </c>
       <c r="V36" s="12" t="n">
         <f aca="false">(G36+H36)*Premissas!$B$21</f>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="X36" s="12" t="n">
         <f aca="false">X35-Y35+C36*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y36" s="12" t="n">
         <f aca="false">IF(OR(X36&gt;=Premissas!$B$13,B36=DATE(YEAR(B36),MONTH(B36)+1,0)),X36,0)</f>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="Z36" s="12" t="n">
         <f aca="false">Z35-AA35+C36/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA36" s="12" t="n">
         <f aca="false">IF(OR(Z36&gt;=Premissas!$B$14,B36=DATE(YEAR(B36),MONTH(B36)+1,0)),Z36,0)</f>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="S37" s="12" t="n">
         <f aca="false">S36+R37</f>
-        <v>2278.55808385333</v>
+        <v>2071.41643986667</v>
       </c>
       <c r="T37" s="15" t="n">
         <f aca="false">IF(AND($A37&gt;$B$100,S37&gt;=0),1,0)</f>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="U37" s="12" t="n">
         <f aca="false">S37-SUM($E$5:E37)-(1+Premissas!$B$17)*SUM($C$5:C37)</f>
-        <v>1402.06708385333</v>
+        <v>1274.60643986667</v>
       </c>
       <c r="V37" s="12" t="n">
         <f aca="false">(G37+H37)*Premissas!$B$21</f>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="X37" s="12" t="n">
         <f aca="false">X36-Y36+C37*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y37" s="12" t="n">
         <f aca="false">IF(OR(X37&gt;=Premissas!$B$13,B37=DATE(YEAR(B37),MONTH(B37)+1,0)),X37,0)</f>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="Z37" s="12" t="n">
         <f aca="false">Z36-AA36+C37/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA37" s="12" t="n">
         <f aca="false">IF(OR(Z37&gt;=Premissas!$B$14,B37=DATE(YEAR(B37),MONTH(B37)+1,0)),Z37,0)</f>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="S38" s="12" t="n">
         <f aca="false">S37+R38</f>
-        <v>2278.55808385333</v>
+        <v>2071.41643986667</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">IF(AND($A38&gt;$B$100,S38&gt;=0),1,0)</f>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="U38" s="12" t="n">
         <f aca="false">S38-SUM($E$5:E38)-(1+Premissas!$B$17)*SUM($C$5:C38)</f>
-        <v>1402.06708385333</v>
+        <v>1274.60643986667</v>
       </c>
       <c r="V38" s="12" t="n">
         <f aca="false">(G38+H38)*Premissas!$B$21</f>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="X38" s="12" t="n">
         <f aca="false">X37-Y37+C38*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y38" s="12" t="n">
         <f aca="false">IF(OR(X38&gt;=Premissas!$B$13,B38=DATE(YEAR(B38),MONTH(B38)+1,0)),X38,0)</f>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Z38" s="12" t="n">
         <f aca="false">Z37-AA37+C38/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA38" s="12" t="n">
         <f aca="false">IF(OR(Z38&gt;=Premissas!$B$14,B38=DATE(YEAR(B38),MONTH(B38)+1,0)),Z38,0)</f>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="S39" s="12" t="n">
         <f aca="false">S38+R39</f>
-        <v>2278.55808385333</v>
+        <v>2071.41643986667</v>
       </c>
       <c r="T39" s="15" t="n">
         <f aca="false">IF(AND($A39&gt;$B$100,S39&gt;=0),1,0)</f>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="U39" s="12" t="n">
         <f aca="false">S39-SUM($E$5:E39)-(1+Premissas!$B$17)*SUM($C$5:C39)</f>
-        <v>1402.06708385333</v>
+        <v>1274.60643986667</v>
       </c>
       <c r="V39" s="12" t="n">
         <f aca="false">(G39+H39)*Premissas!$B$21</f>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="X39" s="12" t="n">
         <f aca="false">X38-Y38+C39*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y39" s="12" t="n">
         <f aca="false">IF(OR(X39&gt;=Premissas!$B$13,B39=DATE(YEAR(B39),MONTH(B39)+1,0)),X39,0)</f>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="Z39" s="12" t="n">
         <f aca="false">Z38-AA38+C39/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA39" s="12" t="n">
         <f aca="false">IF(OR(Z39&gt;=Premissas!$B$14,B39=DATE(YEAR(B39),MONTH(B39)+1,0)),Z39,0)</f>
@@ -7584,11 +7584,11 @@
       </c>
       <c r="E40" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A40,$Y$5:$Y$94)</f>
-        <v>-813.8845</v>
+        <v>-739.895</v>
       </c>
       <c r="F40" s="12" t="n">
         <f aca="false">-SUMIF($W$5:$W$94,A40,$V$5:$V$94)-SUMIF($AB$5:$AB$94,A40,$AA$5:$AA$94)</f>
-        <v>-129.726666666667</v>
+        <v>-117.933333333333</v>
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">C40/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
@@ -7636,11 +7636,11 @@
       </c>
       <c r="R40" s="12" t="n">
         <f aca="false">E40+F40+SUM(I40:Q40)</f>
-        <v>-1001.10116666667</v>
+        <v>-915.318333333334</v>
       </c>
       <c r="S40" s="12" t="n">
         <f aca="false">S39+R40</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T40" s="15" t="n">
         <f aca="false">IF(AND($A40&gt;$B$100,S40&gt;=0),1,0)</f>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="U40" s="12" t="n">
         <f aca="false">S40-SUM($E$5:E40)-(1+Premissas!$B$17)*SUM($C$5:C40)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V40" s="12" t="n">
         <f aca="false">(G40+H40)*Premissas!$B$21</f>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="X40" s="12" t="n">
         <f aca="false">X39-Y39+C40*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y40" s="12" t="n">
         <f aca="false">IF(OR(X40&gt;=Premissas!$B$13,B40=DATE(YEAR(B40),MONTH(B40)+1,0)),X40,0)</f>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z40" s="12" t="n">
         <f aca="false">Z39-AA39+C40/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA40" s="12" t="n">
         <f aca="false">IF(OR(Z40&gt;=Premissas!$B$14,B40=DATE(YEAR(B40),MONTH(B40)+1,0)),Z40,0)</f>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="S41" s="12" t="n">
         <f aca="false">S40+R41</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T41" s="15" t="n">
         <f aca="false">IF(AND($A41&gt;$B$100,S41&gt;=0),1,0)</f>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="U41" s="12" t="n">
         <f aca="false">S41-SUM($E$5:E41)-(1+Premissas!$B$17)*SUM($C$5:C41)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V41" s="12" t="n">
         <f aca="false">(G41+H41)*Premissas!$B$21</f>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="X41" s="12" t="n">
         <f aca="false">X40-Y40+C41*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y41" s="12" t="n">
         <f aca="false">IF(OR(X41&gt;=Premissas!$B$13,B41=DATE(YEAR(B41),MONTH(B41)+1,0)),X41,0)</f>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="Z41" s="12" t="n">
         <f aca="false">Z40-AA40+C41/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA41" s="12" t="n">
         <f aca="false">IF(OR(Z41&gt;=Premissas!$B$14,B41=DATE(YEAR(B41),MONTH(B41)+1,0)),Z41,0)</f>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="S42" s="12" t="n">
         <f aca="false">S41+R42</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T42" s="15" t="n">
         <f aca="false">IF(AND($A42&gt;$B$100,S42&gt;=0),1,0)</f>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="U42" s="12" t="n">
         <f aca="false">S42-SUM($E$5:E42)-(1+Premissas!$B$17)*SUM($C$5:C42)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V42" s="12" t="n">
         <f aca="false">(G42+H42)*Premissas!$B$21</f>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="X42" s="12" t="n">
         <f aca="false">X41-Y41+C42*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y42" s="12" t="n">
         <f aca="false">IF(OR(X42&gt;=Premissas!$B$13,B42=DATE(YEAR(B42),MONTH(B42)+1,0)),X42,0)</f>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="Z42" s="12" t="n">
         <f aca="false">Z41-AA41+C42/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA42" s="12" t="n">
         <f aca="false">IF(OR(Z42&gt;=Premissas!$B$14,B42=DATE(YEAR(B42),MONTH(B42)+1,0)),Z42,0)</f>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="S43" s="12" t="n">
         <f aca="false">S42+R43</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T43" s="15" t="n">
         <f aca="false">IF(AND($A43&gt;$B$100,S43&gt;=0),1,0)</f>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="U43" s="12" t="n">
         <f aca="false">S43-SUM($E$5:E43)-(1+Premissas!$B$17)*SUM($C$5:C43)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V43" s="12" t="n">
         <f aca="false">(G43+H43)*Premissas!$B$21</f>
@@ -7999,19 +7999,19 @@
       </c>
       <c r="X43" s="12" t="n">
         <f aca="false">X42-Y42+C43*(1+Premissas!$B$17)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Y43" s="12" t="n">
         <f aca="false">IF(OR(X43&gt;=Premissas!$B$13,B43=DATE(YEAR(B43),MONTH(B43)+1,0)),X43,0)</f>
-        <v>62.6065</v>
+        <v>56.915</v>
       </c>
       <c r="Z43" s="12" t="n">
         <f aca="false">Z42-AA42+C43/Premissas!$B$18*Premissas!$B$20</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA43" s="12" t="n">
         <f aca="false">IF(OR(Z43&gt;=Premissas!$B$14,B43=DATE(YEAR(B43),MONTH(B43)+1,0)),Z43,0)</f>
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AB43" s="15" t="n">
         <f aca="false">IF(AA43&gt;0,IF(DAY(B43)&lt;=Premissas!$B$12,DATE(YEAR(B43),MONTH(B43),Premissas!$B$16),DATE(YEAR(B43),MONTH(B43)+1,Premissas!$B$16))-Premissas!$B$11+1-Premissas!$B$15,0)</f>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="S44" s="12" t="n">
         <f aca="false">S43+R44</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">IF(AND($A44&gt;$B$100,S44&gt;=0),1,0)</f>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="U44" s="12" t="n">
         <f aca="false">S44-SUM($E$5:E44)-(1+Premissas!$B$17)*SUM($C$5:C44)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V44" s="12" t="n">
         <f aca="false">(G44+H44)*Premissas!$B$21</f>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="S45" s="12" t="n">
         <f aca="false">S44+R45</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T45" s="15" t="n">
         <f aca="false">IF(AND($A45&gt;$B$100,S45&gt;=0),1,0)</f>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="U45" s="12" t="n">
         <f aca="false">S45-SUM($E$5:E45)-(1+Premissas!$B$17)*SUM($C$5:C45)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V45" s="12" t="n">
         <f aca="false">(G45+H45)*Premissas!$B$21</f>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="S46" s="12" t="n">
         <f aca="false">S45+R46</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">IF(AND($A46&gt;$B$100,S46&gt;=0),1,0)</f>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="U46" s="12" t="n">
         <f aca="false">S46-SUM($E$5:E46)-(1+Premissas!$B$17)*SUM($C$5:C46)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V46" s="12" t="n">
         <f aca="false">(G46+H46)*Premissas!$B$21</f>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="S47" s="12" t="n">
         <f aca="false">S46+R47</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">IF(AND($A47&gt;$B$100,S47&gt;=0),1,0)</f>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="U47" s="12" t="n">
         <f aca="false">S47-SUM($E$5:E47)-(1+Premissas!$B$17)*SUM($C$5:C47)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V47" s="12" t="n">
         <f aca="false">(G47+H47)*Premissas!$B$21</f>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="S48" s="12" t="n">
         <f aca="false">S47+R48</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">IF(AND($A48&gt;$B$100,S48&gt;=0),1,0)</f>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="U48" s="12" t="n">
         <f aca="false">S48-SUM($E$5:E48)-(1+Premissas!$B$17)*SUM($C$5:C48)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V48" s="12" t="n">
         <f aca="false">(G48+H48)*Premissas!$B$21</f>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="S49" s="12" t="n">
         <f aca="false">S48+R49</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">IF(AND($A49&gt;$B$100,S49&gt;=0),1,0)</f>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="U49" s="12" t="n">
         <f aca="false">S49-SUM($E$5:E49)-(1+Premissas!$B$17)*SUM($C$5:C49)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V49" s="12" t="n">
         <f aca="false">(G49+H49)*Premissas!$B$21</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="S50" s="12" t="n">
         <f aca="false">S49+R50</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T50" s="15" t="n">
         <f aca="false">IF(AND($A50&gt;$B$100,S50&gt;=0),1,0)</f>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="U50" s="12" t="n">
         <f aca="false">S50-SUM($E$5:E50)-(1+Premissas!$B$17)*SUM($C$5:C50)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V50" s="12" t="n">
         <f aca="false">(G50+H50)*Premissas!$B$21</f>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="S51" s="12" t="n">
         <f aca="false">S50+R51</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T51" s="15" t="n">
         <f aca="false">IF(AND($A51&gt;$B$100,S51&gt;=0),1,0)</f>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="U51" s="12" t="n">
         <f aca="false">S51-SUM($E$5:E51)-(1+Premissas!$B$17)*SUM($C$5:C51)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V51" s="12" t="n">
         <f aca="false">(G51+H51)*Premissas!$B$21</f>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="S52" s="12" t="n">
         <f aca="false">S51+R52</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T52" s="15" t="n">
         <f aca="false">IF(AND($A52&gt;$B$100,S52&gt;=0),1,0)</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="U52" s="12" t="n">
         <f aca="false">S52-SUM($E$5:E52)-(1+Premissas!$B$17)*SUM($C$5:C52)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V52" s="12" t="n">
         <f aca="false">(G52+H52)*Premissas!$B$21</f>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="S53" s="12" t="n">
         <f aca="false">S52+R53</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T53" s="15" t="n">
         <f aca="false">IF(AND($A53&gt;$B$100,S53&gt;=0),1,0)</f>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="U53" s="12" t="n">
         <f aca="false">S53-SUM($E$5:E53)-(1+Premissas!$B$17)*SUM($C$5:C53)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V53" s="12" t="n">
         <f aca="false">(G53+H53)*Premissas!$B$21</f>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="S54" s="12" t="n">
         <f aca="false">S53+R54</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T54" s="15" t="n">
         <f aca="false">IF(AND($A54&gt;$B$100,S54&gt;=0),1,0)</f>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="U54" s="12" t="n">
         <f aca="false">S54-SUM($E$5:E54)-(1+Premissas!$B$17)*SUM($C$5:C54)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V54" s="12" t="n">
         <f aca="false">(G54+H54)*Premissas!$B$21</f>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="S55" s="12" t="n">
         <f aca="false">S54+R55</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T55" s="15" t="n">
         <f aca="false">IF(AND($A55&gt;$B$100,S55&gt;=0),1,0)</f>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="U55" s="12" t="n">
         <f aca="false">S55-SUM($E$5:E55)-(1+Premissas!$B$17)*SUM($C$5:C55)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V55" s="12" t="n">
         <f aca="false">(G55+H55)*Premissas!$B$21</f>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="S56" s="12" t="n">
         <f aca="false">S55+R56</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T56" s="15" t="n">
         <f aca="false">IF(AND($A56&gt;$B$100,S56&gt;=0),1,0)</f>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="U56" s="12" t="n">
         <f aca="false">S56-SUM($E$5:E56)-(1+Premissas!$B$17)*SUM($C$5:C56)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V56" s="12" t="n">
         <f aca="false">(G56+H56)*Premissas!$B$21</f>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="S57" s="12" t="n">
         <f aca="false">S56+R57</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T57" s="15" t="n">
         <f aca="false">IF(AND($A57&gt;$B$100,S57&gt;=0),1,0)</f>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="U57" s="12" t="n">
         <f aca="false">S57-SUM($E$5:E57)-(1+Premissas!$B$17)*SUM($C$5:C57)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V57" s="12" t="n">
         <f aca="false">(G57+H57)*Premissas!$B$21</f>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="S58" s="12" t="n">
         <f aca="false">S57+R58</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T58" s="15" t="n">
         <f aca="false">IF(AND($A58&gt;$B$100,S58&gt;=0),1,0)</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="U58" s="12" t="n">
         <f aca="false">S58-SUM($E$5:E58)-(1+Premissas!$B$17)*SUM($C$5:C58)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V58" s="12" t="n">
         <f aca="false">(G58+H58)*Premissas!$B$21</f>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="S59" s="12" t="n">
         <f aca="false">S58+R59</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T59" s="15" t="n">
         <f aca="false">IF(AND($A59&gt;$B$100,S59&gt;=0),1,0)</f>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="U59" s="12" t="n">
         <f aca="false">S59-SUM($E$5:E59)-(1+Premissas!$B$17)*SUM($C$5:C59)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V59" s="12" t="n">
         <f aca="false">(G59+H59)*Premissas!$B$21</f>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="S60" s="12" t="n">
         <f aca="false">S59+R60</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T60" s="15" t="n">
         <f aca="false">IF(AND($A60&gt;$B$100,S60&gt;=0),1,0)</f>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="U60" s="12" t="n">
         <f aca="false">S60-SUM($E$5:E60)-(1+Premissas!$B$17)*SUM($C$5:C60)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V60" s="12" t="n">
         <f aca="false">(G60+H60)*Premissas!$B$21</f>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="S61" s="12" t="n">
         <f aca="false">S60+R61</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T61" s="15" t="n">
         <f aca="false">IF(AND($A61&gt;$B$100,S61&gt;=0),1,0)</f>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="U61" s="12" t="n">
         <f aca="false">S61-SUM($E$5:E61)-(1+Premissas!$B$17)*SUM($C$5:C61)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V61" s="12" t="n">
         <f aca="false">(G61+H61)*Premissas!$B$21</f>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="S62" s="12" t="n">
         <f aca="false">S61+R62</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T62" s="15" t="n">
         <f aca="false">IF(AND($A62&gt;$B$100,S62&gt;=0),1,0)</f>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="U62" s="12" t="n">
         <f aca="false">S62-SUM($E$5:E62)-(1+Premissas!$B$17)*SUM($C$5:C62)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V62" s="12" t="n">
         <f aca="false">(G62+H62)*Premissas!$B$21</f>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="S63" s="12" t="n">
         <f aca="false">S62+R63</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T63" s="15" t="n">
         <f aca="false">IF(AND($A63&gt;$B$100,S63&gt;=0),1,0)</f>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="U63" s="12" t="n">
         <f aca="false">S63-SUM($E$5:E63)-(1+Premissas!$B$17)*SUM($C$5:C63)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V63" s="12" t="n">
         <f aca="false">(G63+H63)*Premissas!$B$21</f>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="S64" s="12" t="n">
         <f aca="false">S63+R64</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T64" s="15" t="n">
         <f aca="false">IF(AND($A64&gt;$B$100,S64&gt;=0),1,0)</f>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="U64" s="12" t="n">
         <f aca="false">S64-SUM($E$5:E64)-(1+Premissas!$B$17)*SUM($C$5:C64)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V64" s="12" t="n">
         <f aca="false">(G64+H64)*Premissas!$B$21</f>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="S65" s="12" t="n">
         <f aca="false">S64+R65</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T65" s="15" t="n">
         <f aca="false">IF(AND($A65&gt;$B$100,S65&gt;=0),1,0)</f>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="U65" s="12" t="n">
         <f aca="false">S65-SUM($E$5:E65)-(1+Premissas!$B$17)*SUM($C$5:C65)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V65" s="12" t="n">
         <f aca="false">(G65+H65)*Premissas!$B$21</f>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="S66" s="12" t="n">
         <f aca="false">S65+R66</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T66" s="15" t="n">
         <f aca="false">IF(AND($A66&gt;$B$100,S66&gt;=0),1,0)</f>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="U66" s="12" t="n">
         <f aca="false">S66-SUM($E$5:E66)-(1+Premissas!$B$17)*SUM($C$5:C66)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V66" s="12" t="n">
         <f aca="false">(G66+H66)*Premissas!$B$21</f>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="S67" s="12" t="n">
         <f aca="false">S66+R67</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T67" s="15" t="n">
         <f aca="false">IF(AND($A67&gt;$B$100,S67&gt;=0),1,0)</f>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="U67" s="12" t="n">
         <f aca="false">S67-SUM($E$5:E67)-(1+Premissas!$B$17)*SUM($C$5:C67)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V67" s="12" t="n">
         <f aca="false">(G67+H67)*Premissas!$B$21</f>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="S68" s="12" t="n">
         <f aca="false">S67+R68</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T68" s="15" t="n">
         <f aca="false">IF(AND($A68&gt;$B$100,S68&gt;=0),1,0)</f>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="U68" s="12" t="n">
         <f aca="false">S68-SUM($E$5:E68)-(1+Premissas!$B$17)*SUM($C$5:C68)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V68" s="12" t="n">
         <f aca="false">(G68+H68)*Premissas!$B$21</f>
@@ -10917,7 +10917,7 @@
       </c>
       <c r="S69" s="12" t="n">
         <f aca="false">S68+R69</f>
-        <v>1277.45691718667</v>
+        <v>1156.09810653333</v>
       </c>
       <c r="T69" s="15" t="n">
         <f aca="false">IF(AND($A69&gt;$B$100,S69&gt;=0),1,0)</f>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="U69" s="12" t="n">
         <f aca="false">S69-SUM($E$5:E69)-(1+Premissas!$B$17)*SUM($C$5:C69)</f>
-        <v>1214.85041718667</v>
+        <v>1099.18310653333</v>
       </c>
       <c r="V69" s="12" t="n">
         <f aca="false">(G69+H69)*Premissas!$B$21</f>
@@ -10974,11 +10974,11 @@
       </c>
       <c r="E70" s="12" t="n">
         <f aca="false">-SUMIF($D$5:$D$94,A70,$Y$5:$Y$94)</f>
-        <v>-62.6065</v>
+        <v>-56.915</v>
       </c>
       <c r="F70" s="12" t="n">
         <f aca="false">-SUMIF($W$5:$W$94,A70,$V$5:$V$94)-SUMIF($AB$5:$AB$94,A70,$AA$5:$AA$94)</f>
-        <v>-10.9266666666667</v>
+        <v>-9.93333333333334</v>
       </c>
       <c r="G70" s="29" t="n">
         <f aca="false">C70/Premissas!$B$18*Premissas!$B$19*Premissas!$B$23</f>
@@ -11026,11 +11026,11 @@
       </c>
       <c r="R70" s="12" t="n">
         <f aca="false">E70+F70+SUM(I70:Q70)</f>
-        <v>-131.023166666667</v>
+        <v>-124.338333333333</v>
       </c>
       <c r="S70" s="12" t="n">
         <f aca="false">S69+R70</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T70" s="15" t="n">
         <f aca="false">IF(AND($A70&gt;$B$100,S70&gt;=0),1,0)</f>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="U70" s="12" t="n">
         <f aca="false">S70-SUM($E$5:E70)-(1+Premissas!$B$17)*SUM($C$5:C70)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V70" s="12" t="n">
         <f aca="false">(G70+H70)*Premissas!$B$21</f>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="S71" s="12" t="n">
         <f aca="false">S70+R71</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T71" s="15" t="n">
         <f aca="false">IF(AND($A71&gt;$B$100,S71&gt;=0),1,0)</f>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="U71" s="12" t="n">
         <f aca="false">S71-SUM($E$5:E71)-(1+Premissas!$B$17)*SUM($C$5:C71)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V71" s="12" t="n">
         <f aca="false">(G71+H71)*Premissas!$B$21</f>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="S72" s="12" t="n">
         <f aca="false">S71+R72</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T72" s="15" t="n">
         <f aca="false">IF(AND($A72&gt;$B$100,S72&gt;=0),1,0)</f>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="U72" s="12" t="n">
         <f aca="false">S72-SUM($E$5:E72)-(1+Premissas!$B$17)*SUM($C$5:C72)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V72" s="12" t="n">
         <f aca="false">(G72+H72)*Premissas!$B$21</f>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="S73" s="12" t="n">
         <f aca="false">S72+R73</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T73" s="15" t="n">
         <f aca="false">IF(AND($A73&gt;$B$100,S73&gt;=0),1,0)</f>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="U73" s="12" t="n">
         <f aca="false">S73-SUM($E$5:E73)-(1+Premissas!$B$17)*SUM($C$5:C73)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V73" s="12" t="n">
         <f aca="false">(G73+H73)*Premissas!$B$21</f>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="S74" s="12" t="n">
         <f aca="false">S73+R74</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T74" s="15" t="n">
         <f aca="false">IF(AND($A74&gt;$B$100,S74&gt;=0),1,0)</f>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="U74" s="12" t="n">
         <f aca="false">S74-SUM($E$5:E74)-(1+Premissas!$B$17)*SUM($C$5:C74)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V74" s="12" t="n">
         <f aca="false">(G74+H74)*Premissas!$B$21</f>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="S75" s="12" t="n">
         <f aca="false">S74+R75</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T75" s="15" t="n">
         <f aca="false">IF(AND($A75&gt;$B$100,S75&gt;=0),1,0)</f>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="U75" s="12" t="n">
         <f aca="false">S75-SUM($E$5:E75)-(1+Premissas!$B$17)*SUM($C$5:C75)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V75" s="12" t="n">
         <f aca="false">(G75+H75)*Premissas!$B$21</f>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="S76" s="12" t="n">
         <f aca="false">S75+R76</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T76" s="15" t="n">
         <f aca="false">IF(AND($A76&gt;$B$100,S76&gt;=0),1,0)</f>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="U76" s="12" t="n">
         <f aca="false">S76-SUM($E$5:E76)-(1+Premissas!$B$17)*SUM($C$5:C76)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V76" s="12" t="n">
         <f aca="false">(G76+H76)*Premissas!$B$21</f>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="S77" s="12" t="n">
         <f aca="false">S76+R77</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T77" s="15" t="n">
         <f aca="false">IF(AND($A77&gt;$B$100,S77&gt;=0),1,0)</f>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="U77" s="12" t="n">
         <f aca="false">S77-SUM($E$5:E77)-(1+Premissas!$B$17)*SUM($C$5:C77)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V77" s="12" t="n">
         <f aca="false">(G77+H77)*Premissas!$B$21</f>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="S78" s="12" t="n">
         <f aca="false">S77+R78</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T78" s="15" t="n">
         <f aca="false">IF(AND($A78&gt;$B$100,S78&gt;=0),1,0)</f>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="U78" s="12" t="n">
         <f aca="false">S78-SUM($E$5:E78)-(1+Premissas!$B$17)*SUM($C$5:C78)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V78" s="12" t="n">
         <f aca="false">(G78+H78)*Premissas!$B$21</f>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="S79" s="12" t="n">
         <f aca="false">S78+R79</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T79" s="15" t="n">
         <f aca="false">IF(AND($A79&gt;$B$100,S79&gt;=0),1,0)</f>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="U79" s="12" t="n">
         <f aca="false">S79-SUM($E$5:E79)-(1+Premissas!$B$17)*SUM($C$5:C79)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V79" s="12" t="n">
         <f aca="false">(G79+H79)*Premissas!$B$21</f>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="S80" s="12" t="n">
         <f aca="false">S79+R80</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T80" s="15" t="n">
         <f aca="false">IF(AND($A80&gt;$B$100,S80&gt;=0),1,0)</f>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="U80" s="12" t="n">
         <f aca="false">S80-SUM($E$5:E80)-(1+Premissas!$B$17)*SUM($C$5:C80)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V80" s="12" t="n">
         <f aca="false">(G80+H80)*Premissas!$B$21</f>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="S81" s="12" t="n">
         <f aca="false">S80+R81</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T81" s="15" t="n">
         <f aca="false">IF(AND($A81&gt;$B$100,S81&gt;=0),1,0)</f>
@@ -12281,7 +12281,7 @@
       </c>
       <c r="U81" s="12" t="n">
         <f aca="false">S81-SUM($E$5:E81)-(1+Premissas!$B$17)*SUM($C$5:C81)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V81" s="12" t="n">
         <f aca="false">(G81+H81)*Premissas!$B$21</f>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="S82" s="12" t="n">
         <f aca="false">S81+R82</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T82" s="15" t="n">
         <f aca="false">IF(AND($A82&gt;$B$100,S82&gt;=0),1,0)</f>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="U82" s="12" t="n">
         <f aca="false">S82-SUM($E$5:E82)-(1+Premissas!$B$17)*SUM($C$5:C82)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V82" s="12" t="n">
         <f aca="false">(G82+H82)*Premissas!$B$21</f>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="S83" s="12" t="n">
         <f aca="false">S82+R83</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T83" s="15" t="n">
         <f aca="false">IF(AND($A83&gt;$B$100,S83&gt;=0),1,0)</f>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="U83" s="12" t="n">
         <f aca="false">S83-SUM($E$5:E83)-(1+Premissas!$B$17)*SUM($C$5:C83)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V83" s="12" t="n">
         <f aca="false">(G83+H83)*Premissas!$B$21</f>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="S84" s="12" t="n">
         <f aca="false">S83+R84</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T84" s="15" t="n">
         <f aca="false">IF(AND($A84&gt;$B$100,S84&gt;=0),1,0)</f>
@@ -12620,7 +12620,7 @@
       </c>
       <c r="U84" s="12" t="n">
         <f aca="false">S84-SUM($E$5:E84)-(1+Premissas!$B$17)*SUM($C$5:C84)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V84" s="12" t="n">
         <f aca="false">(G84+H84)*Premissas!$B$21</f>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="S85" s="12" t="n">
         <f aca="false">S84+R85</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T85" s="15" t="n">
         <f aca="false">IF(AND($A85&gt;$B$100,S85&gt;=0),1,0)</f>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="U85" s="12" t="n">
         <f aca="false">S85-SUM($E$5:E85)-(1+Premissas!$B$17)*SUM($C$5:C85)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V85" s="12" t="n">
         <f aca="false">(G85+H85)*Premissas!$B$21</f>
@@ -12838,7 +12838,7 @@
       </c>
       <c r="S86" s="12" t="n">
         <f aca="false">S85+R86</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T86" s="15" t="n">
         <f aca="false">IF(AND($A86&gt;$B$100,S86&gt;=0),1,0)</f>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="U86" s="12" t="n">
         <f aca="false">S86-SUM($E$5:E86)-(1+Premissas!$B$17)*SUM($C$5:C86)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V86" s="12" t="n">
         <f aca="false">(G86+H86)*Premissas!$B$21</f>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="S87" s="12" t="n">
         <f aca="false">S86+R87</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T87" s="15" t="n">
         <f aca="false">IF(AND($A87&gt;$B$100,S87&gt;=0),1,0)</f>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="U87" s="12" t="n">
         <f aca="false">S87-SUM($E$5:E87)-(1+Premissas!$B$17)*SUM($C$5:C87)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V87" s="12" t="n">
         <f aca="false">(G87+H87)*Premissas!$B$21</f>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="S88" s="12" t="n">
         <f aca="false">S87+R88</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T88" s="15" t="n">
         <f aca="false">IF(AND($A88&gt;$B$100,S88&gt;=0),1,0)</f>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="U88" s="12" t="n">
         <f aca="false">S88-SUM($E$5:E88)-(1+Premissas!$B$17)*SUM($C$5:C88)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V88" s="12" t="n">
         <f aca="false">(G88+H88)*Premissas!$B$21</f>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="S89" s="12" t="n">
         <f aca="false">S88+R89</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T89" s="15" t="n">
         <f aca="false">IF(AND($A89&gt;$B$100,S89&gt;=0),1,0)</f>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="U89" s="12" t="n">
         <f aca="false">S89-SUM($E$5:E89)-(1+Premissas!$B$17)*SUM($C$5:C89)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V89" s="12" t="n">
         <f aca="false">(G89+H89)*Premissas!$B$21</f>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="S90" s="12" t="n">
         <f aca="false">S89+R90</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T90" s="15" t="n">
         <f aca="false">IF(AND($A90&gt;$B$100,S90&gt;=0),1,0)</f>
@@ -13298,7 +13298,7 @@
       </c>
       <c r="U90" s="12" t="n">
         <f aca="false">S90-SUM($E$5:E90)-(1+Premissas!$B$17)*SUM($C$5:C90)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V90" s="12" t="n">
         <f aca="false">(G90+H90)*Premissas!$B$21</f>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="S91" s="12" t="n">
         <f aca="false">S90+R91</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T91" s="15" t="n">
         <f aca="false">IF(AND($A91&gt;$B$100,S91&gt;=0),1,0)</f>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="U91" s="12" t="n">
         <f aca="false">S91-SUM($E$5:E91)-(1+Premissas!$B$17)*SUM($C$5:C91)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V91" s="12" t="n">
         <f aca="false">(G91+H91)*Premissas!$B$21</f>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="S92" s="12" t="n">
         <f aca="false">S91+R92</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T92" s="15" t="n">
         <f aca="false">IF(AND($A92&gt;$B$100,S92&gt;=0),1,0)</f>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="U92" s="12" t="n">
         <f aca="false">S92-SUM($E$5:E92)-(1+Premissas!$B$17)*SUM($C$5:C92)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V92" s="12" t="n">
         <f aca="false">(G92+H92)*Premissas!$B$21</f>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="S93" s="12" t="n">
         <f aca="false">S92+R93</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T93" s="15" t="n">
         <f aca="false">IF(AND($A93&gt;$B$100,S93&gt;=0),1,0)</f>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="U93" s="12" t="n">
         <f aca="false">S93-SUM($E$5:E93)-(1+Premissas!$B$17)*SUM($C$5:C93)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V93" s="12" t="n">
         <f aca="false">(G93+H93)*Premissas!$B$21</f>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="S94" s="12" t="n">
         <f aca="false">S93+R94</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="T94" s="15" t="n">
         <f aca="false">IF(AND($A94&gt;$B$100,S94&gt;=0),1,0)</f>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="U94" s="12" t="n">
         <f aca="false">S94-SUM($E$5:E94)-(1+Premissas!$B$17)*SUM($C$5:C94)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
       <c r="V94" s="12" t="n">
         <f aca="false">(G94+H94)*Premissas!$B$21</f>
@@ -13787,51 +13787,51 @@
       </c>
       <c r="C95" s="14" t="n">
         <f aca="false">SUM(C5:C94)</f>
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="E95" s="14" t="n">
         <f aca="false">SUM(E5:E94)</f>
-        <v>-876.491</v>
+        <v>-796.81</v>
       </c>
       <c r="F95" s="14" t="n">
         <f aca="false">SUM(F5:F94)</f>
-        <v>-140.653333333333</v>
+        <v>-127.866666666667</v>
       </c>
       <c r="G95" s="31" t="n">
         <f aca="false">SUM(G5:G94)</f>
-        <v>35.9333333333333</v>
+        <v>32.6666666666667</v>
       </c>
       <c r="H95" s="31" t="n">
         <f aca="false">SUM(H5:H94)</f>
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="I95" s="14" t="n">
         <f aca="false">SUM(I5:I94)</f>
-        <v>-2391.723026</v>
+        <v>-2174.29366</v>
       </c>
       <c r="J95" s="14" t="n">
         <f aca="false">SUM(J5:J94)</f>
-        <v>345.56733442</v>
+        <v>314.1521222</v>
       </c>
       <c r="K95" s="14" t="n">
         <f aca="false">SUM(K5:K94)</f>
-        <v>-71.8666666666667</v>
+        <v>-65.3333333333333</v>
       </c>
       <c r="L95" s="14" t="n">
         <f aca="false">SUM(L5:L94)</f>
-        <v>3407.4502</v>
+        <v>3097.682</v>
       </c>
       <c r="M95" s="14" t="n">
         <f aca="false">SUM(M5:M94)</f>
-        <v>1738.9716421</v>
+        <v>1580.883311</v>
       </c>
       <c r="N95" s="14" t="n">
         <f aca="false">SUM(N5:N94)</f>
-        <v>-539</v>
+        <v>-490</v>
       </c>
       <c r="O95" s="14" t="n">
         <f aca="false">SUM(O5:O94)</f>
-        <v>-210.8414</v>
+        <v>-191.674</v>
       </c>
       <c r="P95" s="14" t="n">
         <f aca="false">SUM(P5:P94)</f>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="R95" s="14" t="n">
         <f aca="false">SUM(R5:R94)</f>
-        <v>1146.43375052</v>
+        <v>1031.7597732</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">MIN(S5:S94)</f>
-        <v>-827.567485873333</v>
+        <v>-752.334078066667</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="B102" s="14" t="n">
         <f aca="false">MIN(U5:U94)</f>
-        <v>-1704.05848587333</v>
+        <v>-1549.14407806667</v>
       </c>
     </row>
   </sheetData>
